--- a/research/traditional_assets/database/data/mexico/mexico_recreation.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_recreation.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.136</v>
+        <v>-0.0584</v>
       </c>
       <c r="G2">
-        <v>-0.3440514469453376</v>
+        <v>-0.2447916666666667</v>
       </c>
       <c r="H2">
-        <v>-0.3440514469453376</v>
+        <v>-0.2447916666666667</v>
       </c>
       <c r="I2">
-        <v>-0.8231511254019293</v>
+        <v>-0.1822916666666667</v>
       </c>
       <c r="J2">
-        <v>-0.8231511254019293</v>
+        <v>-0.1822916666666667</v>
       </c>
       <c r="K2">
-        <v>-22.2</v>
+        <v>-20.7</v>
       </c>
       <c r="L2">
-        <v>-0.7138263665594855</v>
+        <v>-0.359375</v>
       </c>
       <c r="M2">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.003216783216783217</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.004144144144144144</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.092</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>4.89</v>
+        <v>4.5</v>
       </c>
       <c r="V2">
-        <v>0.170979020979021</v>
+        <v>0.2486187845303867</v>
       </c>
       <c r="W2">
-        <v>-1.298245614035088</v>
+        <v>6.234939759036145</v>
       </c>
       <c r="X2">
-        <v>0.2816363319000345</v>
+        <v>0.708694281668633</v>
       </c>
       <c r="Y2">
-        <v>-1.579881945935122</v>
+        <v>5.526245477367512</v>
       </c>
       <c r="Z2">
-        <v>0.1936367598530602</v>
+        <v>0.4146868250539957</v>
       </c>
       <c r="AA2">
-        <v>-0.1593923167922296</v>
+        <v>-0.0755939524838013</v>
       </c>
       <c r="AB2">
-        <v>0.06959560608294224</v>
+        <v>0.1196589642480355</v>
       </c>
       <c r="AC2">
-        <v>-0.2289879228751719</v>
+        <v>-0.1952529167318368</v>
       </c>
       <c r="AD2">
-        <v>149.7</v>
+        <v>164.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>149.7</v>
+        <v>164.4</v>
       </c>
       <c r="AG2">
-        <v>144.81</v>
+        <v>159.9</v>
       </c>
       <c r="AH2">
-        <v>0.8395961862030287</v>
+        <v>0.9008219178082192</v>
       </c>
       <c r="AI2">
-        <v>1.022680694083891</v>
+        <v>1.0844327176781</v>
       </c>
       <c r="AJ2">
-        <v>0.8350729485035465</v>
+        <v>0.898314606741573</v>
       </c>
       <c r="AK2">
-        <v>1.023464555798996</v>
+        <v>1.087015635622026</v>
       </c>
       <c r="AL2">
-        <v>16</v>
+        <v>19.1</v>
       </c>
       <c r="AM2">
-        <v>15.813</v>
+        <v>18.825</v>
       </c>
       <c r="AN2">
-        <v>-5.96414342629482</v>
+        <v>-18.26666666666667</v>
       </c>
       <c r="AO2">
-        <v>-1.6</v>
+        <v>-0.5497382198952879</v>
       </c>
       <c r="AP2">
-        <v>-5.769322709163347</v>
+        <v>-17.76666666666667</v>
       </c>
       <c r="AQ2">
-        <v>-1.618921140833491</v>
+        <v>-0.5577689243027888</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.136</v>
+        <v>-0.0584</v>
       </c>
       <c r="G3">
-        <v>-0.3440514469453376</v>
+        <v>-0.2447916666666667</v>
       </c>
       <c r="H3">
-        <v>-0.3440514469453376</v>
+        <v>-0.2447916666666667</v>
       </c>
       <c r="I3">
-        <v>-0.8231511254019293</v>
+        <v>-0.1822916666666667</v>
       </c>
       <c r="J3">
-        <v>-0.8231511254019293</v>
+        <v>-0.1822916666666667</v>
       </c>
       <c r="K3">
-        <v>-22.2</v>
+        <v>-20.7</v>
       </c>
       <c r="L3">
-        <v>-0.7138263665594855</v>
+        <v>-0.359375</v>
       </c>
       <c r="M3">
-        <v>0.092</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.003216783216783217</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.004144144144144144</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.092</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>4.89</v>
+        <v>4.5</v>
       </c>
       <c r="V3">
-        <v>0.170979020979021</v>
+        <v>0.2486187845303867</v>
       </c>
       <c r="W3">
-        <v>-1.298245614035088</v>
+        <v>6.234939759036145</v>
       </c>
       <c r="X3">
-        <v>0.2816363319000345</v>
+        <v>0.708694281668633</v>
       </c>
       <c r="Y3">
-        <v>-1.579881945935122</v>
+        <v>5.526245477367512</v>
       </c>
       <c r="Z3">
-        <v>0.1936367598530602</v>
+        <v>0.4146868250539957</v>
       </c>
       <c r="AA3">
-        <v>-0.1593923167922296</v>
+        <v>-0.0755939524838013</v>
       </c>
       <c r="AB3">
-        <v>0.06959560608294224</v>
+        <v>0.1196589642480355</v>
       </c>
       <c r="AC3">
-        <v>-0.2289879228751719</v>
+        <v>-0.1952529167318368</v>
       </c>
       <c r="AD3">
-        <v>149.7</v>
+        <v>164.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>149.7</v>
+        <v>164.4</v>
       </c>
       <c r="AG3">
-        <v>144.81</v>
+        <v>159.9</v>
       </c>
       <c r="AH3">
-        <v>0.8395961862030287</v>
+        <v>0.9008219178082192</v>
       </c>
       <c r="AI3">
-        <v>1.022680694083891</v>
+        <v>1.0844327176781</v>
       </c>
       <c r="AJ3">
-        <v>0.8350729485035465</v>
+        <v>0.898314606741573</v>
       </c>
       <c r="AK3">
-        <v>1.023464555798996</v>
+        <v>1.087015635622026</v>
       </c>
       <c r="AL3">
-        <v>16</v>
+        <v>19.1</v>
       </c>
       <c r="AM3">
-        <v>15.813</v>
+        <v>18.825</v>
       </c>
       <c r="AN3">
-        <v>-5.96414342629482</v>
+        <v>-18.26666666666667</v>
       </c>
       <c r="AO3">
-        <v>-1.6</v>
+        <v>-0.5497382198952879</v>
       </c>
       <c r="AP3">
-        <v>-5.769322709163347</v>
+        <v>-17.76666666666667</v>
       </c>
       <c r="AQ3">
-        <v>-1.618921140833491</v>
+        <v>-0.5577689243027888</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_recreation.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bmv_sport_s" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0584</v>
+        <v>-0.0333</v>
+      </c>
+      <c r="E2">
+        <v>-0.00391</v>
       </c>
       <c r="G2">
-        <v>-0.2447916666666667</v>
+        <v>-0.02258414766558089</v>
       </c>
       <c r="H2">
-        <v>-0.2447916666666667</v>
+        <v>-0.02258414766558089</v>
       </c>
       <c r="I2">
-        <v>-0.1822916666666667</v>
+        <v>0.04505971769815419</v>
       </c>
       <c r="J2">
-        <v>-0.1822916666666667</v>
+        <v>0.02321721047498114</v>
       </c>
       <c r="K2">
-        <v>-20.7</v>
+        <v>3.04</v>
       </c>
       <c r="L2">
-        <v>-0.359375</v>
+        <v>0.03300760043431054</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="V2">
-        <v>0.2486187845303867</v>
+        <v>0.07656529516994634</v>
       </c>
       <c r="W2">
-        <v>6.234939759036145</v>
+        <v>-0.2375</v>
       </c>
       <c r="X2">
-        <v>0.708694281668633</v>
+        <v>0.2332670607206451</v>
       </c>
       <c r="Y2">
-        <v>5.526245477367512</v>
+        <v>-0.4707670607206451</v>
       </c>
       <c r="Z2">
-        <v>0.4146868250539957</v>
+        <v>0.6375908618899273</v>
       </c>
       <c r="AA2">
-        <v>-0.0755939524838013</v>
+        <v>0.01480308123742308</v>
       </c>
       <c r="AB2">
-        <v>0.1196589642480355</v>
+        <v>0.0987552964713885</v>
       </c>
       <c r="AC2">
-        <v>-0.1952529167318368</v>
+        <v>-0.08395221523396543</v>
       </c>
       <c r="AD2">
-        <v>164.4</v>
+        <v>154.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>164.4</v>
+        <v>154.6</v>
       </c>
       <c r="AG2">
-        <v>159.9</v>
+        <v>150.32</v>
       </c>
       <c r="AH2">
-        <v>0.9008219178082192</v>
+        <v>0.7344418052256532</v>
       </c>
       <c r="AI2">
-        <v>1.0844327176781</v>
+        <v>0.9658877920779707</v>
       </c>
       <c r="AJ2">
-        <v>0.898314606741573</v>
+        <v>0.7289302686451362</v>
       </c>
       <c r="AK2">
-        <v>1.087015635622026</v>
+        <v>0.9649505713185261</v>
       </c>
       <c r="AL2">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="AM2">
-        <v>18.825</v>
+        <v>18.616</v>
       </c>
       <c r="AN2">
-        <v>-18.26666666666667</v>
+        <v>67.51091703056768</v>
       </c>
       <c r="AO2">
-        <v>-0.5497382198952879</v>
+        <v>0.2139175257731959</v>
       </c>
       <c r="AP2">
-        <v>-17.76666666666667</v>
+        <v>65.6419213973799</v>
       </c>
       <c r="AQ2">
-        <v>-0.5577689243027888</v>
+        <v>0.2229265148259562</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0584</v>
+        <v>-0.0333</v>
+      </c>
+      <c r="E3">
+        <v>-0.00391</v>
       </c>
       <c r="G3">
-        <v>-0.2447916666666667</v>
+        <v>-0.02258414766558089</v>
       </c>
       <c r="H3">
-        <v>-0.2447916666666667</v>
+        <v>-0.02258414766558089</v>
       </c>
       <c r="I3">
-        <v>-0.1822916666666667</v>
+        <v>0.04505971769815419</v>
       </c>
       <c r="J3">
-        <v>-0.1822916666666667</v>
+        <v>0.02321721047498114</v>
       </c>
       <c r="K3">
-        <v>-20.7</v>
+        <v>3.04</v>
       </c>
       <c r="L3">
-        <v>-0.359375</v>
+        <v>0.03300760043431054</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8840 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="V3">
-        <v>0.2486187845303867</v>
+        <v>0.07656529516994634</v>
       </c>
       <c r="W3">
-        <v>6.234939759036145</v>
+        <v>-0.2375</v>
       </c>
       <c r="X3">
-        <v>0.708694281668633</v>
+        <v>0.2332670607206451</v>
       </c>
       <c r="Y3">
-        <v>5.526245477367512</v>
+        <v>-0.4707670607206451</v>
       </c>
       <c r="Z3">
-        <v>0.4146868250539957</v>
+        <v>0.6375908618899273</v>
       </c>
       <c r="AA3">
-        <v>-0.0755939524838013</v>
+        <v>0.01480308123742308</v>
       </c>
       <c r="AB3">
-        <v>0.1196589642480355</v>
+        <v>0.0987552964713885</v>
       </c>
       <c r="AC3">
-        <v>-0.1952529167318368</v>
+        <v>-0.08395221523396543</v>
       </c>
       <c r="AD3">
-        <v>164.4</v>
+        <v>154.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>164.4</v>
+        <v>154.6</v>
       </c>
       <c r="AG3">
-        <v>159.9</v>
+        <v>150.32</v>
       </c>
       <c r="AH3">
-        <v>0.9008219178082192</v>
+        <v>0.7344418052256532</v>
       </c>
       <c r="AI3">
-        <v>1.0844327176781</v>
+        <v>0.9658877920779707</v>
       </c>
       <c r="AJ3">
-        <v>0.898314606741573</v>
+        <v>0.7289302686451362</v>
       </c>
       <c r="AK3">
-        <v>1.087015635622026</v>
+        <v>0.9649505713185261</v>
       </c>
       <c r="AL3">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="AM3">
-        <v>18.825</v>
+        <v>18.616</v>
       </c>
       <c r="AN3">
-        <v>-18.26666666666667</v>
+        <v>67.51091703056768</v>
       </c>
       <c r="AO3">
-        <v>-0.5497382198952879</v>
+        <v>0.2139175257731959</v>
       </c>
       <c r="AP3">
-        <v>-17.76666666666667</v>
+        <v>65.6419213973799</v>
       </c>
       <c r="AQ3">
-        <v>-0.5577689243027888</v>
+        <v>0.2229265148259562</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Grupo Sports World, S.A.B. de C.V. (BMV:SPORT S)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BMV:SPORT S</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-1.22731958762887</v>
+      </c>
+      <c r="F2">
+        <v>-42.811046523194</v>
+      </c>
+      <c r="G2">
+        <v>67.5109170305677</v>
+      </c>
+      <c r="H2">
+        <v>0.9192139737991269</v>
+      </c>
+      <c r="I2">
+        <v>0.7344418052256531</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>55.9</v>
+      </c>
+      <c r="L2">
+        <v>117.281807992077</v>
+      </c>
+      <c r="M2">
+        <v>206.22</v>
+      </c>
+      <c r="N2">
+        <v>115.106807992077</v>
+      </c>
+      <c r="O2">
+        <v>154.6</v>
+      </c>
+      <c r="P2">
+        <v>2.105</v>
+      </c>
+      <c r="Q2">
+        <v>0.0987552964713885</v>
+      </c>
+      <c r="R2">
+        <v>0.146213118772095</v>
+      </c>
+      <c r="S2">
+        <v>0.0501187659310687</v>
+      </c>
+      <c r="T2">
+        <v>3.30578337292162</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.233267060720645</v>
+      </c>
+      <c r="X2">
+        <v>0.11429826772008</v>
+      </c>
+      <c r="Y2">
+        <v>2.63339425186063</v>
+      </c>
+      <c r="Z2">
+        <v>1.02236699368381</v>
+      </c>
+      <c r="AA2">
+        <v>154.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.07159823704438384</v>
+      </c>
+      <c r="AC2">
+        <v>-1.227319587628866</v>
+      </c>
+      <c r="AD2">
+        <v>154.6</v>
+      </c>
+      <c r="AE2">
+        <v>19.4</v>
+      </c>
+      <c r="AF2">
+        <v>26.1</v>
+      </c>
+      <c r="AG2">
+        <v>2.29</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>55.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2.499999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>19.4</v>
+      </c>
+      <c r="AS2">
+        <v>154.6</v>
+      </c>
+      <c r="AT2">
+        <v>4.28</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-154.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.28</v>
+      </c>
+      <c r="H2">
+        <v>55.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>4.58</v>
+      </c>
+      <c r="K2">
+        <v>26.1</v>
+      </c>
+      <c r="L2">
+        <v>-21.52</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-21.52</v>
+      </c>
+      <c r="O2">
+        <v>-6.456</v>
+      </c>
+      <c r="P2">
+        <v>-15.064</v>
+      </c>
+      <c r="Q2">
+        <v>11.036</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1462131187720953</v>
+      </c>
+      <c r="C3">
+        <v>117.2818079920771</v>
+      </c>
+      <c r="D3">
+        <v>115.1068079920771</v>
+      </c>
+      <c r="E3">
+        <v>-152.495</v>
+      </c>
+      <c r="F3">
+        <v>2.105</v>
+      </c>
+      <c r="G3">
+        <v>4.28</v>
+      </c>
+      <c r="H3">
+        <v>55.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>4.58</v>
+      </c>
+      <c r="K3">
+        <v>26.1</v>
+      </c>
+      <c r="L3">
+        <v>-21.52</v>
+      </c>
+      <c r="M3">
+        <v>0.5026740000000001</v>
+      </c>
+      <c r="N3">
+        <v>-22.022674</v>
+      </c>
+      <c r="O3">
+        <v>-6.606802200000001</v>
+      </c>
+      <c r="P3">
+        <v>-15.4158718</v>
+      </c>
+      <c r="Q3">
+        <v>10.6841282</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1142982677200799</v>
+      </c>
+      <c r="T3">
+        <v>1.022366993683814</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-12.84331395695819</v>
+      </c>
+      <c r="W3">
+        <v>3.305783372921615</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-42.81104652319396</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1482131187720952</v>
+      </c>
+      <c r="C4">
+        <v>113.072731090077</v>
+      </c>
+      <c r="D4">
+        <v>113.002731090077</v>
+      </c>
+      <c r="E4">
+        <v>-150.39</v>
+      </c>
+      <c r="F4">
+        <v>4.21</v>
+      </c>
+      <c r="G4">
+        <v>4.28</v>
+      </c>
+      <c r="H4">
+        <v>55.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>4.58</v>
+      </c>
+      <c r="K4">
+        <v>26.1</v>
+      </c>
+      <c r="L4">
+        <v>-21.52</v>
+      </c>
+      <c r="M4">
+        <v>1.005348</v>
+      </c>
+      <c r="N4">
+        <v>-22.525348</v>
+      </c>
+      <c r="O4">
+        <v>-6.757604400000001</v>
+      </c>
+      <c r="P4">
+        <v>-15.7677436</v>
+      </c>
+      <c r="Q4">
+        <v>10.3322564</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1150686582070195</v>
+      </c>
+      <c r="T4">
+        <v>1.032799309945894</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-6.421656978479094</v>
+      </c>
+      <c r="W4">
+        <v>1.772291686460808</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-21.40552326159698</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1502131187720953</v>
+      </c>
+      <c r="C5">
+        <v>108.9391956297021</v>
+      </c>
+      <c r="D5">
+        <v>110.9741956297021</v>
+      </c>
+      <c r="E5">
+        <v>-148.285</v>
+      </c>
+      <c r="F5">
+        <v>6.315</v>
+      </c>
+      <c r="G5">
+        <v>4.28</v>
+      </c>
+      <c r="H5">
+        <v>55.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>4.58</v>
+      </c>
+      <c r="K5">
+        <v>26.1</v>
+      </c>
+      <c r="L5">
+        <v>-21.52</v>
+      </c>
+      <c r="M5">
+        <v>1.508022</v>
+      </c>
+      <c r="N5">
+        <v>-23.028022</v>
+      </c>
+      <c r="O5">
+        <v>-6.908406600000001</v>
+      </c>
+      <c r="P5">
+        <v>-16.1196154</v>
+      </c>
+      <c r="Q5">
+        <v>9.980384600000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.115854933033896</v>
+      </c>
+      <c r="T5">
+        <v>1.043446725512346</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-4.281104652319396</v>
+      </c>
+      <c r="W5">
+        <v>1.261127790973872</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-14.27034884106466</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1522131187720952</v>
+      </c>
+      <c r="C6">
+        <v>104.8772051716105</v>
+      </c>
+      <c r="D6">
+        <v>109.0172051716105</v>
+      </c>
+      <c r="E6">
+        <v>-146.18</v>
+      </c>
+      <c r="F6">
+        <v>8.42</v>
+      </c>
+      <c r="G6">
+        <v>4.28</v>
+      </c>
+      <c r="H6">
+        <v>55.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>4.58</v>
+      </c>
+      <c r="K6">
+        <v>26.1</v>
+      </c>
+      <c r="L6">
+        <v>-21.52</v>
+      </c>
+      <c r="M6">
+        <v>2.010696</v>
+      </c>
+      <c r="N6">
+        <v>-23.530696</v>
+      </c>
+      <c r="O6">
+        <v>-7.0592088</v>
+      </c>
+      <c r="P6">
+        <v>-16.4714872</v>
+      </c>
+      <c r="Q6">
+        <v>9.628512799999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1166575885863324</v>
+      </c>
+      <c r="T6">
+        <v>1.054315962236433</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-3.210828489239547</v>
+      </c>
+      <c r="W6">
+        <v>1.005545843230404</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-10.70276163079849</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1542131187720952</v>
+      </c>
+      <c r="C7">
+        <v>100.8830402944896</v>
+      </c>
+      <c r="D7">
+        <v>107.1280402944897</v>
+      </c>
+      <c r="E7">
+        <v>-144.075</v>
+      </c>
+      <c r="F7">
+        <v>10.525</v>
+      </c>
+      <c r="G7">
+        <v>4.28</v>
+      </c>
+      <c r="H7">
+        <v>55.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>4.58</v>
+      </c>
+      <c r="K7">
+        <v>26.1</v>
+      </c>
+      <c r="L7">
+        <v>-21.52</v>
+      </c>
+      <c r="M7">
+        <v>2.51337</v>
+      </c>
+      <c r="N7">
+        <v>-24.03337000000001</v>
+      </c>
+      <c r="O7">
+        <v>-7.210011000000002</v>
+      </c>
+      <c r="P7">
+        <v>-16.823359</v>
+      </c>
+      <c r="Q7">
+        <v>9.276640999999998</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.117477142150399</v>
+      </c>
+      <c r="T7">
+        <v>1.065414024996817</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-2.568662791391638</v>
+      </c>
+      <c r="W7">
+        <v>0.8521966745843231</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-8.562209304638793</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1562131187720952</v>
+      </c>
+      <c r="C8">
+        <v>96.95323500160872</v>
+      </c>
+      <c r="D8">
+        <v>105.3032350016087</v>
+      </c>
+      <c r="E8">
+        <v>-141.97</v>
+      </c>
+      <c r="F8">
+        <v>12.63</v>
+      </c>
+      <c r="G8">
+        <v>4.28</v>
+      </c>
+      <c r="H8">
+        <v>55.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>4.58</v>
+      </c>
+      <c r="K8">
+        <v>26.1</v>
+      </c>
+      <c r="L8">
+        <v>-21.52</v>
+      </c>
+      <c r="M8">
+        <v>3.016044</v>
+      </c>
+      <c r="N8">
+        <v>-24.536044</v>
+      </c>
+      <c r="O8">
+        <v>-7.360813200000001</v>
+      </c>
+      <c r="P8">
+        <v>-17.1752308</v>
+      </c>
+      <c r="Q8">
+        <v>8.9247692</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1183141330243394</v>
+      </c>
+      <c r="T8">
+        <v>1.076748216752102</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-2.140552326159698</v>
+      </c>
+      <c r="W8">
+        <v>0.7499638954869359</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-7.135174420532328</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1582131187720952</v>
+      </c>
+      <c r="C9">
+        <v>93.08455549831083</v>
+      </c>
+      <c r="D9">
+        <v>103.5395554983108</v>
+      </c>
+      <c r="E9">
+        <v>-139.865</v>
+      </c>
+      <c r="F9">
+        <v>14.735</v>
+      </c>
+      <c r="G9">
+        <v>4.28</v>
+      </c>
+      <c r="H9">
+        <v>55.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>4.58</v>
+      </c>
+      <c r="K9">
+        <v>26.1</v>
+      </c>
+      <c r="L9">
+        <v>-21.52</v>
+      </c>
+      <c r="M9">
+        <v>3.518718000000001</v>
+      </c>
+      <c r="N9">
+        <v>-25.038718</v>
+      </c>
+      <c r="O9">
+        <v>-7.5116154</v>
+      </c>
+      <c r="P9">
+        <v>-17.5271026</v>
+      </c>
+      <c r="Q9">
+        <v>8.572897399999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1191691237020205</v>
+      </c>
+      <c r="T9">
+        <v>1.088326154566641</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-1.834759136708312</v>
+      </c>
+      <c r="W9">
+        <v>0.676940481845945</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-6.115863789027708</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1602131187720952</v>
+      </c>
+      <c r="C10">
+        <v>89.27398106705574</v>
+      </c>
+      <c r="D10">
+        <v>101.8339810670557</v>
+      </c>
+      <c r="E10">
+        <v>-137.76</v>
+      </c>
+      <c r="F10">
+        <v>16.84</v>
+      </c>
+      <c r="G10">
+        <v>4.28</v>
+      </c>
+      <c r="H10">
+        <v>55.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>4.58</v>
+      </c>
+      <c r="K10">
+        <v>26.1</v>
+      </c>
+      <c r="L10">
+        <v>-21.52</v>
+      </c>
+      <c r="M10">
+        <v>4.021392000000001</v>
+      </c>
+      <c r="N10">
+        <v>-25.541392</v>
+      </c>
+      <c r="O10">
+        <v>-7.6624176</v>
+      </c>
+      <c r="P10">
+        <v>-17.8789744</v>
+      </c>
+      <c r="Q10">
+        <v>8.221025600000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1200427011335642</v>
+      </c>
+      <c r="T10">
+        <v>1.100155786681495</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-1.605414244619773</v>
+      </c>
+      <c r="W10">
+        <v>0.6221729216152019</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-5.351380815399245</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1622131187720952</v>
+      </c>
+      <c r="C11">
+        <v>85.51868680206579</v>
+      </c>
+      <c r="D11">
+        <v>100.1836868020658</v>
+      </c>
+      <c r="E11">
+        <v>-135.655</v>
+      </c>
+      <c r="F11">
+        <v>18.945</v>
+      </c>
+      <c r="G11">
+        <v>4.28</v>
+      </c>
+      <c r="H11">
+        <v>55.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4.58</v>
+      </c>
+      <c r="K11">
+        <v>26.1</v>
+      </c>
+      <c r="L11">
+        <v>-21.52</v>
+      </c>
+      <c r="M11">
+        <v>4.524066</v>
+      </c>
+      <c r="N11">
+        <v>-26.044066</v>
+      </c>
+      <c r="O11">
+        <v>-7.813219800000001</v>
+      </c>
+      <c r="P11">
+        <v>-18.2308462</v>
+      </c>
+      <c r="Q11">
+        <v>7.869153799999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1209354780690979</v>
+      </c>
+      <c r="T11">
+        <v>1.112245410710963</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-1.427034884106465</v>
+      </c>
+      <c r="W11">
+        <v>0.579575930324624</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-4.756782947021551</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1642131187720953</v>
+      </c>
+      <c r="C12">
+        <v>81.81602799598629</v>
+      </c>
+      <c r="D12">
+        <v>98.58602799598629</v>
+      </c>
+      <c r="E12">
+        <v>-133.55</v>
+      </c>
+      <c r="F12">
+        <v>21.05</v>
+      </c>
+      <c r="G12">
+        <v>4.28</v>
+      </c>
+      <c r="H12">
+        <v>55.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>4.58</v>
+      </c>
+      <c r="K12">
+        <v>26.1</v>
+      </c>
+      <c r="L12">
+        <v>-21.52</v>
+      </c>
+      <c r="M12">
+        <v>5.02674</v>
+      </c>
+      <c r="N12">
+        <v>-26.54674</v>
+      </c>
+      <c r="O12">
+        <v>-7.964022000000001</v>
+      </c>
+      <c r="P12">
+        <v>-18.582718</v>
+      </c>
+      <c r="Q12">
+        <v>7.517281999999998</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1218480944920879</v>
+      </c>
+      <c r="T12">
+        <v>1.124603693052195</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-1.284331395695819</v>
+      </c>
+      <c r="W12">
+        <v>0.5454983372921617</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-4.281104652319397</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1662131187720952</v>
+      </c>
+      <c r="C13">
+        <v>78.16352599703866</v>
+      </c>
+      <c r="D13">
+        <v>97.03852599703866</v>
+      </c>
+      <c r="E13">
+        <v>-131.445</v>
+      </c>
+      <c r="F13">
+        <v>23.155</v>
+      </c>
+      <c r="G13">
+        <v>4.28</v>
+      </c>
+      <c r="H13">
+        <v>55.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>4.58</v>
+      </c>
+      <c r="K13">
+        <v>26.1</v>
+      </c>
+      <c r="L13">
+        <v>-21.52</v>
+      </c>
+      <c r="M13">
+        <v>5.529414000000001</v>
+      </c>
+      <c r="N13">
+        <v>-27.04941400000001</v>
+      </c>
+      <c r="O13">
+        <v>-8.114824200000001</v>
+      </c>
+      <c r="P13">
+        <v>-18.9345898</v>
+      </c>
+      <c r="Q13">
+        <v>7.165410199999997</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1227812191493023</v>
+      </c>
+      <c r="T13">
+        <v>1.137239689603343</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-1.167573996087108</v>
+      </c>
+      <c r="W13">
+        <v>0.5176166702656014</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-3.89191332029036</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1682131187720952</v>
+      </c>
+      <c r="C14">
+        <v>74.55885537758732</v>
+      </c>
+      <c r="D14">
+        <v>95.53885537758732</v>
+      </c>
+      <c r="E14">
+        <v>-129.34</v>
+      </c>
+      <c r="F14">
+        <v>25.26</v>
+      </c>
+      <c r="G14">
+        <v>4.28</v>
+      </c>
+      <c r="H14">
+        <v>55.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>4.58</v>
+      </c>
+      <c r="K14">
+        <v>26.1</v>
+      </c>
+      <c r="L14">
+        <v>-21.52</v>
+      </c>
+      <c r="M14">
+        <v>6.032088</v>
+      </c>
+      <c r="N14">
+        <v>-27.552088</v>
+      </c>
+      <c r="O14">
+        <v>-8.2656264</v>
+      </c>
+      <c r="P14">
+        <v>-19.2864616</v>
+      </c>
+      <c r="Q14">
+        <v>6.813538399999999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1237355511850898</v>
+      </c>
+      <c r="T14">
+        <v>1.150162867894291</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-1.070276163079849</v>
+      </c>
+      <c r="W14">
+        <v>0.4943819477434679</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-3.567587210266164</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1702131187720952</v>
+      </c>
+      <c r="C15">
+        <v>70.99983227441029</v>
+      </c>
+      <c r="D15">
+        <v>94.08483227441029</v>
+      </c>
+      <c r="E15">
+        <v>-127.235</v>
+      </c>
+      <c r="F15">
+        <v>27.365</v>
+      </c>
+      <c r="G15">
+        <v>4.28</v>
+      </c>
+      <c r="H15">
+        <v>55.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>4.58</v>
+      </c>
+      <c r="K15">
+        <v>26.1</v>
+      </c>
+      <c r="L15">
+        <v>-21.52</v>
+      </c>
+      <c r="M15">
+        <v>6.534762000000001</v>
+      </c>
+      <c r="N15">
+        <v>-28.054762</v>
+      </c>
+      <c r="O15">
+        <v>-8.416428600000001</v>
+      </c>
+      <c r="P15">
+        <v>-19.6383334</v>
+      </c>
+      <c r="Q15">
+        <v>6.461666600000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1247118218883668</v>
+      </c>
+      <c r="T15">
+        <v>1.16338313074365</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.9879472274583221</v>
+      </c>
+      <c r="W15">
+        <v>0.4747217979170473</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-3.293157424861074</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1722131187720952</v>
+      </c>
+      <c r="C16">
+        <v>67.48440377771752</v>
+      </c>
+      <c r="D16">
+        <v>92.67440377771752</v>
+      </c>
+      <c r="E16">
+        <v>-125.13</v>
+      </c>
+      <c r="F16">
+        <v>29.47</v>
+      </c>
+      <c r="G16">
+        <v>4.28</v>
+      </c>
+      <c r="H16">
+        <v>55.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>4.58</v>
+      </c>
+      <c r="K16">
+        <v>26.1</v>
+      </c>
+      <c r="L16">
+        <v>-21.52</v>
+      </c>
+      <c r="M16">
+        <v>7.037436000000001</v>
+      </c>
+      <c r="N16">
+        <v>-28.557436</v>
+      </c>
+      <c r="O16">
+        <v>-8.567230800000001</v>
+      </c>
+      <c r="P16">
+        <v>-19.9902052</v>
+      </c>
+      <c r="Q16">
+        <v>6.1097948</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1257107965614873</v>
+      </c>
+      <c r="T16">
+        <v>1.176910841566251</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.9173795683541561</v>
+      </c>
+      <c r="W16">
+        <v>0.4578702409229725</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-3.057931894513854</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1742131187720952</v>
+      </c>
+      <c r="C17">
+        <v>64.0106382604903</v>
+      </c>
+      <c r="D17">
+        <v>91.3056382604903</v>
+      </c>
+      <c r="E17">
+        <v>-123.025</v>
+      </c>
+      <c r="F17">
+        <v>31.575</v>
+      </c>
+      <c r="G17">
+        <v>4.28</v>
+      </c>
+      <c r="H17">
+        <v>55.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>4.58</v>
+      </c>
+      <c r="K17">
+        <v>26.1</v>
+      </c>
+      <c r="L17">
+        <v>-21.52</v>
+      </c>
+      <c r="M17">
+        <v>7.54011</v>
+      </c>
+      <c r="N17">
+        <v>-29.06011</v>
+      </c>
+      <c r="O17">
+        <v>-8.718033</v>
+      </c>
+      <c r="P17">
+        <v>-20.342077</v>
+      </c>
+      <c r="Q17">
+        <v>5.757922999999998</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1267332765210342</v>
+      </c>
+      <c r="T17">
+        <v>1.19075685146703</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.8562209304638793</v>
+      </c>
+      <c r="W17">
+        <v>0.4432655581947744</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-2.854069768212931</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1762131187720953</v>
+      </c>
+      <c r="C18">
+        <v>60.57671655233923</v>
+      </c>
+      <c r="D18">
+        <v>89.97671655233923</v>
+      </c>
+      <c r="E18">
+        <v>-120.92</v>
+      </c>
+      <c r="F18">
+        <v>33.68</v>
+      </c>
+      <c r="G18">
+        <v>4.28</v>
+      </c>
+      <c r="H18">
+        <v>55.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>4.58</v>
+      </c>
+      <c r="K18">
+        <v>26.1</v>
+      </c>
+      <c r="L18">
+        <v>-21.52</v>
+      </c>
+      <c r="M18">
+        <v>8.042784000000001</v>
+      </c>
+      <c r="N18">
+        <v>-29.562784</v>
+      </c>
+      <c r="O18">
+        <v>-8.868835200000001</v>
+      </c>
+      <c r="P18">
+        <v>-20.6939488</v>
+      </c>
+      <c r="Q18">
+        <v>5.4060512</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1277801012415227</v>
+      </c>
+      <c r="T18">
+        <v>1.204932528270209</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.8027071223098867</v>
+      </c>
+      <c r="W18">
+        <v>0.4304864608076009</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-2.675690407699622</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1782131187720952</v>
+      </c>
+      <c r="C19">
+        <v>57.18092387307311</v>
+      </c>
+      <c r="D19">
+        <v>88.68592387307311</v>
+      </c>
+      <c r="E19">
+        <v>-118.815</v>
+      </c>
+      <c r="F19">
+        <v>35.785</v>
+      </c>
+      <c r="G19">
+        <v>4.28</v>
+      </c>
+      <c r="H19">
+        <v>55.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>4.58</v>
+      </c>
+      <c r="K19">
+        <v>26.1</v>
+      </c>
+      <c r="L19">
+        <v>-21.52</v>
+      </c>
+      <c r="M19">
+        <v>8.545458000000002</v>
+      </c>
+      <c r="N19">
+        <v>-30.06545800000001</v>
+      </c>
+      <c r="O19">
+        <v>-9.019637400000002</v>
+      </c>
+      <c r="P19">
+        <v>-21.04582060000001</v>
+      </c>
+      <c r="Q19">
+        <v>5.054179399999995</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1288521506540712</v>
+      </c>
+      <c r="T19">
+        <v>1.219449787646959</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.755489056291658</v>
+      </c>
+      <c r="W19">
+        <v>0.4192107866424479</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-2.518296854305527</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1802131187720952</v>
+      </c>
+      <c r="C20">
+        <v>53.82164245076743</v>
+      </c>
+      <c r="D20">
+        <v>87.43164245076743</v>
+      </c>
+      <c r="E20">
+        <v>-116.71</v>
+      </c>
+      <c r="F20">
+        <v>37.89</v>
+      </c>
+      <c r="G20">
+        <v>4.28</v>
+      </c>
+      <c r="H20">
+        <v>55.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>4.58</v>
+      </c>
+      <c r="K20">
+        <v>26.1</v>
+      </c>
+      <c r="L20">
+        <v>-21.52</v>
+      </c>
+      <c r="M20">
+        <v>9.048132000000001</v>
+      </c>
+      <c r="N20">
+        <v>-30.56813200000001</v>
+      </c>
+      <c r="O20">
+        <v>-9.170439600000002</v>
+      </c>
+      <c r="P20">
+        <v>-21.3976924</v>
+      </c>
+      <c r="Q20">
+        <v>4.702307599999997</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1299503476132672</v>
+      </c>
+      <c r="T20">
+        <v>1.234321126520702</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.7135174420532326</v>
+      </c>
+      <c r="W20">
+        <v>0.409187965162312</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-2.378391473510776</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1822131187720952</v>
+      </c>
+      <c r="C21">
+        <v>50.49734475751095</v>
+      </c>
+      <c r="D21">
+        <v>86.21234475751095</v>
+      </c>
+      <c r="E21">
+        <v>-114.605</v>
+      </c>
+      <c r="F21">
+        <v>39.995</v>
+      </c>
+      <c r="G21">
+        <v>4.28</v>
+      </c>
+      <c r="H21">
+        <v>55.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>4.58</v>
+      </c>
+      <c r="K21">
+        <v>26.1</v>
+      </c>
+      <c r="L21">
+        <v>-21.52</v>
+      </c>
+      <c r="M21">
+        <v>9.550806</v>
+      </c>
+      <c r="N21">
+        <v>-31.070806</v>
+      </c>
+      <c r="O21">
+        <v>-9.321241800000001</v>
+      </c>
+      <c r="P21">
+        <v>-21.7495642</v>
+      </c>
+      <c r="Q21">
+        <v>4.3504358</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1310756605467643</v>
+      </c>
+      <c r="T21">
+        <v>1.249559658946884</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.6759638924714837</v>
+      </c>
+      <c r="W21">
+        <v>0.4002201775221903</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-2.253212974904946</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1842131187720953</v>
+      </c>
+      <c r="C22">
+        <v>47.20658730336221</v>
+      </c>
+      <c r="D22">
+        <v>85.02658730336221</v>
+      </c>
+      <c r="E22">
+        <v>-112.5</v>
+      </c>
+      <c r="F22">
+        <v>42.1</v>
+      </c>
+      <c r="G22">
+        <v>4.28</v>
+      </c>
+      <c r="H22">
+        <v>55.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>4.58</v>
+      </c>
+      <c r="K22">
+        <v>26.1</v>
+      </c>
+      <c r="L22">
+        <v>-21.52</v>
+      </c>
+      <c r="M22">
+        <v>10.05348</v>
+      </c>
+      <c r="N22">
+        <v>-31.57348</v>
+      </c>
+      <c r="O22">
+        <v>-9.472044</v>
+      </c>
+      <c r="P22">
+        <v>-22.101436</v>
+      </c>
+      <c r="Q22">
+        <v>3.998563999999998</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1322291063035989</v>
+      </c>
+      <c r="T22">
+        <v>1.26517915468372</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.6421656978479094</v>
+      </c>
+      <c r="W22">
+        <v>0.3921491686460808</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-2.140552326159698</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1862131187720952</v>
+      </c>
+      <c r="C23">
+        <v>43.94800493550235</v>
+      </c>
+      <c r="D23">
+        <v>83.87300493550235</v>
+      </c>
+      <c r="E23">
+        <v>-110.395</v>
+      </c>
+      <c r="F23">
+        <v>44.205</v>
+      </c>
+      <c r="G23">
+        <v>4.28</v>
+      </c>
+      <c r="H23">
+        <v>55.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>4.58</v>
+      </c>
+      <c r="K23">
+        <v>26.1</v>
+      </c>
+      <c r="L23">
+        <v>-21.52</v>
+      </c>
+      <c r="M23">
+        <v>10.556154</v>
+      </c>
+      <c r="N23">
+        <v>-32.076154</v>
+      </c>
+      <c r="O23">
+        <v>-9.6228462</v>
+      </c>
+      <c r="P23">
+        <v>-22.4533078</v>
+      </c>
+      <c r="Q23">
+        <v>3.646692199999997</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1334117532188343</v>
+      </c>
+      <c r="T23">
+        <v>1.281194080692375</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.611586378902771</v>
+      </c>
+      <c r="W23">
+        <v>0.3848468272819817</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-2.038621263009237</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1882131187720952</v>
+      </c>
+      <c r="C24">
+        <v>40.72030559524647</v>
+      </c>
+      <c r="D24">
+        <v>82.75030559524647</v>
+      </c>
+      <c r="E24">
+        <v>-108.29</v>
+      </c>
+      <c r="F24">
+        <v>46.31</v>
+      </c>
+      <c r="G24">
+        <v>4.28</v>
+      </c>
+      <c r="H24">
+        <v>55.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>4.58</v>
+      </c>
+      <c r="K24">
+        <v>26.1</v>
+      </c>
+      <c r="L24">
+        <v>-21.52</v>
+      </c>
+      <c r="M24">
+        <v>11.058828</v>
+      </c>
+      <c r="N24">
+        <v>-32.578828</v>
+      </c>
+      <c r="O24">
+        <v>-9.773648400000001</v>
+      </c>
+      <c r="P24">
+        <v>-22.8051796</v>
+      </c>
+      <c r="Q24">
+        <v>3.294820399999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1346247244139475</v>
+      </c>
+      <c r="T24">
+        <v>1.297619645829456</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.5837869980435539</v>
+      </c>
+      <c r="W24">
+        <v>0.3782083351328007</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-1.94595666014518</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1902131187720952</v>
+      </c>
+      <c r="C25">
+        <v>37.52226549058022</v>
+      </c>
+      <c r="D25">
+        <v>81.65726549058022</v>
+      </c>
+      <c r="E25">
+        <v>-106.185</v>
+      </c>
+      <c r="F25">
+        <v>48.415</v>
+      </c>
+      <c r="G25">
+        <v>4.28</v>
+      </c>
+      <c r="H25">
+        <v>55.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>4.58</v>
+      </c>
+      <c r="K25">
+        <v>26.1</v>
+      </c>
+      <c r="L25">
+        <v>-21.52</v>
+      </c>
+      <c r="M25">
+        <v>11.561502</v>
+      </c>
+      <c r="N25">
+        <v>-33.081502</v>
+      </c>
+      <c r="O25">
+        <v>-9.9244506</v>
+      </c>
+      <c r="P25">
+        <v>-23.1570514</v>
+      </c>
+      <c r="Q25">
+        <v>2.942948600000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1358692013543884</v>
+      </c>
+      <c r="T25">
+        <v>1.314471849022046</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.558404954650356</v>
+      </c>
+      <c r="W25">
+        <v>0.372147103170505</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-1.86134984883452</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1922131187720952</v>
+      </c>
+      <c r="C26">
+        <v>34.35272464630098</v>
+      </c>
+      <c r="D26">
+        <v>80.59272464630098</v>
+      </c>
+      <c r="E26">
+        <v>-104.08</v>
+      </c>
+      <c r="F26">
+        <v>50.52</v>
+      </c>
+      <c r="G26">
+        <v>4.28</v>
+      </c>
+      <c r="H26">
+        <v>55.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>4.58</v>
+      </c>
+      <c r="K26">
+        <v>26.1</v>
+      </c>
+      <c r="L26">
+        <v>-21.52</v>
+      </c>
+      <c r="M26">
+        <v>12.064176</v>
+      </c>
+      <c r="N26">
+        <v>-33.584176</v>
+      </c>
+      <c r="O26">
+        <v>-10.0752528</v>
+      </c>
+      <c r="P26">
+        <v>-23.5089232</v>
+      </c>
+      <c r="Q26">
+        <v>2.591076800000003</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1371464276879988</v>
+      </c>
+      <c r="T26">
+        <v>1.331767531246021</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.5351380815399245</v>
+      </c>
+      <c r="W26">
+        <v>0.366590973871734</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-1.783793605133082</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1942131187720952</v>
+      </c>
+      <c r="C27">
+        <v>31.21058279774846</v>
+      </c>
+      <c r="D27">
+        <v>79.55558279774846</v>
+      </c>
+      <c r="E27">
+        <v>-101.975</v>
+      </c>
+      <c r="F27">
+        <v>52.625</v>
+      </c>
+      <c r="G27">
+        <v>4.28</v>
+      </c>
+      <c r="H27">
+        <v>55.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>4.58</v>
+      </c>
+      <c r="K27">
+        <v>26.1</v>
+      </c>
+      <c r="L27">
+        <v>-21.52</v>
+      </c>
+      <c r="M27">
+        <v>12.56685</v>
+      </c>
+      <c r="N27">
+        <v>-34.08685000000001</v>
+      </c>
+      <c r="O27">
+        <v>-10.226055</v>
+      </c>
+      <c r="P27">
+        <v>-23.860795</v>
+      </c>
+      <c r="Q27">
+        <v>2.239204999999998</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1384577133905054</v>
+      </c>
+      <c r="T27">
+        <v>1.349524431662634</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.5137325582783275</v>
+      </c>
+      <c r="W27">
+        <v>0.3614793349168647</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-1.712441860927759</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1962131187720952</v>
+      </c>
+      <c r="C28">
+        <v>28.09479559756687</v>
+      </c>
+      <c r="D28">
+        <v>78.54479559756687</v>
+      </c>
+      <c r="E28">
+        <v>-99.86999999999999</v>
+      </c>
+      <c r="F28">
+        <v>54.73</v>
+      </c>
+      <c r="G28">
+        <v>4.28</v>
+      </c>
+      <c r="H28">
+        <v>55.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>4.58</v>
+      </c>
+      <c r="K28">
+        <v>26.1</v>
+      </c>
+      <c r="L28">
+        <v>-21.52</v>
+      </c>
+      <c r="M28">
+        <v>13.069524</v>
+      </c>
+      <c r="N28">
+        <v>-34.589524</v>
+      </c>
+      <c r="O28">
+        <v>-10.3768572</v>
+      </c>
+      <c r="P28">
+        <v>-24.2126668</v>
+      </c>
+      <c r="Q28">
+        <v>1.8873332</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1398044392471339</v>
+      </c>
+      <c r="T28">
+        <v>1.367761248306724</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.493973613729161</v>
+      </c>
+      <c r="W28">
+        <v>0.3567608989585237</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-1.646578712430537</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1982131187720952</v>
+      </c>
+      <c r="C29">
+        <v>25.00437110800703</v>
+      </c>
+      <c r="D29">
+        <v>77.55937110800703</v>
+      </c>
+      <c r="E29">
+        <v>-97.76499999999999</v>
+      </c>
+      <c r="F29">
+        <v>56.835</v>
+      </c>
+      <c r="G29">
+        <v>4.28</v>
+      </c>
+      <c r="H29">
+        <v>55.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>4.58</v>
+      </c>
+      <c r="K29">
+        <v>26.1</v>
+      </c>
+      <c r="L29">
+        <v>-21.52</v>
+      </c>
+      <c r="M29">
+        <v>13.572198</v>
+      </c>
+      <c r="N29">
+        <v>-35.092198</v>
+      </c>
+      <c r="O29">
+        <v>-10.5276594</v>
+      </c>
+      <c r="P29">
+        <v>-24.5645386</v>
+      </c>
+      <c r="Q29">
+        <v>1.535461399999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1411880617025741</v>
+      </c>
+      <c r="T29">
+        <v>1.386497703762981</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.4756782947021552</v>
+      </c>
+      <c r="W29">
+        <v>0.3523919767748747</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-1.585594315673851</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2002131187720952</v>
+      </c>
+      <c r="C30">
+        <v>21.93836655400276</v>
+      </c>
+      <c r="D30">
+        <v>76.59836655400277</v>
+      </c>
+      <c r="E30">
+        <v>-95.66</v>
+      </c>
+      <c r="F30">
+        <v>58.94</v>
+      </c>
+      <c r="G30">
+        <v>4.28</v>
+      </c>
+      <c r="H30">
+        <v>55.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>4.58</v>
+      </c>
+      <c r="K30">
+        <v>26.1</v>
+      </c>
+      <c r="L30">
+        <v>-21.52</v>
+      </c>
+      <c r="M30">
+        <v>14.074872</v>
+      </c>
+      <c r="N30">
+        <v>-35.59487200000001</v>
+      </c>
+      <c r="O30">
+        <v>-10.6784616</v>
+      </c>
+      <c r="P30">
+        <v>-24.91641040000001</v>
+      </c>
+      <c r="Q30">
+        <v>1.183589599999994</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1426101181151098</v>
+      </c>
+      <c r="T30">
+        <v>1.405754616315244</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.4586897841770781</v>
+      </c>
+      <c r="W30">
+        <v>0.3483351204614862</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-1.528965947256927</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2022131187720952</v>
+      </c>
+      <c r="C31">
+        <v>18.89588531468036</v>
+      </c>
+      <c r="D31">
+        <v>75.66088531468036</v>
+      </c>
+      <c r="E31">
+        <v>-93.55500000000001</v>
+      </c>
+      <c r="F31">
+        <v>61.04499999999999</v>
+      </c>
+      <c r="G31">
+        <v>4.28</v>
+      </c>
+      <c r="H31">
+        <v>55.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>4.58</v>
+      </c>
+      <c r="K31">
+        <v>26.1</v>
+      </c>
+      <c r="L31">
+        <v>-21.52</v>
+      </c>
+      <c r="M31">
+        <v>14.577546</v>
+      </c>
+      <c r="N31">
+        <v>-36.097546</v>
+      </c>
+      <c r="O31">
+        <v>-10.8292638</v>
+      </c>
+      <c r="P31">
+        <v>-25.2682822</v>
+      </c>
+      <c r="Q31">
+        <v>0.8317177999999998</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1440722324547593</v>
+      </c>
+      <c r="T31">
+        <v>1.425553977108417</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.4428728950675238</v>
+      </c>
+      <c r="W31">
+        <v>0.3445580473421247</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-1.476242983558413</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2042131187720952</v>
+      </c>
+      <c r="C32">
+        <v>15.87607413312075</v>
+      </c>
+      <c r="D32">
+        <v>74.74607413312074</v>
+      </c>
+      <c r="E32">
+        <v>-91.44999999999999</v>
+      </c>
+      <c r="F32">
+        <v>63.15</v>
+      </c>
+      <c r="G32">
+        <v>4.28</v>
+      </c>
+      <c r="H32">
+        <v>55.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>4.58</v>
+      </c>
+      <c r="K32">
+        <v>26.1</v>
+      </c>
+      <c r="L32">
+        <v>-21.52</v>
+      </c>
+      <c r="M32">
+        <v>15.08022</v>
+      </c>
+      <c r="N32">
+        <v>-36.60022000000001</v>
+      </c>
+      <c r="O32">
+        <v>-10.980066</v>
+      </c>
+      <c r="P32">
+        <v>-25.62015400000001</v>
+      </c>
+      <c r="Q32">
+        <v>0.4798459999999949</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1455761214898272</v>
+      </c>
+      <c r="T32">
+        <v>1.445919033924251</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.4281104652319396</v>
+      </c>
+      <c r="W32">
+        <v>0.3410327790973872</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-1.427034884106466</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2062131187720952</v>
+      </c>
+      <c r="C33">
+        <v>12.87812052612325</v>
+      </c>
+      <c r="D33">
+        <v>73.85312052612325</v>
+      </c>
+      <c r="E33">
+        <v>-89.345</v>
+      </c>
+      <c r="F33">
+        <v>65.255</v>
+      </c>
+      <c r="G33">
+        <v>4.28</v>
+      </c>
+      <c r="H33">
+        <v>55.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>4.58</v>
+      </c>
+      <c r="K33">
+        <v>26.1</v>
+      </c>
+      <c r="L33">
+        <v>-21.52</v>
+      </c>
+      <c r="M33">
+        <v>15.582894</v>
+      </c>
+      <c r="N33">
+        <v>-37.10289400000001</v>
+      </c>
+      <c r="O33">
+        <v>-11.1308682</v>
+      </c>
+      <c r="P33">
+        <v>-25.9720258</v>
+      </c>
+      <c r="Q33">
+        <v>0.127974199999997</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.147123601511419</v>
+      </c>
+      <c r="T33">
+        <v>1.466874382241994</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.4143004502244577</v>
+      </c>
+      <c r="W33">
+        <v>0.3377349475136005</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-1.381001500748193</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2082131187720952</v>
+      </c>
+      <c r="C34">
+        <v>9.901250377442821</v>
+      </c>
+      <c r="D34">
+        <v>72.98125037744282</v>
+      </c>
+      <c r="E34">
+        <v>-87.23999999999999</v>
+      </c>
+      <c r="F34">
+        <v>67.36</v>
+      </c>
+      <c r="G34">
+        <v>4.28</v>
+      </c>
+      <c r="H34">
+        <v>55.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>4.58</v>
+      </c>
+      <c r="K34">
+        <v>26.1</v>
+      </c>
+      <c r="L34">
+        <v>-21.52</v>
+      </c>
+      <c r="M34">
+        <v>16.085568</v>
+      </c>
+      <c r="N34">
+        <v>-37.60556800000001</v>
+      </c>
+      <c r="O34">
+        <v>-11.2816704</v>
+      </c>
+      <c r="P34">
+        <v>-26.3238976</v>
+      </c>
+      <c r="Q34">
+        <v>-0.2238976000000008</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1487165956512927</v>
+      </c>
+      <c r="T34">
+        <v>1.488446064333788</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.4013535611549434</v>
+      </c>
+      <c r="W34">
+        <v>0.3346432304038005</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-1.337845203849811</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2102131187720953</v>
+      </c>
+      <c r="C35">
+        <v>6.944725699515701</v>
+      </c>
+      <c r="D35">
+        <v>72.1297256995157</v>
+      </c>
+      <c r="E35">
+        <v>-85.13499999999999</v>
+      </c>
+      <c r="F35">
+        <v>69.465</v>
+      </c>
+      <c r="G35">
+        <v>4.28</v>
+      </c>
+      <c r="H35">
+        <v>55.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>4.58</v>
+      </c>
+      <c r="K35">
+        <v>26.1</v>
+      </c>
+      <c r="L35">
+        <v>-21.52</v>
+      </c>
+      <c r="M35">
+        <v>16.588242</v>
+      </c>
+      <c r="N35">
+        <v>-38.108242</v>
+      </c>
+      <c r="O35">
+        <v>-11.4324726</v>
+      </c>
+      <c r="P35">
+        <v>-26.6757694</v>
+      </c>
+      <c r="Q35">
+        <v>-0.5757694000000022</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1503571418550434</v>
+      </c>
+      <c r="T35">
+        <v>1.510661677234292</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.3891913320290361</v>
+      </c>
+      <c r="W35">
+        <v>0.3317388900885339</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-1.297304440096787</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2122131187720952</v>
+      </c>
+      <c r="C36">
+        <v>4.007842550071743</v>
+      </c>
+      <c r="D36">
+        <v>71.29784255007175</v>
+      </c>
+      <c r="E36">
+        <v>-83.02999999999999</v>
+      </c>
+      <c r="F36">
+        <v>71.57000000000001</v>
+      </c>
+      <c r="G36">
+        <v>4.28</v>
+      </c>
+      <c r="H36">
+        <v>55.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>4.58</v>
+      </c>
+      <c r="K36">
+        <v>26.1</v>
+      </c>
+      <c r="L36">
+        <v>-21.52</v>
+      </c>
+      <c r="M36">
+        <v>17.090916</v>
+      </c>
+      <c r="N36">
+        <v>-38.610916</v>
+      </c>
+      <c r="O36">
+        <v>-11.5832748</v>
+      </c>
+      <c r="P36">
+        <v>-27.02764120000001</v>
+      </c>
+      <c r="Q36">
+        <v>-0.9276412000000036</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1520474015801198</v>
+      </c>
+      <c r="T36">
+        <v>1.533550490525721</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.377744528145829</v>
+      </c>
+      <c r="W36">
+        <v>0.329005393321224</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-1.259148427152763</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2142131187720952</v>
+      </c>
+      <c r="C37">
+        <v>1.089929091270463</v>
+      </c>
+      <c r="D37">
+        <v>70.48492909127047</v>
+      </c>
+      <c r="E37">
+        <v>-80.92499999999998</v>
+      </c>
+      <c r="F37">
+        <v>73.67500000000001</v>
+      </c>
+      <c r="G37">
+        <v>4.28</v>
+      </c>
+      <c r="H37">
+        <v>55.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>4.58</v>
+      </c>
+      <c r="K37">
+        <v>26.1</v>
+      </c>
+      <c r="L37">
+        <v>-21.52</v>
+      </c>
+      <c r="M37">
+        <v>17.59359</v>
+      </c>
+      <c r="N37">
+        <v>-39.11359</v>
+      </c>
+      <c r="O37">
+        <v>-11.734077</v>
+      </c>
+      <c r="P37">
+        <v>-27.379513</v>
+      </c>
+      <c r="Q37">
+        <v>-1.279513000000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.153789669296737</v>
+      </c>
+      <c r="T37">
+        <v>1.557143574995348</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.3669518273416625</v>
+      </c>
+      <c r="W37">
+        <v>0.326428096369189</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-1.223172757805541</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2162131187720952</v>
+      </c>
+      <c r="C38">
+        <v>-1.809656219884715</v>
+      </c>
+      <c r="D38">
+        <v>69.69034378011528</v>
+      </c>
+      <c r="E38">
+        <v>-78.81999999999999</v>
+      </c>
+      <c r="F38">
+        <v>75.78</v>
+      </c>
+      <c r="G38">
+        <v>4.28</v>
+      </c>
+      <c r="H38">
+        <v>55.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>4.58</v>
+      </c>
+      <c r="K38">
+        <v>26.1</v>
+      </c>
+      <c r="L38">
+        <v>-21.52</v>
+      </c>
+      <c r="M38">
+        <v>18.096264</v>
+      </c>
+      <c r="N38">
+        <v>-39.616264</v>
+      </c>
+      <c r="O38">
+        <v>-11.8848792</v>
+      </c>
+      <c r="P38">
+        <v>-27.7313848</v>
+      </c>
+      <c r="Q38">
+        <v>-1.631384799999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1555863828794986</v>
+      </c>
+      <c r="T38">
+        <v>1.58147394335465</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.3567587210266163</v>
+      </c>
+      <c r="W38">
+        <v>0.323993982581156</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-1.189195736755388</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2182131187720952</v>
+      </c>
+      <c r="C39">
+        <v>-4.691526320099001</v>
+      </c>
+      <c r="D39">
+        <v>68.913473679901</v>
+      </c>
+      <c r="E39">
+        <v>-76.71499999999999</v>
+      </c>
+      <c r="F39">
+        <v>77.88500000000001</v>
+      </c>
+      <c r="G39">
+        <v>4.28</v>
+      </c>
+      <c r="H39">
+        <v>55.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>4.58</v>
+      </c>
+      <c r="K39">
+        <v>26.1</v>
+      </c>
+      <c r="L39">
+        <v>-21.52</v>
+      </c>
+      <c r="M39">
+        <v>18.598938</v>
+      </c>
+      <c r="N39">
+        <v>-40.118938</v>
+      </c>
+      <c r="O39">
+        <v>-12.0356814</v>
+      </c>
+      <c r="P39">
+        <v>-28.0832566</v>
+      </c>
+      <c r="Q39">
+        <v>-1.983256599999997</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1574401349886969</v>
+      </c>
+      <c r="T39">
+        <v>1.606576704360279</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.3471165934313024</v>
+      </c>
+      <c r="W39">
+        <v>0.321691442511395</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-1.157055311437674</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2202131187720953</v>
+      </c>
+      <c r="C40">
+        <v>-7.556267116644989</v>
+      </c>
+      <c r="D40">
+        <v>68.153732883355</v>
+      </c>
+      <c r="E40">
+        <v>-74.61</v>
+      </c>
+      <c r="F40">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="G40">
+        <v>4.28</v>
+      </c>
+      <c r="H40">
+        <v>55.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>4.58</v>
+      </c>
+      <c r="K40">
+        <v>26.1</v>
+      </c>
+      <c r="L40">
+        <v>-21.52</v>
+      </c>
+      <c r="M40">
+        <v>19.101612</v>
+      </c>
+      <c r="N40">
+        <v>-40.621612</v>
+      </c>
+      <c r="O40">
+        <v>-12.1864836</v>
+      </c>
+      <c r="P40">
+        <v>-28.4351284</v>
+      </c>
+      <c r="Q40">
+        <v>-2.335128399999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1593536855530308</v>
+      </c>
+      <c r="T40">
+        <v>1.632489231849961</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.3379819462357418</v>
+      </c>
+      <c r="W40">
+        <v>0.3195100887610952</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-1.126606487452473</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2222131187720953</v>
+      </c>
+      <c r="C41">
+        <v>-10.40443896105424</v>
+      </c>
+      <c r="D41">
+        <v>67.41056103894576</v>
+      </c>
+      <c r="E41">
+        <v>-72.505</v>
+      </c>
+      <c r="F41">
+        <v>82.095</v>
+      </c>
+      <c r="G41">
+        <v>4.28</v>
+      </c>
+      <c r="H41">
+        <v>55.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>4.58</v>
+      </c>
+      <c r="K41">
+        <v>26.1</v>
+      </c>
+      <c r="L41">
+        <v>-21.52</v>
+      </c>
+      <c r="M41">
+        <v>19.604286</v>
+      </c>
+      <c r="N41">
+        <v>-41.12428600000001</v>
+      </c>
+      <c r="O41">
+        <v>-12.3372858</v>
+      </c>
+      <c r="P41">
+        <v>-28.7870002</v>
+      </c>
+      <c r="Q41">
+        <v>-2.6870002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1613299754801296</v>
+      </c>
+      <c r="T41">
+        <v>1.659251350404878</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.3293157424861074</v>
+      </c>
+      <c r="W41">
+        <v>0.3174405993056825</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-1.097719141620358</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2242131187720953</v>
+      </c>
+      <c r="C42">
+        <v>-13.23657802743071</v>
+      </c>
+      <c r="D42">
+        <v>66.68342197256929</v>
+      </c>
+      <c r="E42">
+        <v>-70.39999999999999</v>
+      </c>
+      <c r="F42">
+        <v>84.2</v>
+      </c>
+      <c r="G42">
+        <v>4.28</v>
+      </c>
+      <c r="H42">
+        <v>55.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>4.58</v>
+      </c>
+      <c r="K42">
+        <v>26.1</v>
+      </c>
+      <c r="L42">
+        <v>-21.52</v>
+      </c>
+      <c r="M42">
+        <v>20.10696</v>
+      </c>
+      <c r="N42">
+        <v>-41.62696</v>
+      </c>
+      <c r="O42">
+        <v>-12.488088</v>
+      </c>
+      <c r="P42">
+        <v>-29.138872</v>
+      </c>
+      <c r="Q42">
+        <v>-3.038872000000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1633721417381318</v>
+      </c>
+      <c r="T42">
+        <v>1.686905539578293</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.3210828489239547</v>
+      </c>
+      <c r="W42">
+        <v>0.3154745843230404</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-1.070276163079849</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2262131187720952</v>
+      </c>
+      <c r="C43">
+        <v>-16.05319760251136</v>
+      </c>
+      <c r="D43">
+        <v>65.97180239748864</v>
+      </c>
+      <c r="E43">
+        <v>-68.29499999999999</v>
+      </c>
+      <c r="F43">
+        <v>86.30500000000001</v>
+      </c>
+      <c r="G43">
+        <v>4.28</v>
+      </c>
+      <c r="H43">
+        <v>55.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>4.58</v>
+      </c>
+      <c r="K43">
+        <v>26.1</v>
+      </c>
+      <c r="L43">
+        <v>-21.52</v>
+      </c>
+      <c r="M43">
+        <v>20.609634</v>
+      </c>
+      <c r="N43">
+        <v>-42.12963400000001</v>
+      </c>
+      <c r="O43">
+        <v>-12.6388902</v>
+      </c>
+      <c r="P43">
+        <v>-29.49074380000001</v>
+      </c>
+      <c r="Q43">
+        <v>-3.390743800000006</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1654835339709815</v>
+      </c>
+      <c r="T43">
+        <v>1.715497158893179</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.3132515599258094</v>
+      </c>
+      <c r="W43">
+        <v>0.3136044725102833</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-1.044171866419365</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2282131187720952</v>
+      </c>
+      <c r="C44">
+        <v>-18.85478929399675</v>
+      </c>
+      <c r="D44">
+        <v>65.27521070600325</v>
+      </c>
+      <c r="E44">
+        <v>-66.19</v>
+      </c>
+      <c r="F44">
+        <v>88.41</v>
+      </c>
+      <c r="G44">
+        <v>4.28</v>
+      </c>
+      <c r="H44">
+        <v>55.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>4.58</v>
+      </c>
+      <c r="K44">
+        <v>26.1</v>
+      </c>
+      <c r="L44">
+        <v>-21.52</v>
+      </c>
+      <c r="M44">
+        <v>21.112308</v>
+      </c>
+      <c r="N44">
+        <v>-42.632308</v>
+      </c>
+      <c r="O44">
+        <v>-12.7896924</v>
+      </c>
+      <c r="P44">
+        <v>-29.8426156</v>
+      </c>
+      <c r="Q44">
+        <v>-3.742615600000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1676677328325501</v>
+      </c>
+      <c r="T44">
+        <v>1.745074696115475</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.3057931894513855</v>
+      </c>
+      <c r="W44">
+        <v>0.3118234136409909</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-1.019310631504618</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2302131187720952</v>
+      </c>
+      <c r="C45">
+        <v>-21.64182416312943</v>
+      </c>
+      <c r="D45">
+        <v>64.59317583687057</v>
+      </c>
+      <c r="E45">
+        <v>-64.08499999999999</v>
+      </c>
+      <c r="F45">
+        <v>90.515</v>
+      </c>
+      <c r="G45">
+        <v>4.28</v>
+      </c>
+      <c r="H45">
+        <v>55.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>4.58</v>
+      </c>
+      <c r="K45">
+        <v>26.1</v>
+      </c>
+      <c r="L45">
+        <v>-21.52</v>
+      </c>
+      <c r="M45">
+        <v>21.614982</v>
+      </c>
+      <c r="N45">
+        <v>-43.13498200000001</v>
+      </c>
+      <c r="O45">
+        <v>-12.9404946</v>
+      </c>
+      <c r="P45">
+        <v>-30.19448740000001</v>
+      </c>
+      <c r="Q45">
+        <v>-4.094487400000006</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.169928570250665</v>
+      </c>
+      <c r="T45">
+        <v>1.775690041661361</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.2986817199292602</v>
+      </c>
+      <c r="W45">
+        <v>0.3101251947191073</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.9956057330975341</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2322131187720953</v>
+      </c>
+      <c r="C46">
+        <v>-24.41475378700345</v>
+      </c>
+      <c r="D46">
+        <v>63.92524621299656</v>
+      </c>
+      <c r="E46">
+        <v>-61.97999999999999</v>
+      </c>
+      <c r="F46">
+        <v>92.62</v>
+      </c>
+      <c r="G46">
+        <v>4.28</v>
+      </c>
+      <c r="H46">
+        <v>55.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>4.58</v>
+      </c>
+      <c r="K46">
+        <v>26.1</v>
+      </c>
+      <c r="L46">
+        <v>-21.52</v>
+      </c>
+      <c r="M46">
+        <v>22.117656</v>
+      </c>
+      <c r="N46">
+        <v>-43.63765600000001</v>
+      </c>
+      <c r="O46">
+        <v>-13.0912968</v>
+      </c>
+      <c r="P46">
+        <v>-30.5463592</v>
+      </c>
+      <c r="Q46">
+        <v>-4.446359200000003</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1722701518622841</v>
+      </c>
+      <c r="T46">
+        <v>1.807398792405314</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.291893499021777</v>
+      </c>
+      <c r="W46">
+        <v>0.3085041675664004</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.97297833007259</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2342131187720952</v>
+      </c>
+      <c r="C47">
+        <v>-27.17401125563892</v>
+      </c>
+      <c r="D47">
+        <v>63.27098874436109</v>
+      </c>
+      <c r="E47">
+        <v>-59.87499999999999</v>
+      </c>
+      <c r="F47">
+        <v>94.72500000000001</v>
+      </c>
+      <c r="G47">
+        <v>4.28</v>
+      </c>
+      <c r="H47">
+        <v>55.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>4.58</v>
+      </c>
+      <c r="K47">
+        <v>26.1</v>
+      </c>
+      <c r="L47">
+        <v>-21.52</v>
+      </c>
+      <c r="M47">
+        <v>22.62033</v>
+      </c>
+      <c r="N47">
+        <v>-44.14033000000001</v>
+      </c>
+      <c r="O47">
+        <v>-13.242099</v>
+      </c>
+      <c r="P47">
+        <v>-30.898231</v>
+      </c>
+      <c r="Q47">
+        <v>-4.798231000000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1746968818961438</v>
+      </c>
+      <c r="T47">
+        <v>1.840260588630865</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.2854069768212931</v>
+      </c>
+      <c r="W47">
+        <v>0.3069551860649248</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.9513565894043101</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2362131187720952</v>
+      </c>
+      <c r="C48">
+        <v>-29.92001210844853</v>
+      </c>
+      <c r="D48">
+        <v>62.62998789155147</v>
+      </c>
+      <c r="E48">
+        <v>-57.77</v>
+      </c>
+      <c r="F48">
+        <v>96.83</v>
+      </c>
+      <c r="G48">
+        <v>4.28</v>
+      </c>
+      <c r="H48">
+        <v>55.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>4.58</v>
+      </c>
+      <c r="K48">
+        <v>26.1</v>
+      </c>
+      <c r="L48">
+        <v>-21.52</v>
+      </c>
+      <c r="M48">
+        <v>23.123004</v>
+      </c>
+      <c r="N48">
+        <v>-44.643004</v>
+      </c>
+      <c r="O48">
+        <v>-13.3929012</v>
+      </c>
+      <c r="P48">
+        <v>-31.2501028</v>
+      </c>
+      <c r="Q48">
+        <v>-5.150102800000003</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1772134908201464</v>
+      </c>
+      <c r="T48">
+        <v>1.874339488420325</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.279202477325178</v>
+      </c>
+      <c r="W48">
+        <v>0.3054735515852525</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.9306749244172601</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2382131187720953</v>
+      </c>
+      <c r="C49">
+        <v>-32.65315521435051</v>
+      </c>
+      <c r="D49">
+        <v>62.0018447856495</v>
+      </c>
+      <c r="E49">
+        <v>-55.66499999999999</v>
+      </c>
+      <c r="F49">
+        <v>98.935</v>
+      </c>
+      <c r="G49">
+        <v>4.28</v>
+      </c>
+      <c r="H49">
+        <v>55.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>4.58</v>
+      </c>
+      <c r="K49">
+        <v>26.1</v>
+      </c>
+      <c r="L49">
+        <v>-21.52</v>
+      </c>
+      <c r="M49">
+        <v>23.625678</v>
+      </c>
+      <c r="N49">
+        <v>-45.145678</v>
+      </c>
+      <c r="O49">
+        <v>-13.5437034</v>
+      </c>
+      <c r="P49">
+        <v>-31.60197460000001</v>
+      </c>
+      <c r="Q49">
+        <v>-5.501974600000004</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1798250661186398</v>
+      </c>
+      <c r="T49">
+        <v>1.909704384428256</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.2732619990842168</v>
+      </c>
+      <c r="W49">
+        <v>0.304054965381311</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.9108733302807226</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2402131187720953</v>
+      </c>
+      <c r="C50">
+        <v>-35.37382359944517</v>
+      </c>
+      <c r="D50">
+        <v>61.38617640055482</v>
+      </c>
+      <c r="E50">
+        <v>-53.56</v>
+      </c>
+      <c r="F50">
+        <v>101.04</v>
+      </c>
+      <c r="G50">
+        <v>4.28</v>
+      </c>
+      <c r="H50">
+        <v>55.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>4.58</v>
+      </c>
+      <c r="K50">
+        <v>26.1</v>
+      </c>
+      <c r="L50">
+        <v>-21.52</v>
+      </c>
+      <c r="M50">
+        <v>24.128352</v>
+      </c>
+      <c r="N50">
+        <v>-45.648352</v>
+      </c>
+      <c r="O50">
+        <v>-13.6945056</v>
+      </c>
+      <c r="P50">
+        <v>-31.9538464</v>
+      </c>
+      <c r="Q50">
+        <v>-5.853846400000002</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1825370866209213</v>
+      </c>
+      <c r="T50">
+        <v>1.946429468744184</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.2675690407699622</v>
+      </c>
+      <c r="W50">
+        <v>0.302695486935867</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.891896802566541</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2422131187720952</v>
+      </c>
+      <c r="C51">
+        <v>-38.08238522586448</v>
+      </c>
+      <c r="D51">
+        <v>60.78261477413551</v>
+      </c>
+      <c r="E51">
+        <v>-51.455</v>
+      </c>
+      <c r="F51">
+        <v>103.145</v>
+      </c>
+      <c r="G51">
+        <v>4.28</v>
+      </c>
+      <c r="H51">
+        <v>55.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>4.58</v>
+      </c>
+      <c r="K51">
+        <v>26.1</v>
+      </c>
+      <c r="L51">
+        <v>-21.52</v>
+      </c>
+      <c r="M51">
+        <v>24.631026</v>
+      </c>
+      <c r="N51">
+        <v>-46.151026</v>
+      </c>
+      <c r="O51">
+        <v>-13.8453078</v>
+      </c>
+      <c r="P51">
+        <v>-32.3057182</v>
+      </c>
+      <c r="Q51">
+        <v>-6.2057182</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1853554608683903</v>
+      </c>
+      <c r="T51">
+        <v>1.98459475244505</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.2621084481011875</v>
+      </c>
+      <c r="W51">
+        <v>0.3013914974065636</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.8736948270039582</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2442131187720953</v>
+      </c>
+      <c r="C52">
+        <v>-40.77919372512177</v>
+      </c>
+      <c r="D52">
+        <v>60.19080627487823</v>
+      </c>
+      <c r="E52">
+        <v>-49.34999999999999</v>
+      </c>
+      <c r="F52">
+        <v>105.25</v>
+      </c>
+      <c r="G52">
+        <v>4.28</v>
+      </c>
+      <c r="H52">
+        <v>55.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>4.58</v>
+      </c>
+      <c r="K52">
+        <v>26.1</v>
+      </c>
+      <c r="L52">
+        <v>-21.52</v>
+      </c>
+      <c r="M52">
+        <v>25.1337</v>
+      </c>
+      <c r="N52">
+        <v>-46.6537</v>
+      </c>
+      <c r="O52">
+        <v>-13.99611</v>
+      </c>
+      <c r="P52">
+        <v>-32.65759</v>
+      </c>
+      <c r="Q52">
+        <v>-6.557589999999998</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1882865700857582</v>
+      </c>
+      <c r="T52">
+        <v>2.024286647493952</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.2568662791391638</v>
+      </c>
+      <c r="W52">
+        <v>0.3001396674584323</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.856220930463879</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2462131187720952</v>
+      </c>
+      <c r="C53">
+        <v>-43.4645890890333</v>
+      </c>
+      <c r="D53">
+        <v>59.61041091096671</v>
+      </c>
+      <c r="E53">
+        <v>-47.24499999999999</v>
+      </c>
+      <c r="F53">
+        <v>107.355</v>
+      </c>
+      <c r="G53">
+        <v>4.28</v>
+      </c>
+      <c r="H53">
+        <v>55.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>4.58</v>
+      </c>
+      <c r="K53">
+        <v>26.1</v>
+      </c>
+      <c r="L53">
+        <v>-21.52</v>
+      </c>
+      <c r="M53">
+        <v>25.636374</v>
+      </c>
+      <c r="N53">
+        <v>-47.15637400000001</v>
+      </c>
+      <c r="O53">
+        <v>-14.1469122</v>
+      </c>
+      <c r="P53">
+        <v>-33.0094618</v>
+      </c>
+      <c r="Q53">
+        <v>-6.909461800000003</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1913373164140389</v>
+      </c>
+      <c r="T53">
+        <v>2.065598619891787</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.2518296854305527</v>
+      </c>
+      <c r="W53">
+        <v>0.298936928880816</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.839432284768509</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2482131187720953</v>
+      </c>
+      <c r="C54">
+        <v>-46.13889832104796</v>
+      </c>
+      <c r="D54">
+        <v>59.04110167895205</v>
+      </c>
+      <c r="E54">
+        <v>-45.13999999999999</v>
+      </c>
+      <c r="F54">
+        <v>109.46</v>
+      </c>
+      <c r="G54">
+        <v>4.28</v>
+      </c>
+      <c r="H54">
+        <v>55.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>4.58</v>
+      </c>
+      <c r="K54">
+        <v>26.1</v>
+      </c>
+      <c r="L54">
+        <v>-21.52</v>
+      </c>
+      <c r="M54">
+        <v>26.139048</v>
+      </c>
+      <c r="N54">
+        <v>-47.65904800000001</v>
+      </c>
+      <c r="O54">
+        <v>-14.2977144</v>
+      </c>
+      <c r="P54">
+        <v>-33.3613336</v>
+      </c>
+      <c r="Q54">
+        <v>-7.2613336</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1945151771726648</v>
+      </c>
+      <c r="T54">
+        <v>2.108631924472867</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.2469868068645805</v>
+      </c>
+      <c r="W54">
+        <v>0.2977804494792619</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.8232893562152686</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2502131187720952</v>
+      </c>
+      <c r="C55">
+        <v>-48.80243605060674</v>
+      </c>
+      <c r="D55">
+        <v>58.48256394939327</v>
+      </c>
+      <c r="E55">
+        <v>-43.03499999999998</v>
+      </c>
+      <c r="F55">
+        <v>111.565</v>
+      </c>
+      <c r="G55">
+        <v>4.28</v>
+      </c>
+      <c r="H55">
+        <v>55.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>4.58</v>
+      </c>
+      <c r="K55">
+        <v>26.1</v>
+      </c>
+      <c r="L55">
+        <v>-21.52</v>
+      </c>
+      <c r="M55">
+        <v>26.64172200000001</v>
+      </c>
+      <c r="N55">
+        <v>-48.16172200000001</v>
+      </c>
+      <c r="O55">
+        <v>-14.4485166</v>
+      </c>
+      <c r="P55">
+        <v>-33.71320540000001</v>
+      </c>
+      <c r="Q55">
+        <v>-7.613205400000005</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1978282660486789</v>
+      </c>
+      <c r="T55">
+        <v>2.153496433504204</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.2423266784331733</v>
+      </c>
+      <c r="W55">
+        <v>0.2966676108098418</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.8077555947772446</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2522131187720953</v>
+      </c>
+      <c r="C56">
+        <v>-51.45550511295755</v>
+      </c>
+      <c r="D56">
+        <v>57.93449488704245</v>
+      </c>
+      <c r="E56">
+        <v>-40.92999999999999</v>
+      </c>
+      <c r="F56">
+        <v>113.67</v>
+      </c>
+      <c r="G56">
+        <v>4.28</v>
+      </c>
+      <c r="H56">
+        <v>55.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>4.58</v>
+      </c>
+      <c r="K56">
+        <v>26.1</v>
+      </c>
+      <c r="L56">
+        <v>-21.52</v>
+      </c>
+      <c r="M56">
+        <v>27.144396</v>
+      </c>
+      <c r="N56">
+        <v>-48.664396</v>
+      </c>
+      <c r="O56">
+        <v>-14.5993188</v>
+      </c>
+      <c r="P56">
+        <v>-34.0650772</v>
+      </c>
+      <c r="Q56">
+        <v>-7.965077200000003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2012854022671284</v>
+      </c>
+      <c r="T56">
+        <v>2.200311573362991</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.2378391473510776</v>
+      </c>
+      <c r="W56">
+        <v>0.2955959883874374</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.7927971578369253</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2542131187720952</v>
+      </c>
+      <c r="C57">
+        <v>-54.09839709667034</v>
+      </c>
+      <c r="D57">
+        <v>57.39660290332966</v>
+      </c>
+      <c r="E57">
+        <v>-38.82499999999999</v>
+      </c>
+      <c r="F57">
+        <v>115.775</v>
+      </c>
+      <c r="G57">
+        <v>4.28</v>
+      </c>
+      <c r="H57">
+        <v>55.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>4.58</v>
+      </c>
+      <c r="K57">
+        <v>26.1</v>
+      </c>
+      <c r="L57">
+        <v>-21.52</v>
+      </c>
+      <c r="M57">
+        <v>27.64707</v>
+      </c>
+      <c r="N57">
+        <v>-49.16707000000001</v>
+      </c>
+      <c r="O57">
+        <v>-14.750121</v>
+      </c>
+      <c r="P57">
+        <v>-34.41694900000001</v>
+      </c>
+      <c r="Q57">
+        <v>-8.316949000000008</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2048961889841757</v>
+      </c>
+      <c r="T57">
+        <v>2.249207386104391</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.2335147992174216</v>
+      </c>
+      <c r="W57">
+        <v>0.2945633340531203</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.7783826640580722</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2562131187720952</v>
+      </c>
+      <c r="C58">
+        <v>-56.73139286093236</v>
+      </c>
+      <c r="D58">
+        <v>56.86860713906765</v>
+      </c>
+      <c r="E58">
+        <v>-36.71999999999998</v>
+      </c>
+      <c r="F58">
+        <v>117.88</v>
+      </c>
+      <c r="G58">
+        <v>4.28</v>
+      </c>
+      <c r="H58">
+        <v>55.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>4.58</v>
+      </c>
+      <c r="K58">
+        <v>26.1</v>
+      </c>
+      <c r="L58">
+        <v>-21.52</v>
+      </c>
+      <c r="M58">
+        <v>28.14974400000001</v>
+      </c>
+      <c r="N58">
+        <v>-49.66974400000001</v>
+      </c>
+      <c r="O58">
+        <v>-14.9009232</v>
+      </c>
+      <c r="P58">
+        <v>-34.76882080000001</v>
+      </c>
+      <c r="Q58">
+        <v>-8.668820800000006</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2086711023701797</v>
+      </c>
+      <c r="T58">
+        <v>2.300325735788582</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.229344892088539</v>
+      </c>
+      <c r="W58">
+        <v>0.2935675602307432</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.7644829736284635</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2582131187720953</v>
+      </c>
+      <c r="C59">
+        <v>-59.35476302455179</v>
+      </c>
+      <c r="D59">
+        <v>56.35023697544822</v>
+      </c>
+      <c r="E59">
+        <v>-34.61499999999998</v>
+      </c>
+      <c r="F59">
+        <v>119.985</v>
+      </c>
+      <c r="G59">
+        <v>4.28</v>
+      </c>
+      <c r="H59">
+        <v>55.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>4.58</v>
+      </c>
+      <c r="K59">
+        <v>26.1</v>
+      </c>
+      <c r="L59">
+        <v>-21.52</v>
+      </c>
+      <c r="M59">
+        <v>28.652418</v>
+      </c>
+      <c r="N59">
+        <v>-50.17241800000001</v>
+      </c>
+      <c r="O59">
+        <v>-15.0517254</v>
+      </c>
+      <c r="P59">
+        <v>-35.12069260000001</v>
+      </c>
+      <c r="Q59">
+        <v>-9.020692600000004</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2126215931229747</v>
+      </c>
+      <c r="T59">
+        <v>2.353821683132503</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.2253212974904945</v>
+      </c>
+      <c r="W59">
+        <v>0.2926067258407301</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.7510709916349818</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2602131187720952</v>
+      </c>
+      <c r="C60">
+        <v>-61.96876842845874</v>
+      </c>
+      <c r="D60">
+        <v>55.84123157154124</v>
+      </c>
+      <c r="E60">
+        <v>-32.51000000000001</v>
+      </c>
+      <c r="F60">
+        <v>122.09</v>
+      </c>
+      <c r="G60">
+        <v>4.28</v>
+      </c>
+      <c r="H60">
+        <v>55.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>4.58</v>
+      </c>
+      <c r="K60">
+        <v>26.1</v>
+      </c>
+      <c r="L60">
+        <v>-21.52</v>
+      </c>
+      <c r="M60">
+        <v>29.155092</v>
+      </c>
+      <c r="N60">
+        <v>-50.67509200000001</v>
+      </c>
+      <c r="O60">
+        <v>-15.2025276</v>
+      </c>
+      <c r="P60">
+        <v>-35.4725644</v>
+      </c>
+      <c r="Q60">
+        <v>-9.372564400000002</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2167602024830454</v>
+      </c>
+      <c r="T60">
+        <v>2.409865056540418</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.2214364475337619</v>
+      </c>
+      <c r="W60">
+        <v>0.2916790236710624</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.7381214917792065</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2622131187720952</v>
+      </c>
+      <c r="C61">
+        <v>-64.57366057336458</v>
+      </c>
+      <c r="D61">
+        <v>55.34133942663542</v>
+      </c>
+      <c r="E61">
+        <v>-30.405</v>
+      </c>
+      <c r="F61">
+        <v>124.195</v>
+      </c>
+      <c r="G61">
+        <v>4.28</v>
+      </c>
+      <c r="H61">
+        <v>55.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>4.58</v>
+      </c>
+      <c r="K61">
+        <v>26.1</v>
+      </c>
+      <c r="L61">
+        <v>-21.52</v>
+      </c>
+      <c r="M61">
+        <v>29.657766</v>
+      </c>
+      <c r="N61">
+        <v>-51.17776600000001</v>
+      </c>
+      <c r="O61">
+        <v>-15.3533298</v>
+      </c>
+      <c r="P61">
+        <v>-35.82443620000001</v>
+      </c>
+      <c r="Q61">
+        <v>-9.724436200000007</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2211006952265343</v>
+      </c>
+      <c r="T61">
+        <v>2.468642253041404</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.217683287406071</v>
+      </c>
+      <c r="W61">
+        <v>0.2907827690325698</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.7256109580202368</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2642131187720952</v>
+      </c>
+      <c r="C62">
+        <v>-67.16968203412159</v>
+      </c>
+      <c r="D62">
+        <v>54.8503179658784</v>
+      </c>
+      <c r="E62">
+        <v>-28.3</v>
+      </c>
+      <c r="F62">
+        <v>126.3</v>
+      </c>
+      <c r="G62">
+        <v>4.28</v>
+      </c>
+      <c r="H62">
+        <v>55.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>4.58</v>
+      </c>
+      <c r="K62">
+        <v>26.1</v>
+      </c>
+      <c r="L62">
+        <v>-21.52</v>
+      </c>
+      <c r="M62">
+        <v>30.16044</v>
+      </c>
+      <c r="N62">
+        <v>-51.68044</v>
+      </c>
+      <c r="O62">
+        <v>-15.504132</v>
+      </c>
+      <c r="P62">
+        <v>-36.17630800000001</v>
+      </c>
+      <c r="Q62">
+        <v>-10.076308</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2256582126071977</v>
+      </c>
+      <c r="T62">
+        <v>2.530358309367439</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.2140552326159698</v>
+      </c>
+      <c r="W62">
+        <v>0.2899163895486936</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.7135174420532326</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2662131187720952</v>
+      </c>
+      <c r="C63">
+        <v>-69.75706685221863</v>
+      </c>
+      <c r="D63">
+        <v>54.36793314778137</v>
+      </c>
+      <c r="E63">
+        <v>-26.19499999999999</v>
+      </c>
+      <c r="F63">
+        <v>128.405</v>
+      </c>
+      <c r="G63">
+        <v>4.28</v>
+      </c>
+      <c r="H63">
+        <v>55.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>4.58</v>
+      </c>
+      <c r="K63">
+        <v>26.1</v>
+      </c>
+      <c r="L63">
+        <v>-21.52</v>
+      </c>
+      <c r="M63">
+        <v>30.663114</v>
+      </c>
+      <c r="N63">
+        <v>-52.183114</v>
+      </c>
+      <c r="O63">
+        <v>-15.6549342</v>
+      </c>
+      <c r="P63">
+        <v>-36.5281798</v>
+      </c>
+      <c r="Q63">
+        <v>-10.4281798</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2304494488278951</v>
+      </c>
+      <c r="T63">
+        <v>2.595239291658912</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.2105461304419375</v>
+      </c>
+      <c r="W63">
+        <v>0.2890784159495347</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.7018204348064585</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2682131187720952</v>
+      </c>
+      <c r="C64">
+        <v>-72.33604090774585</v>
+      </c>
+      <c r="D64">
+        <v>53.89395909225414</v>
+      </c>
+      <c r="E64">
+        <v>-24.09</v>
+      </c>
+      <c r="F64">
+        <v>130.51</v>
+      </c>
+      <c r="G64">
+        <v>4.28</v>
+      </c>
+      <c r="H64">
+        <v>55.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>4.58</v>
+      </c>
+      <c r="K64">
+        <v>26.1</v>
+      </c>
+      <c r="L64">
+        <v>-21.52</v>
+      </c>
+      <c r="M64">
+        <v>31.165788</v>
+      </c>
+      <c r="N64">
+        <v>-52.685788</v>
+      </c>
+      <c r="O64">
+        <v>-15.8057364</v>
+      </c>
+      <c r="P64">
+        <v>-36.8800516</v>
+      </c>
+      <c r="Q64">
+        <v>-10.7800516</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2354928553759975</v>
+      </c>
+      <c r="T64">
+        <v>2.663535062492041</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.2071502251122289</v>
+      </c>
+      <c r="W64">
+        <v>0.2882674737568002</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.6905007503740963</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2702131187720952</v>
+      </c>
+      <c r="C65">
+        <v>-74.90682227207148</v>
+      </c>
+      <c r="D65">
+        <v>53.42817772792853</v>
+      </c>
+      <c r="E65">
+        <v>-21.98499999999999</v>
+      </c>
+      <c r="F65">
+        <v>132.615</v>
+      </c>
+      <c r="G65">
+        <v>4.28</v>
+      </c>
+      <c r="H65">
+        <v>55.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>4.58</v>
+      </c>
+      <c r="K65">
+        <v>26.1</v>
+      </c>
+      <c r="L65">
+        <v>-21.52</v>
+      </c>
+      <c r="M65">
+        <v>31.66846200000001</v>
+      </c>
+      <c r="N65">
+        <v>-53.18846200000001</v>
+      </c>
+      <c r="O65">
+        <v>-15.9565386</v>
+      </c>
+      <c r="P65">
+        <v>-37.23192340000001</v>
+      </c>
+      <c r="Q65">
+        <v>-11.13192340000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2408088784942677</v>
+      </c>
+      <c r="T65">
+        <v>2.735522496613448</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.2038621263009236</v>
+      </c>
+      <c r="W65">
+        <v>0.2874822757606605</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.6795404210030787</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2722131187720952</v>
+      </c>
+      <c r="C66">
+        <v>-77.46962154238666</v>
+      </c>
+      <c r="D66">
+        <v>52.97037845761334</v>
+      </c>
+      <c r="E66">
+        <v>-19.88</v>
+      </c>
+      <c r="F66">
+        <v>134.72</v>
+      </c>
+      <c r="G66">
+        <v>4.28</v>
+      </c>
+      <c r="H66">
+        <v>55.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>4.58</v>
+      </c>
+      <c r="K66">
+        <v>26.1</v>
+      </c>
+      <c r="L66">
+        <v>-21.52</v>
+      </c>
+      <c r="M66">
+        <v>32.171136</v>
+      </c>
+      <c r="N66">
+        <v>-53.69113600000001</v>
+      </c>
+      <c r="O66">
+        <v>-16.1073408</v>
+      </c>
+      <c r="P66">
+        <v>-37.5837952</v>
+      </c>
+      <c r="Q66">
+        <v>-11.4837952</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2464202362302196</v>
+      </c>
+      <c r="T66">
+        <v>2.811509232630488</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.2006767805774717</v>
+      </c>
+      <c r="W66">
+        <v>0.2867216152019003</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.6689226019249057</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2742131187720953</v>
+      </c>
+      <c r="C67">
+        <v>-80.02464215919773</v>
+      </c>
+      <c r="D67">
+        <v>52.5203578408023</v>
+      </c>
+      <c r="E67">
+        <v>-17.77499999999998</v>
+      </c>
+      <c r="F67">
+        <v>136.825</v>
+      </c>
+      <c r="G67">
+        <v>4.28</v>
+      </c>
+      <c r="H67">
+        <v>55.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>4.58</v>
+      </c>
+      <c r="K67">
+        <v>26.1</v>
+      </c>
+      <c r="L67">
+        <v>-21.52</v>
+      </c>
+      <c r="M67">
+        <v>32.67381</v>
+      </c>
+      <c r="N67">
+        <v>-54.19381000000001</v>
+      </c>
+      <c r="O67">
+        <v>-16.258143</v>
+      </c>
+      <c r="P67">
+        <v>-37.93566700000001</v>
+      </c>
+      <c r="Q67">
+        <v>-11.83566700000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2523522429796545</v>
+      </c>
+      <c r="T67">
+        <v>2.891838067848503</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.1975894454916644</v>
+      </c>
+      <c r="W67">
+        <v>0.2859843595834095</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.6586314849722148</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2762131187720953</v>
+      </c>
+      <c r="C68">
+        <v>-82.57208070777024</v>
+      </c>
+      <c r="D68">
+        <v>52.07791929222977</v>
+      </c>
+      <c r="E68">
+        <v>-15.66999999999999</v>
+      </c>
+      <c r="F68">
+        <v>138.93</v>
+      </c>
+      <c r="G68">
+        <v>4.28</v>
+      </c>
+      <c r="H68">
+        <v>55.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>4.58</v>
+      </c>
+      <c r="K68">
+        <v>26.1</v>
+      </c>
+      <c r="L68">
+        <v>-21.52</v>
+      </c>
+      <c r="M68">
+        <v>33.176484</v>
+      </c>
+      <c r="N68">
+        <v>-54.69648400000001</v>
+      </c>
+      <c r="O68">
+        <v>-16.4089452</v>
+      </c>
+      <c r="P68">
+        <v>-38.28753880000001</v>
+      </c>
+      <c r="Q68">
+        <v>-12.18753880000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2586331913025856</v>
+      </c>
+      <c r="T68">
+        <v>2.976892128667576</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.194595666014518</v>
+      </c>
+      <c r="W68">
+        <v>0.2852694450442669</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.6486522200483933</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2782131187720953</v>
+      </c>
+      <c r="C69">
+        <v>-85.11212720446454</v>
+      </c>
+      <c r="D69">
+        <v>51.64287279553546</v>
+      </c>
+      <c r="E69">
+        <v>-13.565</v>
+      </c>
+      <c r="F69">
+        <v>141.035</v>
+      </c>
+      <c r="G69">
+        <v>4.28</v>
+      </c>
+      <c r="H69">
+        <v>55.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>4.58</v>
+      </c>
+      <c r="K69">
+        <v>26.1</v>
+      </c>
+      <c r="L69">
+        <v>-21.52</v>
+      </c>
+      <c r="M69">
+        <v>33.679158</v>
+      </c>
+      <c r="N69">
+        <v>-55.199158</v>
+      </c>
+      <c r="O69">
+        <v>-16.5597474</v>
+      </c>
+      <c r="P69">
+        <v>-38.63941060000001</v>
+      </c>
+      <c r="Q69">
+        <v>-12.5394106</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2652948031602397</v>
+      </c>
+      <c r="T69">
+        <v>3.067100981051442</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.1916912530889282</v>
+      </c>
+      <c r="W69">
+        <v>0.2845758712376361</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.6389708436297608</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2802131187720953</v>
+      </c>
+      <c r="C70">
+        <v>-87.64496536883777</v>
+      </c>
+      <c r="D70">
+        <v>51.21503463116223</v>
+      </c>
+      <c r="E70">
+        <v>-11.45999999999998</v>
+      </c>
+      <c r="F70">
+        <v>143.14</v>
+      </c>
+      <c r="G70">
+        <v>4.28</v>
+      </c>
+      <c r="H70">
+        <v>55.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>4.58</v>
+      </c>
+      <c r="K70">
+        <v>26.1</v>
+      </c>
+      <c r="L70">
+        <v>-21.52</v>
+      </c>
+      <c r="M70">
+        <v>34.18183200000001</v>
+      </c>
+      <c r="N70">
+        <v>-55.70183200000001</v>
+      </c>
+      <c r="O70">
+        <v>-16.7105496</v>
+      </c>
+      <c r="P70">
+        <v>-38.9912824</v>
+      </c>
+      <c r="Q70">
+        <v>-12.8912824</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2723727657589972</v>
+      </c>
+      <c r="T70">
+        <v>3.1629478867093</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.1888722640729145</v>
+      </c>
+      <c r="W70">
+        <v>0.283902696660612</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.6295742135763818</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2822131187720952</v>
+      </c>
+      <c r="C71">
+        <v>-90.17077288233186</v>
+      </c>
+      <c r="D71">
+        <v>50.79422711766814</v>
+      </c>
+      <c r="E71">
+        <v>-9.35499999999999</v>
+      </c>
+      <c r="F71">
+        <v>145.245</v>
+      </c>
+      <c r="G71">
+        <v>4.28</v>
+      </c>
+      <c r="H71">
+        <v>55.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>4.58</v>
+      </c>
+      <c r="K71">
+        <v>26.1</v>
+      </c>
+      <c r="L71">
+        <v>-21.52</v>
+      </c>
+      <c r="M71">
+        <v>34.68450600000001</v>
+      </c>
+      <c r="N71">
+        <v>-56.20450600000001</v>
+      </c>
+      <c r="O71">
+        <v>-16.8613518</v>
+      </c>
+      <c r="P71">
+        <v>-39.34315420000001</v>
+      </c>
+      <c r="Q71">
+        <v>-13.24315420000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2799073711060616</v>
+      </c>
+      <c r="T71">
+        <v>3.264978463699923</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.186134984883452</v>
+      </c>
+      <c r="W71">
+        <v>0.2832490343901684</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.6204499496115066</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2842131187720953</v>
+      </c>
+      <c r="C72">
+        <v>-92.68972163431232</v>
+      </c>
+      <c r="D72">
+        <v>50.38027836568771</v>
+      </c>
+      <c r="E72">
+        <v>-7.249999999999972</v>
+      </c>
+      <c r="F72">
+        <v>147.35</v>
+      </c>
+      <c r="G72">
+        <v>4.28</v>
+      </c>
+      <c r="H72">
+        <v>55.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>4.58</v>
+      </c>
+      <c r="K72">
+        <v>26.1</v>
+      </c>
+      <c r="L72">
+        <v>-21.52</v>
+      </c>
+      <c r="M72">
+        <v>35.18718000000001</v>
+      </c>
+      <c r="N72">
+        <v>-56.70718000000001</v>
+      </c>
+      <c r="O72">
+        <v>-17.012154</v>
+      </c>
+      <c r="P72">
+        <v>-39.69502600000001</v>
+      </c>
+      <c r="Q72">
+        <v>-13.595026</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2879442834762637</v>
+      </c>
+      <c r="T72">
+        <v>3.373811079156587</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.1834759136708312</v>
+      </c>
+      <c r="W72">
+        <v>0.2826140481845945</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.6115863789027709</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2862131187720953</v>
+      </c>
+      <c r="C73">
+        <v>-95.20197795617366</v>
+      </c>
+      <c r="D73">
+        <v>49.97302204382633</v>
+      </c>
+      <c r="E73">
+        <v>-5.14500000000001</v>
+      </c>
+      <c r="F73">
+        <v>149.455</v>
+      </c>
+      <c r="G73">
+        <v>4.28</v>
+      </c>
+      <c r="H73">
+        <v>55.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>4.58</v>
+      </c>
+      <c r="K73">
+        <v>26.1</v>
+      </c>
+      <c r="L73">
+        <v>-21.52</v>
+      </c>
+      <c r="M73">
+        <v>35.689854</v>
+      </c>
+      <c r="N73">
+        <v>-57.209854</v>
+      </c>
+      <c r="O73">
+        <v>-17.1629562</v>
+      </c>
+      <c r="P73">
+        <v>-40.0468978</v>
+      </c>
+      <c r="Q73">
+        <v>-13.9468978</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2965354656651003</v>
+      </c>
+      <c r="T73">
+        <v>3.490149392230951</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.1808917458726506</v>
+      </c>
+      <c r="W73">
+        <v>0.281996948914389</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.6029724862421686</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2882131187720952</v>
+      </c>
+      <c r="C74">
+        <v>-97.70770284418157</v>
+      </c>
+      <c r="D74">
+        <v>49.57229715581843</v>
+      </c>
+      <c r="E74">
+        <v>-3.039999999999992</v>
+      </c>
+      <c r="F74">
+        <v>151.56</v>
+      </c>
+      <c r="G74">
+        <v>4.28</v>
+      </c>
+      <c r="H74">
+        <v>55.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>4.58</v>
+      </c>
+      <c r="K74">
+        <v>26.1</v>
+      </c>
+      <c r="L74">
+        <v>-21.52</v>
+      </c>
+      <c r="M74">
+        <v>36.192528</v>
+      </c>
+      <c r="N74">
+        <v>-57.71252800000001</v>
+      </c>
+      <c r="O74">
+        <v>-17.3137584</v>
+      </c>
+      <c r="P74">
+        <v>-40.39876960000001</v>
+      </c>
+      <c r="Q74">
+        <v>-14.29876960000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3057403037245682</v>
+      </c>
+      <c r="T74">
+        <v>3.614797584810628</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.1783793605133082</v>
+      </c>
+      <c r="W74">
+        <v>0.281396991290578</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.594597868377694</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2902131187720953</v>
+      </c>
+      <c r="C75">
+        <v>-100.2070521716783</v>
+      </c>
+      <c r="D75">
+        <v>49.17794782832166</v>
+      </c>
+      <c r="E75">
+        <v>-0.9350000000000023</v>
+      </c>
+      <c r="F75">
+        <v>153.665</v>
+      </c>
+      <c r="G75">
+        <v>4.28</v>
+      </c>
+      <c r="H75">
+        <v>55.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>4.58</v>
+      </c>
+      <c r="K75">
+        <v>26.1</v>
+      </c>
+      <c r="L75">
+        <v>-21.52</v>
+      </c>
+      <c r="M75">
+        <v>36.695202</v>
+      </c>
+      <c r="N75">
+        <v>-58.21520200000001</v>
+      </c>
+      <c r="O75">
+        <v>-17.4645606</v>
+      </c>
+      <c r="P75">
+        <v>-40.75064140000001</v>
+      </c>
+      <c r="Q75">
+        <v>-14.6506414</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3156269816402928</v>
+      </c>
+      <c r="T75">
+        <v>3.748678976840651</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.1759358076295642</v>
+      </c>
+      <c r="W75">
+        <v>0.28081347086194</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.5864526920985473</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2922131187720953</v>
+      </c>
+      <c r="C76">
+        <v>-102.7001768912399</v>
+      </c>
+      <c r="D76">
+        <v>48.78982310876007</v>
+      </c>
+      <c r="E76">
+        <v>1.170000000000016</v>
+      </c>
+      <c r="F76">
+        <v>155.77</v>
+      </c>
+      <c r="G76">
+        <v>4.28</v>
+      </c>
+      <c r="H76">
+        <v>55.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>4.58</v>
+      </c>
+      <c r="K76">
+        <v>26.1</v>
+      </c>
+      <c r="L76">
+        <v>-21.52</v>
+      </c>
+      <c r="M76">
+        <v>37.197876</v>
+      </c>
+      <c r="N76">
+        <v>-58.717876</v>
+      </c>
+      <c r="O76">
+        <v>-17.6153628</v>
+      </c>
+      <c r="P76">
+        <v>-41.1025132</v>
+      </c>
+      <c r="Q76">
+        <v>-15.0025132</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3262741732418426</v>
+      </c>
+      <c r="T76">
+        <v>3.892858937488368</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.1735582967156512</v>
+      </c>
+      <c r="W76">
+        <v>0.2802457212556975</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.5785276557188372</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2942131187720952</v>
+      </c>
+      <c r="C77">
+        <v>-105.1872232273351</v>
+      </c>
+      <c r="D77">
+        <v>48.40777677266492</v>
+      </c>
+      <c r="E77">
+        <v>3.275000000000006</v>
+      </c>
+      <c r="F77">
+        <v>157.875</v>
+      </c>
+      <c r="G77">
+        <v>4.28</v>
+      </c>
+      <c r="H77">
+        <v>55.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>4.58</v>
+      </c>
+      <c r="K77">
+        <v>26.1</v>
+      </c>
+      <c r="L77">
+        <v>-21.52</v>
+      </c>
+      <c r="M77">
+        <v>37.70055</v>
+      </c>
+      <c r="N77">
+        <v>-59.22055</v>
+      </c>
+      <c r="O77">
+        <v>-17.766165</v>
+      </c>
+      <c r="P77">
+        <v>-41.454385</v>
+      </c>
+      <c r="Q77">
+        <v>-15.354385</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3377731401715163</v>
+      </c>
+      <c r="T77">
+        <v>4.048573294987904</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.1712441860927759</v>
+      </c>
+      <c r="W77">
+        <v>0.2796931116389549</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.5708139536425862</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2962131187720952</v>
+      </c>
+      <c r="C78">
+        <v>-107.6683328600032</v>
+      </c>
+      <c r="D78">
+        <v>48.03166713999678</v>
+      </c>
+      <c r="E78">
+        <v>5.379999999999995</v>
+      </c>
+      <c r="F78">
+        <v>159.98</v>
+      </c>
+      <c r="G78">
+        <v>4.28</v>
+      </c>
+      <c r="H78">
+        <v>55.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>4.58</v>
+      </c>
+      <c r="K78">
+        <v>26.1</v>
+      </c>
+      <c r="L78">
+        <v>-21.52</v>
+      </c>
+      <c r="M78">
+        <v>38.203224</v>
+      </c>
+      <c r="N78">
+        <v>-59.723224</v>
+      </c>
+      <c r="O78">
+        <v>-17.9169672</v>
+      </c>
+      <c r="P78">
+        <v>-41.8062568</v>
+      </c>
+      <c r="Q78">
+        <v>-15.7062568</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3502303543453295</v>
+      </c>
+      <c r="T78">
+        <v>4.217263848945732</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.1689909731178709</v>
+      </c>
+      <c r="W78">
+        <v>0.2791550443805476</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.5633032437262364</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2982131187720952</v>
+      </c>
+      <c r="C79">
+        <v>-110.1436431000354</v>
+      </c>
+      <c r="D79">
+        <v>47.66135689996459</v>
+      </c>
+      <c r="E79">
+        <v>7.485000000000014</v>
+      </c>
+      <c r="F79">
+        <v>162.085</v>
+      </c>
+      <c r="G79">
+        <v>4.28</v>
+      </c>
+      <c r="H79">
+        <v>55.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>4.58</v>
+      </c>
+      <c r="K79">
+        <v>26.1</v>
+      </c>
+      <c r="L79">
+        <v>-21.52</v>
+      </c>
+      <c r="M79">
+        <v>38.705898</v>
+      </c>
+      <c r="N79">
+        <v>-60.22589800000001</v>
+      </c>
+      <c r="O79">
+        <v>-18.0677694</v>
+      </c>
+      <c r="P79">
+        <v>-42.1581286</v>
+      </c>
+      <c r="Q79">
+        <v>-16.0581286</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3637708045342569</v>
+      </c>
+      <c r="T79">
+        <v>4.400623146725982</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.1667962851553011</v>
+      </c>
+      <c r="W79">
+        <v>0.2786309528950859</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.5559876171843372</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3002131187720953</v>
+      </c>
+      <c r="C80">
+        <v>-112.6132870561141</v>
+      </c>
+      <c r="D80">
+        <v>47.29671294388588</v>
+      </c>
+      <c r="E80">
+        <v>9.590000000000003</v>
+      </c>
+      <c r="F80">
+        <v>164.19</v>
+      </c>
+      <c r="G80">
+        <v>4.28</v>
+      </c>
+      <c r="H80">
+        <v>55.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>4.58</v>
+      </c>
+      <c r="K80">
+        <v>26.1</v>
+      </c>
+      <c r="L80">
+        <v>-21.52</v>
+      </c>
+      <c r="M80">
+        <v>39.208572</v>
+      </c>
+      <c r="N80">
+        <v>-60.72857200000001</v>
+      </c>
+      <c r="O80">
+        <v>-18.2185716</v>
+      </c>
+      <c r="P80">
+        <v>-42.51000040000001</v>
+      </c>
+      <c r="Q80">
+        <v>-16.41000040000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3785422047403595</v>
+      </c>
+      <c r="T80">
+        <v>4.600651471577163</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.1646578712430537</v>
+      </c>
+      <c r="W80">
+        <v>0.2781202996528412</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.5488595708101789</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3022131187720953</v>
+      </c>
+      <c r="C81">
+        <v>-115.0773937943385</v>
+      </c>
+      <c r="D81">
+        <v>46.93760620566147</v>
+      </c>
+      <c r="E81">
+        <v>11.69500000000002</v>
+      </c>
+      <c r="F81">
+        <v>166.295</v>
+      </c>
+      <c r="G81">
+        <v>4.28</v>
+      </c>
+      <c r="H81">
+        <v>55.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>4.58</v>
+      </c>
+      <c r="K81">
+        <v>26.1</v>
+      </c>
+      <c r="L81">
+        <v>-21.52</v>
+      </c>
+      <c r="M81">
+        <v>39.711246</v>
+      </c>
+      <c r="N81">
+        <v>-61.23124600000001</v>
+      </c>
+      <c r="O81">
+        <v>-18.3693738</v>
+      </c>
+      <c r="P81">
+        <v>-42.86187220000001</v>
+      </c>
+      <c r="Q81">
+        <v>-16.76187220000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.394720404966091</v>
+      </c>
+      <c r="T81">
+        <v>4.819730113080839</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.1625735943918758</v>
+      </c>
+      <c r="W81">
+        <v>0.27762257434078</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.5419119813062527</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3042131187720952</v>
+      </c>
+      <c r="C82">
+        <v>-117.5360884905375</v>
+      </c>
+      <c r="D82">
+        <v>46.58391150946247</v>
+      </c>
+      <c r="E82">
+        <v>13.80000000000001</v>
+      </c>
+      <c r="F82">
+        <v>168.4</v>
+      </c>
+      <c r="G82">
+        <v>4.28</v>
+      </c>
+      <c r="H82">
+        <v>55.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>4.58</v>
+      </c>
+      <c r="K82">
+        <v>26.1</v>
+      </c>
+      <c r="L82">
+        <v>-21.52</v>
+      </c>
+      <c r="M82">
+        <v>40.21392</v>
+      </c>
+      <c r="N82">
+        <v>-61.73392</v>
+      </c>
+      <c r="O82">
+        <v>-18.520176</v>
+      </c>
+      <c r="P82">
+        <v>-43.21374400000001</v>
+      </c>
+      <c r="Q82">
+        <v>-17.113744</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4125164252143954</v>
+      </c>
+      <c r="T82">
+        <v>5.06071661873488</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.1605414244619774</v>
+      </c>
+      <c r="W82">
+        <v>0.2771372921615202</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.5351380815399245</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3062131187720952</v>
+      </c>
+      <c r="C83">
+        <v>-119.9894925757475</v>
+      </c>
+      <c r="D83">
+        <v>46.23550742425255</v>
+      </c>
+      <c r="E83">
+        <v>15.90500000000003</v>
+      </c>
+      <c r="F83">
+        <v>170.505</v>
+      </c>
+      <c r="G83">
+        <v>4.28</v>
+      </c>
+      <c r="H83">
+        <v>55.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>4.58</v>
+      </c>
+      <c r="K83">
+        <v>26.1</v>
+      </c>
+      <c r="L83">
+        <v>-21.52</v>
+      </c>
+      <c r="M83">
+        <v>40.71659400000001</v>
+      </c>
+      <c r="N83">
+        <v>-62.23659400000001</v>
+      </c>
+      <c r="O83">
+        <v>-18.6709782</v>
+      </c>
+      <c r="P83">
+        <v>-43.5656158</v>
+      </c>
+      <c r="Q83">
+        <v>-17.4656158</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4321857107519952</v>
+      </c>
+      <c r="T83">
+        <v>5.327070124984084</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.158559431567385</v>
+      </c>
+      <c r="W83">
+        <v>0.2766639922582916</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.52853143855795</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3082131187720952</v>
+      </c>
+      <c r="C84">
+        <v>-122.4377238752104</v>
+      </c>
+      <c r="D84">
+        <v>45.89227612478962</v>
+      </c>
+      <c r="E84">
+        <v>18.01000000000002</v>
+      </c>
+      <c r="F84">
+        <v>172.61</v>
+      </c>
+      <c r="G84">
+        <v>4.28</v>
+      </c>
+      <c r="H84">
+        <v>55.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>4.58</v>
+      </c>
+      <c r="K84">
+        <v>26.1</v>
+      </c>
+      <c r="L84">
+        <v>-21.52</v>
+      </c>
+      <c r="M84">
+        <v>41.21926800000001</v>
+      </c>
+      <c r="N84">
+        <v>-62.73926800000001</v>
+      </c>
+      <c r="O84">
+        <v>-18.8217804</v>
+      </c>
+      <c r="P84">
+        <v>-43.91748760000001</v>
+      </c>
+      <c r="Q84">
+        <v>-17.81748760000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4540404724604394</v>
+      </c>
+      <c r="T84">
+        <v>5.623018465260978</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.1566257799629047</v>
+      </c>
+      <c r="W84">
+        <v>0.2762022362551417</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.5220859332096823</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3102131187720952</v>
+      </c>
+      <c r="C85">
+        <v>-124.8808967412267</v>
+      </c>
+      <c r="D85">
+        <v>45.55410325877332</v>
+      </c>
+      <c r="E85">
+        <v>20.11500000000001</v>
+      </c>
+      <c r="F85">
+        <v>174.715</v>
+      </c>
+      <c r="G85">
+        <v>4.28</v>
+      </c>
+      <c r="H85">
+        <v>55.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>4.58</v>
+      </c>
+      <c r="K85">
+        <v>26.1</v>
+      </c>
+      <c r="L85">
+        <v>-21.52</v>
+      </c>
+      <c r="M85">
+        <v>41.72194200000001</v>
+      </c>
+      <c r="N85">
+        <v>-63.24194200000001</v>
+      </c>
+      <c r="O85">
+        <v>-18.9725826</v>
+      </c>
+      <c r="P85">
+        <v>-44.26935940000001</v>
+      </c>
+      <c r="Q85">
+        <v>-18.1693594</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4784663826051712</v>
+      </c>
+      <c r="T85">
+        <v>5.953784257335154</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.1547387223729902</v>
+      </c>
+      <c r="W85">
+        <v>0.27575160690267</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.5157957412433007</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3122131187720952</v>
+      </c>
+      <c r="C86">
+        <v>-127.3191221801767</v>
+      </c>
+      <c r="D86">
+        <v>45.22087781982324</v>
+      </c>
+      <c r="E86">
+        <v>22.22</v>
+      </c>
+      <c r="F86">
+        <v>176.82</v>
+      </c>
+      <c r="G86">
+        <v>4.28</v>
+      </c>
+      <c r="H86">
+        <v>55.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>4.58</v>
+      </c>
+      <c r="K86">
+        <v>26.1</v>
+      </c>
+      <c r="L86">
+        <v>-21.52</v>
+      </c>
+      <c r="M86">
+        <v>42.224616</v>
+      </c>
+      <c r="N86">
+        <v>-63.744616</v>
+      </c>
+      <c r="O86">
+        <v>-19.1233848</v>
+      </c>
+      <c r="P86">
+        <v>-44.6212312</v>
+      </c>
+      <c r="Q86">
+        <v>-18.5212312</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5059455315179942</v>
+      </c>
+      <c r="T86">
+        <v>6.325895773418599</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.1528965947256928</v>
+      </c>
+      <c r="W86">
+        <v>0.2753117068204954</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.5096553157523092</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3142131187720953</v>
+      </c>
+      <c r="C87">
+        <v>-129.7525079740085</v>
+      </c>
+      <c r="D87">
+        <v>44.89249202599149</v>
+      </c>
+      <c r="E87">
+        <v>24.32499999999999</v>
+      </c>
+      <c r="F87">
+        <v>178.925</v>
+      </c>
+      <c r="G87">
+        <v>4.28</v>
+      </c>
+      <c r="H87">
+        <v>55.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>4.58</v>
+      </c>
+      <c r="K87">
+        <v>26.1</v>
+      </c>
+      <c r="L87">
+        <v>-21.52</v>
+      </c>
+      <c r="M87">
+        <v>42.72729</v>
+      </c>
+      <c r="N87">
+        <v>-64.24728999999999</v>
+      </c>
+      <c r="O87">
+        <v>-19.274187</v>
+      </c>
+      <c r="P87">
+        <v>-44.97310299999999</v>
+      </c>
+      <c r="Q87">
+        <v>-18.87310299999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5370885669525272</v>
+      </c>
+      <c r="T87">
+        <v>6.747622158313172</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.1510978112583316</v>
+      </c>
+      <c r="W87">
+        <v>0.2748821573284896</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.5036593708611052</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3162131187720952</v>
+      </c>
+      <c r="C88">
+        <v>-132.1811587964692</v>
+      </c>
+      <c r="D88">
+        <v>44.56884120353079</v>
+      </c>
+      <c r="E88">
+        <v>26.43000000000001</v>
+      </c>
+      <c r="F88">
+        <v>181.03</v>
+      </c>
+      <c r="G88">
+        <v>4.28</v>
+      </c>
+      <c r="H88">
+        <v>55.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>4.58</v>
+      </c>
+      <c r="K88">
+        <v>26.1</v>
+      </c>
+      <c r="L88">
+        <v>-21.52</v>
+      </c>
+      <c r="M88">
+        <v>43.229964</v>
+      </c>
+      <c r="N88">
+        <v>-64.74996400000001</v>
+      </c>
+      <c r="O88">
+        <v>-19.4249892</v>
+      </c>
+      <c r="P88">
+        <v>-45.32497480000001</v>
+      </c>
+      <c r="Q88">
+        <v>-19.22497480000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5726806074491364</v>
+      </c>
+      <c r="T88">
+        <v>7.229595169621256</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.1493408599646301</v>
+      </c>
+      <c r="W88">
+        <v>0.2744625973595537</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.497802866548767</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3182131187720952</v>
+      </c>
+      <c r="C89">
+        <v>-134.6051763243462</v>
+      </c>
+      <c r="D89">
+        <v>44.24982367565383</v>
+      </c>
+      <c r="E89">
+        <v>28.535</v>
+      </c>
+      <c r="F89">
+        <v>183.135</v>
+      </c>
+      <c r="G89">
+        <v>4.28</v>
+      </c>
+      <c r="H89">
+        <v>55.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>4.58</v>
+      </c>
+      <c r="K89">
+        <v>26.1</v>
+      </c>
+      <c r="L89">
+        <v>-21.52</v>
+      </c>
+      <c r="M89">
+        <v>43.732638</v>
+      </c>
+      <c r="N89">
+        <v>-65.252638</v>
+      </c>
+      <c r="O89">
+        <v>-19.5757914</v>
+      </c>
+      <c r="P89">
+        <v>-45.6768466</v>
+      </c>
+      <c r="Q89">
+        <v>-19.5768466</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6137483464836853</v>
+      </c>
+      <c r="T89">
+        <v>7.785717874976736</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.1476242983558413</v>
+      </c>
+      <c r="W89">
+        <v>0.2740526824473749</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.4920809945194708</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3202131187720952</v>
+      </c>
+      <c r="C90">
+        <v>-137.0246593439632</v>
+      </c>
+      <c r="D90">
+        <v>43.93534065603676</v>
+      </c>
+      <c r="E90">
+        <v>30.64000000000001</v>
+      </c>
+      <c r="F90">
+        <v>185.24</v>
+      </c>
+      <c r="G90">
+        <v>4.28</v>
+      </c>
+      <c r="H90">
+        <v>55.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>4.58</v>
+      </c>
+      <c r="K90">
+        <v>26.1</v>
+      </c>
+      <c r="L90">
+        <v>-21.52</v>
+      </c>
+      <c r="M90">
+        <v>44.23531200000001</v>
+      </c>
+      <c r="N90">
+        <v>-65.755312</v>
+      </c>
+      <c r="O90">
+        <v>-19.7265936</v>
+      </c>
+      <c r="P90">
+        <v>-46.0287184</v>
+      </c>
+      <c r="Q90">
+        <v>-19.9287184</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.661660708690659</v>
+      </c>
+      <c r="T90">
+        <v>8.434527697891465</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.1459467495108885</v>
+      </c>
+      <c r="W90">
+        <v>0.2736520837832002</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.4864891650362948</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3222131187720953</v>
+      </c>
+      <c r="C91">
+        <v>-139.4397038531687</v>
+      </c>
+      <c r="D91">
+        <v>43.62529614683133</v>
+      </c>
+      <c r="E91">
+        <v>32.745</v>
+      </c>
+      <c r="F91">
+        <v>187.345</v>
+      </c>
+      <c r="G91">
+        <v>4.28</v>
+      </c>
+      <c r="H91">
+        <v>55.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>4.58</v>
+      </c>
+      <c r="K91">
+        <v>26.1</v>
+      </c>
+      <c r="L91">
+        <v>-21.52</v>
+      </c>
+      <c r="M91">
+        <v>44.737986</v>
+      </c>
+      <c r="N91">
+        <v>-66.257986</v>
+      </c>
+      <c r="O91">
+        <v>-19.8773958</v>
+      </c>
+      <c r="P91">
+        <v>-46.3805902</v>
+      </c>
+      <c r="Q91">
+        <v>-20.2805902</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.718284409480719</v>
+      </c>
+      <c r="T91">
+        <v>9.201302943154326</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.1443068983927887</v>
+      </c>
+      <c r="W91">
+        <v>0.273260487336198</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.4810229946426288</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3242131187720953</v>
+      </c>
+      <c r="C92">
+        <v>-141.8504031590346</v>
+      </c>
+      <c r="D92">
+        <v>43.31959684096537</v>
+      </c>
+      <c r="E92">
+        <v>34.85000000000002</v>
+      </c>
+      <c r="F92">
+        <v>189.45</v>
+      </c>
+      <c r="G92">
+        <v>4.28</v>
+      </c>
+      <c r="H92">
+        <v>55.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>4.58</v>
+      </c>
+      <c r="K92">
+        <v>26.1</v>
+      </c>
+      <c r="L92">
+        <v>-21.52</v>
+      </c>
+      <c r="M92">
+        <v>45.24066000000001</v>
+      </c>
+      <c r="N92">
+        <v>-66.76066</v>
+      </c>
+      <c r="O92">
+        <v>-20.028198</v>
+      </c>
+      <c r="P92">
+        <v>-46.732462</v>
+      </c>
+      <c r="Q92">
+        <v>-20.632462</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7862328504287908</v>
+      </c>
+      <c r="T92">
+        <v>10.12143323746976</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.1427034884106465</v>
+      </c>
+      <c r="W92">
+        <v>0.2728775930324625</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.4756782947021549</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3262131187720952</v>
+      </c>
+      <c r="C93">
+        <v>-144.2568479714777</v>
+      </c>
+      <c r="D93">
+        <v>43.01815202852232</v>
+      </c>
+      <c r="E93">
+        <v>36.95500000000001</v>
+      </c>
+      <c r="F93">
+        <v>191.555</v>
+      </c>
+      <c r="G93">
+        <v>4.28</v>
+      </c>
+      <c r="H93">
+        <v>55.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>4.58</v>
+      </c>
+      <c r="K93">
+        <v>26.1</v>
+      </c>
+      <c r="L93">
+        <v>-21.52</v>
+      </c>
+      <c r="M93">
+        <v>45.743334</v>
+      </c>
+      <c r="N93">
+        <v>-67.26333400000001</v>
+      </c>
+      <c r="O93">
+        <v>-20.1790002</v>
+      </c>
+      <c r="P93">
+        <v>-47.08433380000001</v>
+      </c>
+      <c r="Q93">
+        <v>-20.98433380000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8692809449208789</v>
+      </c>
+      <c r="T93">
+        <v>11.24603693052196</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.1411353182083318</v>
+      </c>
+      <c r="W93">
+        <v>0.2725031139881496</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.4704510606944392</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3282131187720953</v>
+      </c>
+      <c r="C94">
+        <v>-146.6591264929976</v>
+      </c>
+      <c r="D94">
+        <v>42.72087350700238</v>
+      </c>
+      <c r="E94">
+        <v>39.06</v>
+      </c>
+      <c r="F94">
+        <v>193.66</v>
+      </c>
+      <c r="G94">
+        <v>4.28</v>
+      </c>
+      <c r="H94">
+        <v>55.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>4.58</v>
+      </c>
+      <c r="K94">
+        <v>26.1</v>
+      </c>
+      <c r="L94">
+        <v>-21.52</v>
+      </c>
+      <c r="M94">
+        <v>46.246008</v>
+      </c>
+      <c r="N94">
+        <v>-67.766008</v>
+      </c>
+      <c r="O94">
+        <v>-20.3298024</v>
+      </c>
+      <c r="P94">
+        <v>-47.4362056</v>
+      </c>
+      <c r="Q94">
+        <v>-21.3362056</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.973091063035989</v>
+      </c>
+      <c r="T94">
+        <v>12.65179154683721</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.139601238662589</v>
+      </c>
+      <c r="W94">
+        <v>0.2721367757926263</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.4653374622086299</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3302131187720952</v>
+      </c>
+      <c r="C95">
+        <v>-149.0573245047207</v>
+      </c>
+      <c r="D95">
+        <v>42.42767549527927</v>
+      </c>
+      <c r="E95">
+        <v>41.16500000000002</v>
+      </c>
+      <c r="F95">
+        <v>195.765</v>
+      </c>
+      <c r="G95">
+        <v>4.28</v>
+      </c>
+      <c r="H95">
+        <v>55.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>4.58</v>
+      </c>
+      <c r="K95">
+        <v>26.1</v>
+      </c>
+      <c r="L95">
+        <v>-21.52</v>
+      </c>
+      <c r="M95">
+        <v>46.74868200000001</v>
+      </c>
+      <c r="N95">
+        <v>-68.26868200000001</v>
+      </c>
+      <c r="O95">
+        <v>-20.4806046</v>
+      </c>
+      <c r="P95">
+        <v>-47.78807740000001</v>
+      </c>
+      <c r="Q95">
+        <v>-21.6880774</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.106561214898273</v>
+      </c>
+      <c r="T95">
+        <v>14.45919033924252</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.1381001500748192</v>
+      </c>
+      <c r="W95">
+        <v>0.2717783158378668</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.4603338335827307</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3322131187720953</v>
+      </c>
+      <c r="C96">
+        <v>-151.4515254489241</v>
+      </c>
+      <c r="D96">
+        <v>42.13847455107586</v>
+      </c>
+      <c r="E96">
+        <v>43.27000000000001</v>
+      </c>
+      <c r="F96">
+        <v>197.87</v>
+      </c>
+      <c r="G96">
+        <v>4.28</v>
+      </c>
+      <c r="H96">
+        <v>55.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>4.58</v>
+      </c>
+      <c r="K96">
+        <v>26.1</v>
+      </c>
+      <c r="L96">
+        <v>-21.52</v>
+      </c>
+      <c r="M96">
+        <v>47.251356</v>
+      </c>
+      <c r="N96">
+        <v>-68.771356</v>
+      </c>
+      <c r="O96">
+        <v>-20.6314068</v>
+      </c>
+      <c r="P96">
+        <v>-48.1399492</v>
+      </c>
+      <c r="Q96">
+        <v>-22.0399492</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.284521417381319</v>
+      </c>
+      <c r="T96">
+        <v>16.86905539578295</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.1366309995421084</v>
+      </c>
+      <c r="W96">
+        <v>0.2714274826906555</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.4554366651403612</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3342131187720953</v>
+      </c>
+      <c r="C97">
+        <v>-153.8418105082081</v>
+      </c>
+      <c r="D97">
+        <v>41.85318949179192</v>
+      </c>
+      <c r="E97">
+        <v>45.37500000000003</v>
+      </c>
+      <c r="F97">
+        <v>199.975</v>
+      </c>
+      <c r="G97">
+        <v>4.28</v>
+      </c>
+      <c r="H97">
+        <v>55.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>4.58</v>
+      </c>
+      <c r="K97">
+        <v>26.1</v>
+      </c>
+      <c r="L97">
+        <v>-21.52</v>
+      </c>
+      <c r="M97">
+        <v>47.75403000000001</v>
+      </c>
+      <c r="N97">
+        <v>-69.27403000000001</v>
+      </c>
+      <c r="O97">
+        <v>-20.782209</v>
+      </c>
+      <c r="P97">
+        <v>-48.49182100000001</v>
+      </c>
+      <c r="Q97">
+        <v>-22.39182100000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.533665700857584</v>
+      </c>
+      <c r="T97">
+        <v>20.24286647493955</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.1351927784942967</v>
+      </c>
+      <c r="W97">
+        <v>0.2710840355044381</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.4506425949809891</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3362131187720953</v>
+      </c>
+      <c r="C98">
+        <v>-156.2282586814735</v>
+      </c>
+      <c r="D98">
+        <v>41.57174131852648</v>
+      </c>
+      <c r="E98">
+        <v>47.47999999999999</v>
+      </c>
+      <c r="F98">
+        <v>202.08</v>
+      </c>
+      <c r="G98">
+        <v>4.28</v>
+      </c>
+      <c r="H98">
+        <v>55.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>4.58</v>
+      </c>
+      <c r="K98">
+        <v>26.1</v>
+      </c>
+      <c r="L98">
+        <v>-21.52</v>
+      </c>
+      <c r="M98">
+        <v>48.256704</v>
+      </c>
+      <c r="N98">
+        <v>-69.776704</v>
+      </c>
+      <c r="O98">
+        <v>-20.9330112</v>
+      </c>
+      <c r="P98">
+        <v>-48.8436928</v>
+      </c>
+      <c r="Q98">
+        <v>-22.7436928</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.907382126071975</v>
+      </c>
+      <c r="T98">
+        <v>25.30358309367438</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.1337845203849811</v>
+      </c>
+      <c r="W98">
+        <v>0.2707477434679335</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.4459484012832704</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3382131187720953</v>
+      </c>
+      <c r="C99">
+        <v>-158.6109468568548</v>
+      </c>
+      <c r="D99">
+        <v>41.29405314314517</v>
+      </c>
+      <c r="E99">
+        <v>49.58500000000001</v>
+      </c>
+      <c r="F99">
+        <v>204.185</v>
+      </c>
+      <c r="G99">
+        <v>4.28</v>
+      </c>
+      <c r="H99">
+        <v>55.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>4.58</v>
+      </c>
+      <c r="K99">
+        <v>26.1</v>
+      </c>
+      <c r="L99">
+        <v>-21.52</v>
+      </c>
+      <c r="M99">
+        <v>48.75937800000001</v>
+      </c>
+      <c r="N99">
+        <v>-70.27937800000001</v>
+      </c>
+      <c r="O99">
+        <v>-21.0838134</v>
+      </c>
+      <c r="P99">
+        <v>-49.19556460000001</v>
+      </c>
+      <c r="Q99">
+        <v>-23.09556460000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.530242834762634</v>
+      </c>
+      <c r="T99">
+        <v>33.73811079156583</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.1324052985253421</v>
+      </c>
+      <c r="W99">
+        <v>0.2704183852878517</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.4413509950844738</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3402131187720953</v>
+      </c>
+      <c r="C100">
+        <v>-160.9899498817488</v>
+      </c>
+      <c r="D100">
+        <v>41.02005011825117</v>
+      </c>
+      <c r="E100">
+        <v>51.69</v>
+      </c>
+      <c r="F100">
+        <v>206.29</v>
+      </c>
+      <c r="G100">
+        <v>4.28</v>
+      </c>
+      <c r="H100">
+        <v>55.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>4.58</v>
+      </c>
+      <c r="K100">
+        <v>26.1</v>
+      </c>
+      <c r="L100">
+        <v>-21.52</v>
+      </c>
+      <c r="M100">
+        <v>49.262052</v>
+      </c>
+      <c r="N100">
+        <v>-70.78205200000001</v>
+      </c>
+      <c r="O100">
+        <v>-21.2346156</v>
+      </c>
+      <c r="P100">
+        <v>-49.54743640000001</v>
+      </c>
+      <c r="Q100">
+        <v>-23.44743640000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.775964252143951</v>
+      </c>
+      <c r="T100">
+        <v>50.60716618734875</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.1310542240505937</v>
+      </c>
+      <c r="W100">
+        <v>0.2700957487032818</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.4368474135019791</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3422131187720953</v>
+      </c>
+      <c r="C101">
+        <v>-163.3653406300742</v>
+      </c>
+      <c r="D101">
+        <v>40.74965936992584</v>
+      </c>
+      <c r="E101">
+        <v>53.79500000000002</v>
+      </c>
+      <c r="F101">
+        <v>208.395</v>
+      </c>
+      <c r="G101">
+        <v>4.28</v>
+      </c>
+      <c r="H101">
+        <v>55.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>4.58</v>
+      </c>
+      <c r="K101">
+        <v>26.1</v>
+      </c>
+      <c r="L101">
+        <v>-21.52</v>
+      </c>
+      <c r="M101">
+        <v>49.764726</v>
+      </c>
+      <c r="N101">
+        <v>-71.28472600000001</v>
+      </c>
+      <c r="O101">
+        <v>-21.3854178</v>
+      </c>
+      <c r="P101">
+        <v>-49.89930820000001</v>
+      </c>
+      <c r="Q101">
+        <v>-23.79930820000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.513128504287902</v>
+      </c>
+      <c r="T101">
+        <v>101.2143323746975</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.1297304440096787</v>
+      </c>
+      <c r="W101">
+        <v>0.2697796300295113</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.4324348133655955</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_recreation.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_recreation.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1074405949523856</v>
+        <v>0.1071497731675284</v>
       </c>
       <c r="C2">
-        <v>180.9498754153254</v>
+        <v>179.4251262626323</v>
       </c>
       <c r="D2">
-        <v>167.1498754153253</v>
+        <v>167.5841262626323</v>
       </c>
       <c r="E2">
-        <v>-121.7</v>
+        <v>-119.741</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.959</v>
       </c>
       <c r="G2">
         <v>13.8</v>
@@ -1445,28 +1445,28 @@
         <v>13.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09853769999999999</v>
       </c>
       <c r="N2">
-        <v>13.6</v>
+        <v>13.5014623</v>
       </c>
       <c r="O2">
-        <v>4.08</v>
+        <v>4.05043869</v>
       </c>
       <c r="P2">
-        <v>9.520000000000001</v>
+        <v>9.451023610000002</v>
       </c>
       <c r="Q2">
-        <v>30.42</v>
+        <v>30.35102361</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1074405949523856</v>
+        <v>0.107876437542958</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.903287804088733</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>138.0182407342571</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1071497731675284</v>
+        <v>0.1068589513826713</v>
       </c>
       <c r="C3">
-        <v>179.4251262626323</v>
+        <v>177.9026393309984</v>
       </c>
       <c r="D3">
-        <v>167.5841262626323</v>
+        <v>168.0206393309984</v>
       </c>
       <c r="E3">
-        <v>-119.741</v>
+        <v>-117.782</v>
       </c>
       <c r="F3">
-        <v>1.959</v>
+        <v>3.918</v>
       </c>
       <c r="G3">
         <v>13.8</v>
@@ -1527,28 +1527,28 @@
         <v>13.6</v>
       </c>
       <c r="M3">
-        <v>0.09853769999999999</v>
+        <v>0.1970754</v>
       </c>
       <c r="N3">
-        <v>13.5014623</v>
+        <v>13.4029246</v>
       </c>
       <c r="O3">
-        <v>4.05043869</v>
+        <v>4.020877380000001</v>
       </c>
       <c r="P3">
-        <v>9.451023610000002</v>
+        <v>9.38204722</v>
       </c>
       <c r="Q3">
-        <v>30.35102361</v>
+        <v>30.28204722</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.107876437542958</v>
+        <v>0.1083211748802768</v>
       </c>
       <c r="T3">
-        <v>0.903287804088733</v>
+        <v>0.9097592742426858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>138.0182407342571</v>
+        <v>69.00912036712853</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1068589513826713</v>
+        <v>0.1065681295978141</v>
       </c>
       <c r="C4">
-        <v>177.9026393309984</v>
+        <v>176.3824323440818</v>
       </c>
       <c r="D4">
-        <v>168.0206393309984</v>
+        <v>168.4594323440818</v>
       </c>
       <c r="E4">
-        <v>-117.782</v>
+        <v>-115.823</v>
       </c>
       <c r="F4">
-        <v>3.918</v>
+        <v>5.877</v>
       </c>
       <c r="G4">
         <v>13.8</v>
@@ -1609,28 +1609,28 @@
         <v>13.6</v>
       </c>
       <c r="M4">
-        <v>0.1970754</v>
+        <v>0.2956131</v>
       </c>
       <c r="N4">
-        <v>13.4029246</v>
+        <v>13.3043869</v>
       </c>
       <c r="O4">
-        <v>4.020877380000001</v>
+        <v>3.99131607</v>
       </c>
       <c r="P4">
-        <v>9.38204722</v>
+        <v>9.313070830000001</v>
       </c>
       <c r="Q4">
-        <v>30.28204722</v>
+        <v>30.21307083</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1083211748802768</v>
+        <v>0.1087750820596022</v>
       </c>
       <c r="T4">
-        <v>0.9097592742426858</v>
+        <v>0.9163641767709468</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.00912036712853</v>
+        <v>46.00608024475235</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1065681295978141</v>
+        <v>0.106277307812957</v>
       </c>
       <c r="C5">
-        <v>176.3824323440818</v>
+        <v>174.8645232111698</v>
       </c>
       <c r="D5">
-        <v>168.4594323440818</v>
+        <v>168.9005232111698</v>
       </c>
       <c r="E5">
-        <v>-115.823</v>
+        <v>-113.864</v>
       </c>
       <c r="F5">
-        <v>5.877</v>
+        <v>7.836</v>
       </c>
       <c r="G5">
         <v>13.8</v>
@@ -1691,28 +1691,28 @@
         <v>13.6</v>
       </c>
       <c r="M5">
-        <v>0.2956131</v>
+        <v>0.3941508</v>
       </c>
       <c r="N5">
-        <v>13.3043869</v>
+        <v>13.2058492</v>
       </c>
       <c r="O5">
-        <v>3.99131607</v>
+        <v>3.96175476</v>
       </c>
       <c r="P5">
-        <v>9.313070830000001</v>
+        <v>9.244094440000001</v>
       </c>
       <c r="Q5">
-        <v>30.21307083</v>
+        <v>30.14409444</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1087750820596022</v>
+        <v>0.1092384456384968</v>
       </c>
       <c r="T5">
-        <v>0.9163641767709468</v>
+        <v>0.9231066814352133</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.00608024475235</v>
+        <v>34.50456018356427</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.106277307812957</v>
+        <v>0.1059864860280998</v>
       </c>
       <c r="C6">
-        <v>174.8645232111698</v>
+        <v>173.3489300296154</v>
       </c>
       <c r="D6">
-        <v>168.9005232111698</v>
+        <v>169.3439300296154</v>
       </c>
       <c r="E6">
-        <v>-113.864</v>
+        <v>-111.905</v>
       </c>
       <c r="F6">
-        <v>7.836</v>
+        <v>9.795000000000002</v>
       </c>
       <c r="G6">
         <v>13.8</v>
@@ -1773,28 +1773,28 @@
         <v>13.6</v>
       </c>
       <c r="M6">
-        <v>0.3941508</v>
+        <v>0.4926885000000001</v>
       </c>
       <c r="N6">
-        <v>13.2058492</v>
+        <v>13.1073115</v>
       </c>
       <c r="O6">
-        <v>3.96175476</v>
+        <v>3.93219345</v>
       </c>
       <c r="P6">
-        <v>9.244094440000001</v>
+        <v>9.175118050000002</v>
       </c>
       <c r="Q6">
-        <v>30.14409444</v>
+        <v>30.07511805</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1092384456384968</v>
+        <v>0.1097115642401051</v>
       </c>
       <c r="T6">
-        <v>0.9231066814352133</v>
+        <v>0.9299911335660961</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.50456018356427</v>
+        <v>27.60364814685141</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1059864860280998</v>
+        <v>0.1056956642432427</v>
       </c>
       <c r="C7">
-        <v>173.3489300296154</v>
+        <v>171.8356710873126</v>
       </c>
       <c r="D7">
-        <v>169.3439300296154</v>
+        <v>169.7896710873125</v>
       </c>
       <c r="E7">
-        <v>-111.905</v>
+        <v>-109.946</v>
       </c>
       <c r="F7">
-        <v>9.795000000000002</v>
+        <v>11.754</v>
       </c>
       <c r="G7">
         <v>13.8</v>
@@ -1855,28 +1855,28 @@
         <v>13.6</v>
       </c>
       <c r="M7">
-        <v>0.4926885000000001</v>
+        <v>0.5912262</v>
       </c>
       <c r="N7">
-        <v>13.1073115</v>
+        <v>13.0087738</v>
       </c>
       <c r="O7">
-        <v>3.93219345</v>
+        <v>3.902632140000001</v>
       </c>
       <c r="P7">
-        <v>9.175118050000002</v>
+        <v>9.106141660000002</v>
       </c>
       <c r="Q7">
-        <v>30.07511805</v>
+        <v>30.00614166</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1097115642401051</v>
+        <v>0.110194749194939</v>
       </c>
       <c r="T7">
-        <v>0.9299911335660961</v>
+        <v>0.9370220634018912</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.60364814685141</v>
+        <v>23.00304012237618</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1056956642432427</v>
+        <v>0.1054048424583855</v>
       </c>
       <c r="C8">
-        <v>171.8356710873126</v>
+        <v>170.3247648652103</v>
       </c>
       <c r="D8">
-        <v>169.7896710873125</v>
+        <v>170.2377648652103</v>
       </c>
       <c r="E8">
-        <v>-109.946</v>
+        <v>-107.987</v>
       </c>
       <c r="F8">
-        <v>11.754</v>
+        <v>13.713</v>
       </c>
       <c r="G8">
         <v>13.8</v>
@@ -1937,28 +1937,28 @@
         <v>13.6</v>
       </c>
       <c r="M8">
-        <v>0.5912261999999999</v>
+        <v>0.6897638999999999</v>
       </c>
       <c r="N8">
-        <v>13.0087738</v>
+        <v>12.9102361</v>
       </c>
       <c r="O8">
-        <v>3.902632140000001</v>
+        <v>3.873070830000001</v>
       </c>
       <c r="P8">
-        <v>9.106141660000002</v>
+        <v>9.037165270000003</v>
       </c>
       <c r="Q8">
-        <v>30.00614166</v>
+        <v>29.93716527</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.110194749194939</v>
+        <v>0.1106883252240704</v>
       </c>
       <c r="T8">
-        <v>0.9370220634018912</v>
+        <v>0.9442041960298541</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.00304012237618</v>
+        <v>19.7168915334653</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1054048424583855</v>
+        <v>0.1051140206735283</v>
       </c>
       <c r="C9">
-        <v>170.3247648652103</v>
+        <v>168.816230039867</v>
       </c>
       <c r="D9">
-        <v>170.2377648652103</v>
+        <v>170.688230039867</v>
       </c>
       <c r="E9">
-        <v>-107.987</v>
+        <v>-106.028</v>
       </c>
       <c r="F9">
-        <v>13.713</v>
+        <v>15.672</v>
       </c>
       <c r="G9">
         <v>13.8</v>
@@ -2019,28 +2019,28 @@
         <v>13.6</v>
       </c>
       <c r="M9">
-        <v>0.6897639</v>
+        <v>0.7883015999999999</v>
       </c>
       <c r="N9">
-        <v>12.9102361</v>
+        <v>12.8116984</v>
       </c>
       <c r="O9">
-        <v>3.873070830000001</v>
+        <v>3.84350952</v>
       </c>
       <c r="P9">
-        <v>9.037165270000003</v>
+        <v>8.968188880000001</v>
       </c>
       <c r="Q9">
-        <v>29.93716527</v>
+        <v>29.86818888</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1106883252240704</v>
+        <v>0.1111926311668786</v>
       </c>
       <c r="T9">
-        <v>0.9442041960298541</v>
+        <v>0.9515424619758159</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.71689153346529</v>
+        <v>17.25228009178213</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1051140206735283</v>
+        <v>0.1048231988886712</v>
       </c>
       <c r="C10">
-        <v>168.816230039867</v>
+        <v>167.3100854860452</v>
       </c>
       <c r="D10">
-        <v>170.688230039867</v>
+        <v>171.1410854860451</v>
       </c>
       <c r="E10">
-        <v>-106.028</v>
+        <v>-104.069</v>
       </c>
       <c r="F10">
-        <v>15.672</v>
+        <v>17.631</v>
       </c>
       <c r="G10">
         <v>13.8</v>
@@ -2101,28 +2101,28 @@
         <v>13.6</v>
       </c>
       <c r="M10">
-        <v>0.7883015999999999</v>
+        <v>0.8868393</v>
       </c>
       <c r="N10">
-        <v>12.8116984</v>
+        <v>12.7131607</v>
       </c>
       <c r="O10">
-        <v>3.84350952</v>
+        <v>3.81394821</v>
       </c>
       <c r="P10">
-        <v>8.968188880000001</v>
+        <v>8.89921249</v>
       </c>
       <c r="Q10">
-        <v>29.86818888</v>
+        <v>29.79921249</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1111926311668786</v>
+        <v>0.1117080207567815</v>
       </c>
       <c r="T10">
-        <v>0.9515424619758159</v>
+        <v>0.9590420084920187</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.25228009178213</v>
+        <v>15.33536008158412</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1048231988886712</v>
+        <v>0.104532377103814</v>
       </c>
       <c r="C11">
-        <v>167.3100854860452</v>
+        <v>165.8063502793478</v>
       </c>
       <c r="D11">
-        <v>171.1410854860451</v>
+        <v>171.5963502793478</v>
       </c>
       <c r="E11">
-        <v>-104.069</v>
+        <v>-102.11</v>
       </c>
       <c r="F11">
-        <v>17.631</v>
+        <v>19.59</v>
       </c>
       <c r="G11">
         <v>13.8</v>
@@ -2183,28 +2183,28 @@
         <v>13.6</v>
       </c>
       <c r="M11">
-        <v>0.8868393</v>
+        <v>0.9853769999999999</v>
       </c>
       <c r="N11">
-        <v>12.7131607</v>
+        <v>12.614623</v>
       </c>
       <c r="O11">
-        <v>3.81394821</v>
+        <v>3.7843869</v>
       </c>
       <c r="P11">
-        <v>8.89921249</v>
+        <v>8.8302361</v>
       </c>
       <c r="Q11">
-        <v>29.79921249</v>
+        <v>29.7302361</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1117080207567815</v>
+        <v>0.1122348634486822</v>
       </c>
       <c r="T11">
-        <v>0.9590420084920187</v>
+        <v>0.9667082115974704</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.33536008158412</v>
+        <v>13.80182407342571</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.104532377103814</v>
+        <v>0.1043570553189569</v>
       </c>
       <c r="C12">
-        <v>165.8063502793478</v>
+        <v>164.122978580777</v>
       </c>
       <c r="D12">
-        <v>171.5963502793478</v>
+        <v>171.871978580777</v>
       </c>
       <c r="E12">
-        <v>-102.11</v>
+        <v>-100.151</v>
       </c>
       <c r="F12">
-        <v>19.59</v>
+        <v>21.549</v>
       </c>
       <c r="G12">
         <v>13.8</v>
@@ -2265,45 +2265,45 @@
         <v>13.6</v>
       </c>
       <c r="M12">
-        <v>0.9853770000000002</v>
+        <v>1.1162382</v>
       </c>
       <c r="N12">
-        <v>12.614623</v>
+        <v>12.4837618</v>
       </c>
       <c r="O12">
-        <v>3.7843869</v>
+        <v>3.745128540000001</v>
       </c>
       <c r="P12">
-        <v>8.8302361</v>
+        <v>8.73863326</v>
       </c>
       <c r="Q12">
-        <v>29.7302361</v>
+        <v>29.63863326</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1122348634486822</v>
+        <v>0.1127735453021987</v>
       </c>
       <c r="T12">
-        <v>0.9667082115974704</v>
+        <v>0.9745466889300111</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.8018240734257</v>
+        <v>12.18377941195706</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1043570553189569</v>
+        <v>0.1040767335340997</v>
       </c>
       <c r="C13">
-        <v>164.122978580777</v>
+        <v>162.6065247801063</v>
       </c>
       <c r="D13">
-        <v>171.871978580777</v>
+        <v>172.3145247801063</v>
       </c>
       <c r="E13">
-        <v>-100.151</v>
+        <v>-98.19200000000001</v>
       </c>
       <c r="F13">
-        <v>21.549</v>
+        <v>23.508</v>
       </c>
       <c r="G13">
         <v>13.8</v>
@@ -2347,28 +2347,28 @@
         <v>13.6</v>
       </c>
       <c r="M13">
-        <v>1.1162382</v>
+        <v>1.2177144</v>
       </c>
       <c r="N13">
-        <v>12.4837618</v>
+        <v>12.3822856</v>
       </c>
       <c r="O13">
-        <v>3.745128540000001</v>
+        <v>3.71468568</v>
       </c>
       <c r="P13">
-        <v>8.73863326</v>
+        <v>8.667599920000001</v>
       </c>
       <c r="Q13">
-        <v>29.63863326</v>
+        <v>29.56759992</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1127735453021987</v>
+        <v>0.1133244699251133</v>
       </c>
       <c r="T13">
-        <v>0.9745466889300111</v>
+        <v>0.9825633134746549</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.18377941195706</v>
+        <v>11.16846446096063</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1040767335340997</v>
+        <v>0.1037964117492425</v>
       </c>
       <c r="C14">
-        <v>162.6065247801063</v>
+        <v>161.0923558512433</v>
       </c>
       <c r="D14">
-        <v>172.3145247801063</v>
+        <v>172.7593558512433</v>
       </c>
       <c r="E14">
-        <v>-98.19200000000001</v>
+        <v>-96.233</v>
       </c>
       <c r="F14">
-        <v>23.508</v>
+        <v>25.467</v>
       </c>
       <c r="G14">
         <v>13.8</v>
@@ -2429,28 +2429,28 @@
         <v>13.6</v>
       </c>
       <c r="M14">
-        <v>1.2177144</v>
+        <v>1.3191906</v>
       </c>
       <c r="N14">
-        <v>12.3822856</v>
+        <v>12.2808094</v>
       </c>
       <c r="O14">
-        <v>3.71468568</v>
+        <v>3.68424282</v>
       </c>
       <c r="P14">
-        <v>8.667599920000001</v>
+        <v>8.596566580000001</v>
       </c>
       <c r="Q14">
-        <v>29.56759992</v>
+        <v>29.49656658</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1133244699251133</v>
+        <v>0.113888059481888</v>
       </c>
       <c r="T14">
-        <v>0.9825633134746549</v>
+        <v>0.9907642282387158</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.16846446096063</v>
+        <v>10.30935181011751</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1037964117492425</v>
+        <v>0.1036826899643854</v>
       </c>
       <c r="C15">
-        <v>161.0923558512433</v>
+        <v>159.3144717958022</v>
       </c>
       <c r="D15">
-        <v>172.7593558512433</v>
+        <v>172.9404717958022</v>
       </c>
       <c r="E15">
-        <v>-96.233</v>
+        <v>-94.274</v>
       </c>
       <c r="F15">
-        <v>25.467</v>
+        <v>27.426</v>
       </c>
       <c r="G15">
         <v>13.8</v>
@@ -2511,45 +2511,45 @@
         <v>13.6</v>
       </c>
       <c r="M15">
-        <v>1.3191906</v>
+        <v>1.467291</v>
       </c>
       <c r="N15">
-        <v>12.2808094</v>
+        <v>12.132709</v>
       </c>
       <c r="O15">
-        <v>3.68424282</v>
+        <v>3.6398127</v>
       </c>
       <c r="P15">
-        <v>8.596566580000001</v>
+        <v>8.492896300000002</v>
       </c>
       <c r="Q15">
-        <v>29.49656658</v>
+        <v>29.3928963</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.113888059481888</v>
+        <v>0.1144647557725412</v>
       </c>
       <c r="T15">
-        <v>0.9907642282387158</v>
+        <v>0.999155861950778</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.30935181011751</v>
+        <v>9.268781720872003</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1036826899643854</v>
+        <v>0.1034142681795282</v>
       </c>
       <c r="C16">
-        <v>159.3144717958022</v>
+        <v>157.7844762871217</v>
       </c>
       <c r="D16">
-        <v>172.9404717958022</v>
+        <v>173.3694762871217</v>
       </c>
       <c r="E16">
-        <v>-94.274</v>
+        <v>-92.315</v>
       </c>
       <c r="F16">
-        <v>27.426</v>
+        <v>29.38500000000001</v>
       </c>
       <c r="G16">
         <v>13.8</v>
@@ -2593,28 +2593,28 @@
         <v>13.6</v>
       </c>
       <c r="M16">
-        <v>1.467291</v>
+        <v>1.5720975</v>
       </c>
       <c r="N16">
-        <v>12.132709</v>
+        <v>12.0279025</v>
       </c>
       <c r="O16">
-        <v>3.6398127</v>
+        <v>3.60837075</v>
       </c>
       <c r="P16">
-        <v>8.492896300000002</v>
+        <v>8.419531750000001</v>
       </c>
       <c r="Q16">
-        <v>29.3928963</v>
+        <v>29.31953175</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1144647557725412</v>
+        <v>0.1150550213876803</v>
       </c>
       <c r="T16">
-        <v>0.999155861950778</v>
+        <v>1.00774494586783</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.268781720872003</v>
+        <v>8.650862939480536</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1034142681795282</v>
+        <v>0.1031458463946711</v>
       </c>
       <c r="C17">
-        <v>157.7844762871217</v>
+        <v>156.2566144899729</v>
       </c>
       <c r="D17">
-        <v>173.3694762871217</v>
+        <v>173.8006144899729</v>
       </c>
       <c r="E17">
-        <v>-92.315</v>
+        <v>-90.35599999999999</v>
       </c>
       <c r="F17">
-        <v>29.385</v>
+        <v>31.344</v>
       </c>
       <c r="G17">
         <v>13.8</v>
@@ -2675,28 +2675,28 @@
         <v>13.6</v>
       </c>
       <c r="M17">
-        <v>1.5720975</v>
+        <v>1.676904</v>
       </c>
       <c r="N17">
-        <v>12.0279025</v>
+        <v>11.923096</v>
       </c>
       <c r="O17">
-        <v>3.60837075</v>
+        <v>3.5769288</v>
       </c>
       <c r="P17">
-        <v>8.419531750000001</v>
+        <v>8.3461672</v>
       </c>
       <c r="Q17">
-        <v>29.31953175</v>
+        <v>29.2461672</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1150550213876803</v>
+        <v>0.115659340946037</v>
       </c>
       <c r="T17">
-        <v>1.00774494586783</v>
+        <v>1.016538531782907</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.650862939480536</v>
+        <v>8.110184005763003</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1031458463946711</v>
+        <v>0.1028774246098139</v>
       </c>
       <c r="C18">
-        <v>156.2566144899729</v>
+        <v>154.7309023624928</v>
       </c>
       <c r="D18">
-        <v>173.8006144899729</v>
+        <v>174.2339023624928</v>
       </c>
       <c r="E18">
-        <v>-90.35599999999999</v>
+        <v>-88.39699999999999</v>
       </c>
       <c r="F18">
-        <v>31.344</v>
+        <v>33.303</v>
       </c>
       <c r="G18">
         <v>13.8</v>
@@ -2757,28 +2757,28 @@
         <v>13.6</v>
       </c>
       <c r="M18">
-        <v>1.676904</v>
+        <v>1.7817105</v>
       </c>
       <c r="N18">
-        <v>11.923096</v>
+        <v>11.8182895</v>
       </c>
       <c r="O18">
-        <v>3.5769288</v>
+        <v>3.54548685</v>
       </c>
       <c r="P18">
-        <v>8.3461672</v>
+        <v>8.272802650000001</v>
       </c>
       <c r="Q18">
-        <v>29.2461672</v>
+        <v>29.17280265</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.115659340946037</v>
+        <v>0.1162782224214626</v>
       </c>
       <c r="T18">
-        <v>1.016538531782907</v>
+        <v>1.025544011334492</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.110184005763003</v>
+        <v>7.633114358365177</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1028774246098139</v>
+        <v>0.1027098028249568</v>
       </c>
       <c r="C19">
-        <v>154.7309023624928</v>
+        <v>153.0435758357031</v>
       </c>
       <c r="D19">
-        <v>174.2339023624928</v>
+        <v>174.5055758357031</v>
       </c>
       <c r="E19">
-        <v>-88.39699999999999</v>
+        <v>-86.43799999999999</v>
       </c>
       <c r="F19">
-        <v>33.303</v>
+        <v>35.26200000000001</v>
       </c>
       <c r="G19">
         <v>13.8</v>
@@ -2839,45 +2839,45 @@
         <v>13.6</v>
       </c>
       <c r="M19">
-        <v>1.7817105</v>
+        <v>1.914726600000001</v>
       </c>
       <c r="N19">
-        <v>11.8182895</v>
+        <v>11.6852734</v>
       </c>
       <c r="O19">
-        <v>3.54548685</v>
+        <v>3.50558202</v>
       </c>
       <c r="P19">
-        <v>8.272802650000001</v>
+        <v>8.179691380000001</v>
       </c>
       <c r="Q19">
-        <v>29.17280265</v>
+        <v>29.07969138</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1162782224214626</v>
+        <v>0.1169121985670205</v>
       </c>
       <c r="T19">
-        <v>1.025544011334492</v>
+        <v>1.034769136728799</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.633114358365177</v>
+        <v>7.102841732078093</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1027098028249568</v>
+        <v>0.1024469810400996</v>
       </c>
       <c r="C20">
-        <v>153.0435758357031</v>
+        <v>151.5122547583755</v>
       </c>
       <c r="D20">
-        <v>174.5055758357031</v>
+        <v>174.9332547583755</v>
       </c>
       <c r="E20">
-        <v>-86.438</v>
+        <v>-84.479</v>
       </c>
       <c r="F20">
-        <v>35.262</v>
+        <v>37.221</v>
       </c>
       <c r="G20">
         <v>13.8</v>
@@ -2921,28 +2921,28 @@
         <v>13.6</v>
       </c>
       <c r="M20">
-        <v>1.9147266</v>
+        <v>2.0211003</v>
       </c>
       <c r="N20">
-        <v>11.6852734</v>
+        <v>11.5788997</v>
       </c>
       <c r="O20">
-        <v>3.50558202</v>
+        <v>3.47366991</v>
       </c>
       <c r="P20">
-        <v>8.179691380000001</v>
+        <v>8.105229790000001</v>
       </c>
       <c r="Q20">
-        <v>29.07969138</v>
+        <v>29.00522979</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1169121985670205</v>
+        <v>0.1175618284445674</v>
       </c>
       <c r="T20">
-        <v>1.034769136728799</v>
+        <v>1.044222042997039</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.102841732078095</v>
+        <v>6.729007956705563</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1024469810400996</v>
+        <v>0.1021841592552425</v>
       </c>
       <c r="C21">
-        <v>151.5122547583755</v>
+        <v>149.9830351455548</v>
       </c>
       <c r="D21">
-        <v>174.9332547583755</v>
+        <v>175.3630351455548</v>
       </c>
       <c r="E21">
-        <v>-84.479</v>
+        <v>-82.52</v>
       </c>
       <c r="F21">
-        <v>37.221</v>
+        <v>39.18000000000001</v>
       </c>
       <c r="G21">
         <v>13.8</v>
@@ -3003,28 +3003,28 @@
         <v>13.6</v>
       </c>
       <c r="M21">
-        <v>2.0211003</v>
+        <v>2.127474</v>
       </c>
       <c r="N21">
-        <v>11.5788997</v>
+        <v>11.472526</v>
       </c>
       <c r="O21">
-        <v>3.47366991</v>
+        <v>3.4417578</v>
       </c>
       <c r="P21">
-        <v>8.105229790000001</v>
+        <v>8.030768200000001</v>
       </c>
       <c r="Q21">
-        <v>29.00522979</v>
+        <v>28.9307682</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1175618284445674</v>
+        <v>0.1182276990690531</v>
       </c>
       <c r="T21">
-        <v>1.044222042997039</v>
+        <v>1.053911271921985</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.729007956705563</v>
+        <v>6.392557558870285</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1021841592552425</v>
+        <v>0.1020683374703853</v>
       </c>
       <c r="C22">
-        <v>149.9830351455548</v>
+        <v>148.2141042912282</v>
       </c>
       <c r="D22">
-        <v>175.3630351455548</v>
+        <v>175.5531042912282</v>
       </c>
       <c r="E22">
-        <v>-82.52</v>
+        <v>-80.56100000000001</v>
       </c>
       <c r="F22">
-        <v>39.18000000000001</v>
+        <v>41.139</v>
       </c>
       <c r="G22">
         <v>13.8</v>
@@ -3085,45 +3085,45 @@
         <v>13.6</v>
       </c>
       <c r="M22">
-        <v>2.127474</v>
+        <v>2.2749867</v>
       </c>
       <c r="N22">
-        <v>11.472526</v>
+        <v>11.3250133</v>
       </c>
       <c r="O22">
-        <v>3.4417578</v>
+        <v>3.397503990000001</v>
       </c>
       <c r="P22">
-        <v>8.030768200000001</v>
+        <v>7.927509310000001</v>
       </c>
       <c r="Q22">
-        <v>28.9307682</v>
+        <v>28.82750931</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1182276990690531</v>
+        <v>0.1189104271777029</v>
       </c>
       <c r="T22">
-        <v>1.053911271921985</v>
+        <v>1.063845797781739</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.392557558870285</v>
+        <v>5.978056926662473</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1020683374703853</v>
+        <v>0.1018125156855282</v>
       </c>
       <c r="C23">
-        <v>148.2141042912282</v>
+        <v>146.676383759402</v>
       </c>
       <c r="D23">
-        <v>175.5531042912282</v>
+        <v>175.974383759402</v>
       </c>
       <c r="E23">
-        <v>-80.56100000000001</v>
+        <v>-78.602</v>
       </c>
       <c r="F23">
-        <v>41.139</v>
+        <v>43.098</v>
       </c>
       <c r="G23">
         <v>13.8</v>
@@ -3167,28 +3167,28 @@
         <v>13.6</v>
       </c>
       <c r="M23">
-        <v>2.2749867</v>
+        <v>2.3833194</v>
       </c>
       <c r="N23">
-        <v>11.3250133</v>
+        <v>11.2166806</v>
       </c>
       <c r="O23">
-        <v>3.397503990000001</v>
+        <v>3.365004180000001</v>
       </c>
       <c r="P23">
-        <v>7.927509310000001</v>
+        <v>7.851676420000001</v>
       </c>
       <c r="Q23">
-        <v>28.82750931</v>
+        <v>28.75167642</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1189104271777029</v>
+        <v>0.1196106611352925</v>
       </c>
       <c r="T23">
-        <v>1.063845797781739</v>
+        <v>1.074035055073796</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.978056926662473</v>
+        <v>5.706327066359633</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1018125156855282</v>
+        <v>0.101556693900671</v>
       </c>
       <c r="C24">
-        <v>146.676383759402</v>
+        <v>145.1406900024409</v>
       </c>
       <c r="D24">
-        <v>175.974383759402</v>
+        <v>176.3976900024409</v>
       </c>
       <c r="E24">
-        <v>-78.602</v>
+        <v>-76.643</v>
       </c>
       <c r="F24">
-        <v>43.098</v>
+        <v>45.057</v>
       </c>
       <c r="G24">
         <v>13.8</v>
@@ -3249,28 +3249,28 @@
         <v>13.6</v>
       </c>
       <c r="M24">
-        <v>2.3833194</v>
+        <v>2.4916521</v>
       </c>
       <c r="N24">
-        <v>11.2166806</v>
+        <v>11.1083479</v>
       </c>
       <c r="O24">
-        <v>3.365004180000001</v>
+        <v>3.332504370000001</v>
       </c>
       <c r="P24">
-        <v>7.851676420000001</v>
+        <v>7.775843530000001</v>
       </c>
       <c r="Q24">
-        <v>28.75167642</v>
+        <v>28.67584353</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1196106611352925</v>
+        <v>0.1203290829878844</v>
       </c>
       <c r="T24">
-        <v>1.074035055073796</v>
+        <v>1.084488968399411</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.706327066359633</v>
+        <v>5.458225889561389</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.101556693900671</v>
+        <v>0.1013008721158138</v>
       </c>
       <c r="C25">
-        <v>145.1406900024409</v>
+        <v>143.607037681829</v>
       </c>
       <c r="D25">
-        <v>176.3976900024409</v>
+        <v>176.8230376818289</v>
       </c>
       <c r="E25">
-        <v>-76.643</v>
+        <v>-74.684</v>
       </c>
       <c r="F25">
-        <v>45.057</v>
+        <v>47.01600000000001</v>
       </c>
       <c r="G25">
         <v>13.8</v>
@@ -3331,28 +3331,28 @@
         <v>13.6</v>
       </c>
       <c r="M25">
-        <v>2.4916521</v>
+        <v>2.599984800000001</v>
       </c>
       <c r="N25">
-        <v>11.1083479</v>
+        <v>11.0000152</v>
       </c>
       <c r="O25">
-        <v>3.332504370000001</v>
+        <v>3.30000456</v>
       </c>
       <c r="P25">
-        <v>7.775843530000001</v>
+        <v>7.70001064</v>
       </c>
       <c r="Q25">
-        <v>28.67584353</v>
+        <v>28.60001064</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1203290829878844</v>
+        <v>0.1210664106787024</v>
       </c>
       <c r="T25">
-        <v>1.084488968399411</v>
+        <v>1.095217984707281</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.458225889561389</v>
+        <v>5.230799810829662</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1013008721158138</v>
+        <v>0.1010450503309567</v>
       </c>
       <c r="C26">
-        <v>143.607037681829</v>
+        <v>142.0754416008053</v>
       </c>
       <c r="D26">
-        <v>176.8230376818289</v>
+        <v>177.2504416008053</v>
       </c>
       <c r="E26">
-        <v>-74.684</v>
+        <v>-72.72499999999999</v>
       </c>
       <c r="F26">
-        <v>47.016</v>
+        <v>48.975</v>
       </c>
       <c r="G26">
         <v>13.8</v>
@@ -3413,28 +3413,28 @@
         <v>13.6</v>
       </c>
       <c r="M26">
-        <v>2.5999848</v>
+        <v>2.7083175</v>
       </c>
       <c r="N26">
-        <v>11.0000152</v>
+        <v>10.8916825</v>
       </c>
       <c r="O26">
-        <v>3.300004560000001</v>
+        <v>3.267504750000001</v>
       </c>
       <c r="P26">
-        <v>7.700010640000001</v>
+        <v>7.624177750000001</v>
       </c>
       <c r="Q26">
-        <v>28.60001064</v>
+        <v>28.52417775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1210664106787024</v>
+        <v>0.1218234004412756</v>
       </c>
       <c r="T26">
-        <v>1.095217984707281</v>
+        <v>1.106233108116693</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.230799810829664</v>
+        <v>5.021567818396477</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1010450503309567</v>
+        <v>0.1007892285460995</v>
       </c>
       <c r="C27">
-        <v>142.0754416008053</v>
+        <v>140.545916706081</v>
       </c>
       <c r="D27">
-        <v>177.2504416008053</v>
+        <v>177.679916706081</v>
       </c>
       <c r="E27">
-        <v>-72.72499999999999</v>
+        <v>-70.76599999999999</v>
       </c>
       <c r="F27">
-        <v>48.975</v>
+        <v>50.934</v>
       </c>
       <c r="G27">
         <v>13.8</v>
@@ -3495,28 +3495,28 @@
         <v>13.6</v>
       </c>
       <c r="M27">
-        <v>2.7083175</v>
+        <v>2.8166502</v>
       </c>
       <c r="N27">
-        <v>10.8916825</v>
+        <v>10.7833498</v>
       </c>
       <c r="O27">
-        <v>3.267504750000001</v>
+        <v>3.23500494</v>
       </c>
       <c r="P27">
-        <v>7.624177750000001</v>
+        <v>7.548344860000001</v>
       </c>
       <c r="Q27">
-        <v>28.52417775</v>
+        <v>28.44834486</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1218234004412756</v>
+        <v>0.122600849386621</v>
       </c>
       <c r="T27">
-        <v>1.106233108116693</v>
+        <v>1.117545937564198</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.021567818396477</v>
+        <v>4.828430594611998</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1007892285460995</v>
+        <v>0.1005334067612424</v>
       </c>
       <c r="C28">
-        <v>140.545916706081</v>
+        <v>139.0184780895815</v>
       </c>
       <c r="D28">
-        <v>177.679916706081</v>
+        <v>178.1114780895815</v>
       </c>
       <c r="E28">
-        <v>-70.76599999999999</v>
+        <v>-68.80699999999999</v>
       </c>
       <c r="F28">
-        <v>50.934</v>
+        <v>52.89300000000001</v>
       </c>
       <c r="G28">
         <v>13.8</v>
@@ -3577,28 +3577,28 @@
         <v>13.6</v>
       </c>
       <c r="M28">
-        <v>2.8166502</v>
+        <v>2.924982900000001</v>
       </c>
       <c r="N28">
-        <v>10.7833498</v>
+        <v>10.6750171</v>
       </c>
       <c r="O28">
-        <v>3.23500494</v>
+        <v>3.20250513</v>
       </c>
       <c r="P28">
-        <v>7.548344860000001</v>
+        <v>7.472511970000001</v>
       </c>
       <c r="Q28">
-        <v>28.44834486</v>
+        <v>28.37251197</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.122600849386621</v>
+        <v>0.1233995983030717</v>
       </c>
       <c r="T28">
-        <v>1.117545937564198</v>
+        <v>1.12916870754451</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.828430594611998</v>
+        <v>4.649599831848589</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1005334067612424</v>
+        <v>0.1007675849763852</v>
       </c>
       <c r="C29">
-        <v>139.0184780895815</v>
+        <v>136.6643475653413</v>
       </c>
       <c r="D29">
-        <v>178.1114780895815</v>
+        <v>177.7163475653413</v>
       </c>
       <c r="E29">
-        <v>-68.80699999999999</v>
+        <v>-66.848</v>
       </c>
       <c r="F29">
-        <v>52.89300000000001</v>
+        <v>54.852</v>
       </c>
       <c r="G29">
         <v>13.8</v>
@@ -3659,45 +3659,45 @@
         <v>13.6</v>
       </c>
       <c r="M29">
-        <v>2.924982900000001</v>
+        <v>3.1704456</v>
       </c>
       <c r="N29">
-        <v>10.6750171</v>
+        <v>10.4295544</v>
       </c>
       <c r="O29">
-        <v>3.20250513</v>
+        <v>3.12886632</v>
       </c>
       <c r="P29">
-        <v>7.472511970000001</v>
+        <v>7.30068808</v>
       </c>
       <c r="Q29">
-        <v>28.37251197</v>
+        <v>28.20068808</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1233995983030717</v>
+        <v>0.1242205346894239</v>
       </c>
       <c r="T29">
-        <v>1.12916870754451</v>
+        <v>1.141114332246499</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.649599831848589</v>
+        <v>4.289617837946818</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1007675849763852</v>
+        <v>0.1005292631915281</v>
       </c>
       <c r="C30">
-        <v>136.6643475653413</v>
+        <v>135.1074853838142</v>
       </c>
       <c r="D30">
-        <v>177.7163475653413</v>
+        <v>178.1184853838142</v>
       </c>
       <c r="E30">
-        <v>-66.848</v>
+        <v>-64.889</v>
       </c>
       <c r="F30">
-        <v>54.852</v>
+        <v>56.81100000000001</v>
       </c>
       <c r="G30">
         <v>13.8</v>
@@ -3741,28 +3741,28 @@
         <v>13.6</v>
       </c>
       <c r="M30">
-        <v>3.1704456</v>
+        <v>3.283675800000001</v>
       </c>
       <c r="N30">
-        <v>10.4295544</v>
+        <v>10.3163242</v>
       </c>
       <c r="O30">
-        <v>3.12886632</v>
+        <v>3.09489726</v>
       </c>
       <c r="P30">
-        <v>7.30068808</v>
+        <v>7.221426940000001</v>
       </c>
       <c r="Q30">
-        <v>28.20068808</v>
+        <v>28.12142694</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1242205346894239</v>
+        <v>0.1250645960444057</v>
       </c>
       <c r="T30">
-        <v>1.141114332246499</v>
+        <v>1.153396453418966</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.289617837946818</v>
+        <v>4.141699981465893</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1005292631915281</v>
+        <v>0.1002909414066709</v>
       </c>
       <c r="C31">
-        <v>135.1074853838142</v>
+        <v>133.5524472504024</v>
       </c>
       <c r="D31">
-        <v>178.1184853838142</v>
+        <v>178.5224472504024</v>
       </c>
       <c r="E31">
-        <v>-64.88900000000001</v>
+        <v>-62.93000000000001</v>
       </c>
       <c r="F31">
-        <v>56.811</v>
+        <v>58.77</v>
       </c>
       <c r="G31">
         <v>13.8</v>
@@ -3823,28 +3823,28 @@
         <v>13.6</v>
       </c>
       <c r="M31">
-        <v>3.2836758</v>
+        <v>3.396906</v>
       </c>
       <c r="N31">
-        <v>10.3163242</v>
+        <v>10.203094</v>
       </c>
       <c r="O31">
-        <v>3.09489726</v>
+        <v>3.060928200000001</v>
       </c>
       <c r="P31">
-        <v>7.221426940000001</v>
+        <v>7.142165800000001</v>
       </c>
       <c r="Q31">
-        <v>28.12142694</v>
+        <v>28.0421658</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1250645960444057</v>
+        <v>0.1259327734381013</v>
       </c>
       <c r="T31">
-        <v>1.153396453418966</v>
+        <v>1.166029492339217</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.141699981465893</v>
+        <v>4.00364331541703</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1002909414066709</v>
+        <v>0.1008121196218137</v>
       </c>
       <c r="C32">
-        <v>133.5524472504024</v>
+        <v>130.7124022704003</v>
       </c>
       <c r="D32">
-        <v>178.5224472504024</v>
+        <v>177.6414022704003</v>
       </c>
       <c r="E32">
-        <v>-62.93000000000001</v>
+        <v>-60.971</v>
       </c>
       <c r="F32">
-        <v>58.77</v>
+        <v>60.729</v>
       </c>
       <c r="G32">
         <v>13.8</v>
@@ -3905,45 +3905,45 @@
         <v>13.6</v>
       </c>
       <c r="M32">
-        <v>3.396906</v>
+        <v>3.7226877</v>
       </c>
       <c r="N32">
-        <v>10.203094</v>
+        <v>9.877312300000002</v>
       </c>
       <c r="O32">
-        <v>3.060928200000001</v>
+        <v>2.96319369</v>
       </c>
       <c r="P32">
-        <v>7.142165800000001</v>
+        <v>6.914118610000001</v>
       </c>
       <c r="Q32">
-        <v>28.0421658</v>
+        <v>27.81411861</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1259327734381013</v>
+        <v>0.126826115393933</v>
       </c>
       <c r="T32">
-        <v>1.166029492339217</v>
+        <v>1.179028706300635</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.00364331541703</v>
+        <v>3.653274487677277</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1008121196218137</v>
+        <v>0.1005982978369566</v>
       </c>
       <c r="C33">
-        <v>130.7124022704003</v>
+        <v>129.1138110538703</v>
       </c>
       <c r="D33">
-        <v>177.6414022704003</v>
+        <v>178.0018110538703</v>
       </c>
       <c r="E33">
-        <v>-60.971</v>
+        <v>-59.012</v>
       </c>
       <c r="F33">
-        <v>60.729</v>
+        <v>62.688</v>
       </c>
       <c r="G33">
         <v>13.8</v>
@@ -3987,28 +3987,28 @@
         <v>13.6</v>
       </c>
       <c r="M33">
-        <v>3.7226877</v>
+        <v>3.8427744</v>
       </c>
       <c r="N33">
-        <v>9.877312300000002</v>
+        <v>9.757225600000002</v>
       </c>
       <c r="O33">
-        <v>2.96319369</v>
+        <v>2.927167680000001</v>
       </c>
       <c r="P33">
-        <v>6.914118610000001</v>
+        <v>6.830057920000002</v>
       </c>
       <c r="Q33">
-        <v>27.81411861</v>
+        <v>27.73005792</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.126826115393933</v>
+        <v>0.1277457321131714</v>
       </c>
       <c r="T33">
-        <v>1.179028706300635</v>
+        <v>1.192410250084448</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.653274487677277</v>
+        <v>3.539109659937362</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1005982978369566</v>
+        <v>0.1010312760520994</v>
       </c>
       <c r="C34">
-        <v>129.1138110538703</v>
+        <v>126.4265130486995</v>
       </c>
       <c r="D34">
-        <v>178.0018110538703</v>
+        <v>177.2735130486995</v>
       </c>
       <c r="E34">
-        <v>-59.012</v>
+        <v>-57.053</v>
       </c>
       <c r="F34">
-        <v>62.688</v>
+        <v>64.64700000000001</v>
       </c>
       <c r="G34">
         <v>13.8</v>
@@ -4069,45 +4069,45 @@
         <v>13.6</v>
       </c>
       <c r="M34">
-        <v>3.8427744</v>
+        <v>4.1438727</v>
       </c>
       <c r="N34">
-        <v>9.757225600000002</v>
+        <v>9.456127300000002</v>
       </c>
       <c r="O34">
-        <v>2.927167680000001</v>
+        <v>2.83683819</v>
       </c>
       <c r="P34">
-        <v>6.830057920000002</v>
+        <v>6.619289110000002</v>
       </c>
       <c r="Q34">
-        <v>27.73005792</v>
+        <v>27.51928911</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1277457321131714</v>
+        <v>0.1286928000777603</v>
       </c>
       <c r="T34">
-        <v>1.192410250084448</v>
+        <v>1.206191242936435</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.539109659937362</v>
+        <v>3.281954100568775</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1010312760520994</v>
+        <v>0.1008370542672423</v>
       </c>
       <c r="C35">
-        <v>126.4265130486995</v>
+        <v>124.7934685057161</v>
       </c>
       <c r="D35">
-        <v>177.2735130486995</v>
+        <v>177.5994685057161</v>
       </c>
       <c r="E35">
-        <v>-57.053</v>
+        <v>-55.09399999999999</v>
       </c>
       <c r="F35">
-        <v>64.64700000000001</v>
+        <v>66.60600000000001</v>
       </c>
       <c r="G35">
         <v>13.8</v>
@@ -4151,28 +4151,28 @@
         <v>13.6</v>
       </c>
       <c r="M35">
-        <v>4.1438727</v>
+        <v>4.269444600000001</v>
       </c>
       <c r="N35">
-        <v>9.456127300000002</v>
+        <v>9.330555400000001</v>
       </c>
       <c r="O35">
-        <v>2.83683819</v>
+        <v>2.79916662</v>
       </c>
       <c r="P35">
-        <v>6.619289110000002</v>
+        <v>6.531388780000001</v>
       </c>
       <c r="Q35">
-        <v>27.51928911</v>
+        <v>27.43138878</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1286928000777603</v>
+        <v>0.1296685670715792</v>
       </c>
       <c r="T35">
-        <v>1.206191242936435</v>
+        <v>1.220389841632421</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.281954100568775</v>
+        <v>3.18542603878734</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1008370542672423</v>
+        <v>0.1006428324823851</v>
       </c>
       <c r="C36">
-        <v>124.7934685057161</v>
+        <v>123.1616248491581</v>
       </c>
       <c r="D36">
-        <v>177.5994685057161</v>
+        <v>177.9266248491581</v>
       </c>
       <c r="E36">
-        <v>-55.09399999999999</v>
+        <v>-53.13499999999999</v>
       </c>
       <c r="F36">
-        <v>66.60600000000001</v>
+        <v>68.56500000000001</v>
       </c>
       <c r="G36">
         <v>13.8</v>
@@ -4233,28 +4233,28 @@
         <v>13.6</v>
       </c>
       <c r="M36">
-        <v>4.269444600000001</v>
+        <v>4.395016500000001</v>
       </c>
       <c r="N36">
-        <v>9.330555400000001</v>
+        <v>9.204983500000001</v>
       </c>
       <c r="O36">
-        <v>2.79916662</v>
+        <v>2.76149505</v>
       </c>
       <c r="P36">
-        <v>6.531388780000001</v>
+        <v>6.44348845</v>
       </c>
       <c r="Q36">
-        <v>27.43138878</v>
+        <v>27.34348845</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1296685670715792</v>
+        <v>0.1306743576652079</v>
       </c>
       <c r="T36">
-        <v>1.220389841632421</v>
+        <v>1.235025320288283</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.18542603878734</v>
+        <v>3.094413866250559</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1006428324823851</v>
+        <v>0.100448610697528</v>
       </c>
       <c r="C37">
-        <v>123.1616248491581</v>
+        <v>121.530988727739</v>
       </c>
       <c r="D37">
-        <v>177.9266248491581</v>
+        <v>178.254988727739</v>
       </c>
       <c r="E37">
-        <v>-53.13499999999999</v>
+        <v>-51.17599999999999</v>
       </c>
       <c r="F37">
-        <v>68.56500000000001</v>
+        <v>70.52400000000002</v>
       </c>
       <c r="G37">
         <v>13.8</v>
@@ -4315,28 +4315,28 @@
         <v>13.6</v>
       </c>
       <c r="M37">
-        <v>4.395016500000001</v>
+        <v>4.520588400000001</v>
       </c>
       <c r="N37">
-        <v>9.204983500000001</v>
+        <v>9.0794116</v>
       </c>
       <c r="O37">
-        <v>2.76149505</v>
+        <v>2.72382348</v>
       </c>
       <c r="P37">
-        <v>6.44348845</v>
+        <v>6.35558812</v>
       </c>
       <c r="Q37">
-        <v>27.34348845</v>
+        <v>27.25558812</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1306743576652079</v>
+        <v>0.1317115792148874</v>
       </c>
       <c r="T37">
-        <v>1.235025320288283</v>
+        <v>1.250118157652141</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.094413866250559</v>
+        <v>3.008457925521376</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.100448610697528</v>
+        <v>0.1022745889126708</v>
       </c>
       <c r="C38">
-        <v>121.530988727739</v>
+        <v>116.5319215823038</v>
       </c>
       <c r="D38">
-        <v>178.254988727739</v>
+        <v>175.2149215823038</v>
       </c>
       <c r="E38">
-        <v>-51.176</v>
+        <v>-49.217</v>
       </c>
       <c r="F38">
-        <v>70.524</v>
+        <v>72.483</v>
       </c>
       <c r="G38">
         <v>13.8</v>
@@ -4397,45 +4397,45 @@
         <v>13.6</v>
       </c>
       <c r="M38">
-        <v>4.5205884</v>
+        <v>5.2115277</v>
       </c>
       <c r="N38">
-        <v>9.0794116</v>
+        <v>8.3884723</v>
       </c>
       <c r="O38">
-        <v>2.72382348</v>
+        <v>2.51654169</v>
       </c>
       <c r="P38">
-        <v>6.35558812</v>
+        <v>5.87193061</v>
       </c>
       <c r="Q38">
-        <v>27.25558812</v>
+        <v>26.77193061</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1317115792148874</v>
+        <v>0.1327817284328108</v>
       </c>
       <c r="T38">
-        <v>1.250118157652141</v>
+        <v>1.26569013271009</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.008457925521377</v>
+        <v>2.609599484619452</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1022745889126708</v>
+        <v>0.1021349671278136</v>
       </c>
       <c r="C39">
-        <v>116.5319215823038</v>
+        <v>114.8017115003405</v>
       </c>
       <c r="D39">
-        <v>175.2149215823038</v>
+        <v>175.4437115003405</v>
       </c>
       <c r="E39">
-        <v>-49.217</v>
+        <v>-47.258</v>
       </c>
       <c r="F39">
-        <v>72.483</v>
+        <v>74.44200000000001</v>
       </c>
       <c r="G39">
         <v>13.8</v>
@@ -4479,28 +4479,28 @@
         <v>13.6</v>
       </c>
       <c r="M39">
-        <v>5.2115277</v>
+        <v>5.352379800000001</v>
       </c>
       <c r="N39">
-        <v>8.3884723</v>
+        <v>8.2476202</v>
       </c>
       <c r="O39">
-        <v>2.51654169</v>
+        <v>2.47428606</v>
       </c>
       <c r="P39">
-        <v>5.87193061</v>
+        <v>5.77333414</v>
       </c>
       <c r="Q39">
-        <v>26.77193061</v>
+        <v>26.67333414</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1327817284328108</v>
+        <v>0.1338863985932478</v>
       </c>
       <c r="T39">
-        <v>1.26569013271009</v>
+        <v>1.281764429544102</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.609599484619452</v>
+        <v>2.540925813971572</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1021349671278136</v>
+        <v>0.1030600453429565</v>
       </c>
       <c r="C40">
-        <v>114.8017115003405</v>
+        <v>111.337880487671</v>
       </c>
       <c r="D40">
-        <v>175.4437115003405</v>
+        <v>173.938880487671</v>
       </c>
       <c r="E40">
-        <v>-47.258</v>
+        <v>-45.29899999999999</v>
       </c>
       <c r="F40">
-        <v>74.44200000000001</v>
+        <v>76.40100000000001</v>
       </c>
       <c r="G40">
         <v>13.8</v>
@@ -4561,45 +4561,45 @@
         <v>13.6</v>
       </c>
       <c r="M40">
-        <v>5.352379800000001</v>
+        <v>5.791195800000001</v>
       </c>
       <c r="N40">
-        <v>8.2476202</v>
+        <v>7.8088042</v>
       </c>
       <c r="O40">
-        <v>2.47428606</v>
+        <v>2.34264126</v>
       </c>
       <c r="P40">
-        <v>5.77333414</v>
+        <v>5.46616294</v>
       </c>
       <c r="Q40">
-        <v>26.67333414</v>
+        <v>26.36616294</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1338863985932478</v>
+        <v>0.1350272874474696</v>
       </c>
       <c r="T40">
-        <v>1.281764429544102</v>
+        <v>1.298365752503819</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.540925813971572</v>
+        <v>2.348392364837673</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1030600453429565</v>
+        <v>0.1029477235580993</v>
       </c>
       <c r="C41">
-        <v>111.337880487671</v>
+        <v>109.5602167533948</v>
       </c>
       <c r="D41">
-        <v>173.938880487671</v>
+        <v>174.1202167533948</v>
       </c>
       <c r="E41">
-        <v>-45.29899999999999</v>
+        <v>-43.33999999999999</v>
       </c>
       <c r="F41">
-        <v>76.40100000000001</v>
+        <v>78.36000000000001</v>
       </c>
       <c r="G41">
         <v>13.8</v>
@@ -4643,28 +4643,28 @@
         <v>13.6</v>
       </c>
       <c r="M41">
-        <v>5.791195800000001</v>
+        <v>5.939688000000001</v>
       </c>
       <c r="N41">
-        <v>7.8088042</v>
+        <v>7.660312</v>
       </c>
       <c r="O41">
-        <v>2.34264126</v>
+        <v>2.2980936</v>
       </c>
       <c r="P41">
-        <v>5.46616294</v>
+        <v>5.3622184</v>
       </c>
       <c r="Q41">
-        <v>26.36616294</v>
+        <v>26.2622184</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1350272874474696</v>
+        <v>0.1362062059301656</v>
       </c>
       <c r="T41">
-        <v>1.298365752503819</v>
+        <v>1.315520452895527</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.348392364837673</v>
+        <v>2.289682555716731</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1029477235580993</v>
+        <v>0.1028354017732422</v>
       </c>
       <c r="C42">
-        <v>109.5602167533948</v>
+        <v>107.7829315102099</v>
       </c>
       <c r="D42">
-        <v>174.1202167533948</v>
+        <v>174.3019315102099</v>
       </c>
       <c r="E42">
-        <v>-43.33999999999999</v>
+        <v>-41.381</v>
       </c>
       <c r="F42">
-        <v>78.36000000000001</v>
+        <v>80.319</v>
       </c>
       <c r="G42">
         <v>13.8</v>
@@ -4725,28 +4725,28 @@
         <v>13.6</v>
       </c>
       <c r="M42">
-        <v>5.939688000000001</v>
+        <v>6.088180200000001</v>
       </c>
       <c r="N42">
-        <v>7.660312</v>
+        <v>7.5118198</v>
       </c>
       <c r="O42">
-        <v>2.2980936</v>
+        <v>2.25354594</v>
       </c>
       <c r="P42">
-        <v>5.3622184</v>
+        <v>5.258273860000001</v>
       </c>
       <c r="Q42">
-        <v>26.2622184</v>
+        <v>26.15827386</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1362062059301656</v>
+        <v>0.1374250877512579</v>
       </c>
       <c r="T42">
-        <v>1.315520452895527</v>
+        <v>1.33325666855475</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.289682555716731</v>
+        <v>2.23383663972364</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1028354017732422</v>
+        <v>0.102723079988385</v>
       </c>
       <c r="C43">
-        <v>107.7829315102099</v>
+        <v>106.0060259443531</v>
       </c>
       <c r="D43">
-        <v>174.3019315102099</v>
+        <v>174.4840259443531</v>
       </c>
       <c r="E43">
-        <v>-41.381</v>
+        <v>-39.422</v>
       </c>
       <c r="F43">
-        <v>80.319</v>
+        <v>82.27800000000001</v>
       </c>
       <c r="G43">
         <v>13.8</v>
@@ -4807,28 +4807,28 @@
         <v>13.6</v>
       </c>
       <c r="M43">
-        <v>6.088180200000001</v>
+        <v>6.236672400000001</v>
       </c>
       <c r="N43">
-        <v>7.5118198</v>
+        <v>7.363327600000001</v>
       </c>
       <c r="O43">
-        <v>2.25354594</v>
+        <v>2.20899828</v>
       </c>
       <c r="P43">
-        <v>5.258273860000001</v>
+        <v>5.15432932</v>
       </c>
       <c r="Q43">
-        <v>26.15827386</v>
+        <v>26.05432932</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1374250877512579</v>
+        <v>0.1386859999799742</v>
       </c>
       <c r="T43">
-        <v>1.33325666855475</v>
+        <v>1.351604477857395</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.23383663972364</v>
+        <v>2.180650053063554</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.102723079988385</v>
+        <v>0.1026107582035279</v>
       </c>
       <c r="C44">
-        <v>106.0060259443531</v>
+        <v>104.2295012470235</v>
       </c>
       <c r="D44">
-        <v>174.4840259443531</v>
+        <v>174.6665012470235</v>
       </c>
       <c r="E44">
-        <v>-39.422</v>
+        <v>-37.46300000000001</v>
       </c>
       <c r="F44">
-        <v>82.27800000000001</v>
+        <v>84.23699999999999</v>
       </c>
       <c r="G44">
         <v>13.8</v>
@@ -4889,28 +4889,28 @@
         <v>13.6</v>
       </c>
       <c r="M44">
-        <v>6.236672400000001</v>
+        <v>6.3851646</v>
       </c>
       <c r="N44">
-        <v>7.363327600000001</v>
+        <v>7.214835400000001</v>
       </c>
       <c r="O44">
-        <v>2.20899828</v>
+        <v>2.16445062</v>
       </c>
       <c r="P44">
-        <v>5.15432932</v>
+        <v>5.050384780000001</v>
       </c>
       <c r="Q44">
-        <v>26.05432932</v>
+        <v>25.95038478</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1386859999799741</v>
+        <v>0.1399911547430313</v>
       </c>
       <c r="T44">
-        <v>1.351604477857395</v>
+        <v>1.370596069942588</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.180650053063554</v>
+        <v>2.129937261131843</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1026107582035279</v>
+        <v>0.1024984364186707</v>
       </c>
       <c r="C45">
-        <v>104.2295012470235</v>
+        <v>102.4533586144082</v>
       </c>
       <c r="D45">
-        <v>174.6665012470235</v>
+        <v>174.8493586144082</v>
       </c>
       <c r="E45">
-        <v>-37.46300000000001</v>
+        <v>-35.504</v>
       </c>
       <c r="F45">
-        <v>84.23699999999999</v>
+        <v>86.196</v>
       </c>
       <c r="G45">
         <v>13.8</v>
@@ -4971,28 +4971,28 @@
         <v>13.6</v>
       </c>
       <c r="M45">
-        <v>6.3851646</v>
+        <v>6.5336568</v>
       </c>
       <c r="N45">
-        <v>7.214835400000001</v>
+        <v>7.066343200000001</v>
       </c>
       <c r="O45">
-        <v>2.16445062</v>
+        <v>2.11990296</v>
       </c>
       <c r="P45">
-        <v>5.050384780000001</v>
+        <v>4.946440240000001</v>
       </c>
       <c r="Q45">
-        <v>25.95038478</v>
+        <v>25.84644024</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1399911547430313</v>
+        <v>0.1413429221761977</v>
       </c>
       <c r="T45">
-        <v>1.370596069942588</v>
+        <v>1.390265933173682</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.129937261131843</v>
+        <v>2.08152959610612</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1024984364186707</v>
+        <v>0.1023861146338136</v>
       </c>
       <c r="C46">
-        <v>102.4533586144082</v>
+        <v>100.6775992477091</v>
       </c>
       <c r="D46">
-        <v>174.8493586144082</v>
+        <v>175.0325992477091</v>
       </c>
       <c r="E46">
-        <v>-35.504</v>
+        <v>-33.545</v>
       </c>
       <c r="F46">
-        <v>86.196</v>
+        <v>88.155</v>
       </c>
       <c r="G46">
         <v>13.8</v>
@@ -5053,28 +5053,28 @@
         <v>13.6</v>
       </c>
       <c r="M46">
-        <v>6.5336568</v>
+        <v>6.682149000000001</v>
       </c>
       <c r="N46">
-        <v>7.066343200000001</v>
+        <v>6.917851000000001</v>
       </c>
       <c r="O46">
-        <v>2.11990296</v>
+        <v>2.0753553</v>
       </c>
       <c r="P46">
-        <v>4.946440240000001</v>
+        <v>4.842495700000001</v>
       </c>
       <c r="Q46">
-        <v>25.84644024</v>
+        <v>25.7424957</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1413429221761977</v>
+        <v>0.1427438447887519</v>
       </c>
       <c r="T46">
-        <v>1.390265933173682</v>
+        <v>1.410651064158633</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.08152959610612</v>
+        <v>2.035273382859317</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1023861146338136</v>
+        <v>0.1068461928489564</v>
       </c>
       <c r="C47">
-        <v>100.6775992477091</v>
+        <v>91.72584150780028</v>
       </c>
       <c r="D47">
-        <v>175.0325992477091</v>
+        <v>168.0398415078003</v>
       </c>
       <c r="E47">
-        <v>-33.545</v>
+        <v>-31.586</v>
       </c>
       <c r="F47">
-        <v>88.155</v>
+        <v>90.114</v>
       </c>
       <c r="G47">
         <v>13.8</v>
@@ -5135,45 +5135,45 @@
         <v>13.6</v>
       </c>
       <c r="M47">
-        <v>6.682149000000001</v>
+        <v>8.11026</v>
       </c>
       <c r="N47">
-        <v>6.917851000000001</v>
+        <v>5.489740000000001</v>
       </c>
       <c r="O47">
-        <v>2.0753553</v>
+        <v>1.646922</v>
       </c>
       <c r="P47">
-        <v>4.842495700000001</v>
+        <v>3.842818000000001</v>
       </c>
       <c r="Q47">
-        <v>25.7424957</v>
+        <v>24.742818</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1427438447887519</v>
+        <v>0.1441966534239933</v>
       </c>
       <c r="T47">
-        <v>1.410651064158633</v>
+        <v>1.431791199994879</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.035273382859317</v>
+        <v>1.676888287181916</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1068461928489564</v>
+        <v>0.1068332710640992</v>
       </c>
       <c r="C48">
-        <v>91.72584150780028</v>
+        <v>89.78629385918202</v>
       </c>
       <c r="D48">
-        <v>168.0398415078003</v>
+        <v>168.059293859182</v>
       </c>
       <c r="E48">
-        <v>-31.586</v>
+        <v>-29.627</v>
       </c>
       <c r="F48">
-        <v>90.114</v>
+        <v>92.07300000000001</v>
       </c>
       <c r="G48">
         <v>13.8</v>
@@ -5217,28 +5217,28 @@
         <v>13.6</v>
       </c>
       <c r="M48">
-        <v>8.11026</v>
+        <v>8.286570000000001</v>
       </c>
       <c r="N48">
-        <v>5.489740000000001</v>
+        <v>5.31343</v>
       </c>
       <c r="O48">
-        <v>1.646922</v>
+        <v>1.594029</v>
       </c>
       <c r="P48">
-        <v>3.842818000000001</v>
+        <v>3.719401</v>
       </c>
       <c r="Q48">
-        <v>24.742818</v>
+        <v>24.619401</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1441966534239933</v>
+        <v>0.1457042850266023</v>
       </c>
       <c r="T48">
-        <v>1.431791199994879</v>
+        <v>1.453729076806078</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.676888287181916</v>
+        <v>1.641209812986555</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1068332710640992</v>
+        <v>0.1068203492792421</v>
       </c>
       <c r="C49">
-        <v>89.78629385918202</v>
+        <v>87.84675071470735</v>
       </c>
       <c r="D49">
-        <v>168.059293859182</v>
+        <v>168.0787507147074</v>
       </c>
       <c r="E49">
-        <v>-29.627</v>
+        <v>-27.66799999999999</v>
       </c>
       <c r="F49">
-        <v>92.07300000000001</v>
+        <v>94.03200000000001</v>
       </c>
       <c r="G49">
         <v>13.8</v>
@@ -5299,28 +5299,28 @@
         <v>13.6</v>
       </c>
       <c r="M49">
-        <v>8.286570000000001</v>
+        <v>8.46288</v>
       </c>
       <c r="N49">
-        <v>5.31343</v>
+        <v>5.137120000000001</v>
       </c>
       <c r="O49">
-        <v>1.594029</v>
+        <v>1.541136</v>
       </c>
       <c r="P49">
-        <v>3.719401</v>
+        <v>3.595984000000001</v>
       </c>
       <c r="Q49">
-        <v>24.619401</v>
+        <v>24.495984</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1457042850266023</v>
+        <v>0.1472699024600809</v>
       </c>
       <c r="T49">
-        <v>1.453729076806078</v>
+        <v>1.476510718110014</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.641209812986555</v>
+        <v>1.607017941882669</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1068203492792421</v>
+        <v>0.1068074274943849</v>
       </c>
       <c r="C50">
-        <v>87.84675071470737</v>
+        <v>85.90721207594079</v>
       </c>
       <c r="D50">
-        <v>168.0787507147074</v>
+        <v>168.0982120759408</v>
       </c>
       <c r="E50">
-        <v>-27.66800000000001</v>
+        <v>-25.709</v>
       </c>
       <c r="F50">
-        <v>94.032</v>
+        <v>95.991</v>
       </c>
       <c r="G50">
         <v>13.8</v>
@@ -5381,28 +5381,28 @@
         <v>13.6</v>
       </c>
       <c r="M50">
-        <v>8.46288</v>
+        <v>8.639189999999999</v>
       </c>
       <c r="N50">
-        <v>5.137120000000001</v>
+        <v>4.960810000000002</v>
       </c>
       <c r="O50">
-        <v>1.541136</v>
+        <v>1.488243000000001</v>
       </c>
       <c r="P50">
-        <v>3.595984000000001</v>
+        <v>3.472567000000002</v>
       </c>
       <c r="Q50">
-        <v>24.495984</v>
+        <v>24.372567</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1472699024600809</v>
+        <v>0.1488969166556567</v>
       </c>
       <c r="T50">
-        <v>1.476510718110014</v>
+        <v>1.500185757112145</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.607017941882669</v>
+        <v>1.574221657354451</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1068074274943849</v>
+        <v>0.1067945057095278</v>
       </c>
       <c r="C51">
-        <v>85.90721207594079</v>
+        <v>83.96767794444754</v>
       </c>
       <c r="D51">
-        <v>168.0982120759408</v>
+        <v>168.1176779444475</v>
       </c>
       <c r="E51">
-        <v>-25.709</v>
+        <v>-23.75</v>
       </c>
       <c r="F51">
-        <v>95.991</v>
+        <v>97.95</v>
       </c>
       <c r="G51">
         <v>13.8</v>
@@ -5463,28 +5463,28 @@
         <v>13.6</v>
       </c>
       <c r="M51">
-        <v>8.639189999999999</v>
+        <v>8.8155</v>
       </c>
       <c r="N51">
-        <v>4.960810000000002</v>
+        <v>4.784500000000001</v>
       </c>
       <c r="O51">
-        <v>1.488243000000001</v>
+        <v>1.43535</v>
       </c>
       <c r="P51">
-        <v>3.472567000000002</v>
+        <v>3.349150000000001</v>
       </c>
       <c r="Q51">
-        <v>24.372567</v>
+        <v>24.24915</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1488969166556567</v>
+        <v>0.1505890114190555</v>
       </c>
       <c r="T51">
-        <v>1.500185757112145</v>
+        <v>1.524807797674361</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.574221657354451</v>
+        <v>1.542737224207362</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1067945057095278</v>
+        <v>0.1067815839246706</v>
       </c>
       <c r="C52">
-        <v>83.96767794444754</v>
+        <v>82.02814832179372</v>
       </c>
       <c r="D52">
-        <v>168.1176779444475</v>
+        <v>168.1371483217937</v>
       </c>
       <c r="E52">
-        <v>-23.75</v>
+        <v>-21.791</v>
       </c>
       <c r="F52">
-        <v>97.95</v>
+        <v>99.90900000000001</v>
       </c>
       <c r="G52">
         <v>13.8</v>
@@ -5545,28 +5545,28 @@
         <v>13.6</v>
       </c>
       <c r="M52">
-        <v>8.8155</v>
+        <v>8.991810000000001</v>
       </c>
       <c r="N52">
-        <v>4.784500000000001</v>
+        <v>4.60819</v>
       </c>
       <c r="O52">
-        <v>1.43535</v>
+        <v>1.382457</v>
       </c>
       <c r="P52">
-        <v>3.349150000000001</v>
+        <v>3.225733</v>
       </c>
       <c r="Q52">
-        <v>24.24915</v>
+        <v>24.125733</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1505890114190555</v>
+        <v>0.152350171274838</v>
       </c>
       <c r="T52">
-        <v>1.524807797674361</v>
+        <v>1.550434819484014</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.542737224207362</v>
+        <v>1.5124874747131</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1067815839246706</v>
+        <v>0.1303885079242442</v>
       </c>
       <c r="C53">
-        <v>82.02814832179372</v>
+        <v>50.70692804997513</v>
       </c>
       <c r="D53">
-        <v>168.1371483217937</v>
+        <v>138.7749280499751</v>
       </c>
       <c r="E53">
-        <v>-21.791</v>
+        <v>-19.83199999999999</v>
       </c>
       <c r="F53">
-        <v>99.90900000000001</v>
+        <v>101.868</v>
       </c>
       <c r="G53">
         <v>13.8</v>
@@ -5627,45 +5627,45 @@
         <v>13.6</v>
       </c>
       <c r="M53">
-        <v>8.991810000000001</v>
+        <v>14.9542224</v>
       </c>
       <c r="N53">
-        <v>4.60819</v>
+        <v>-1.354222400000001</v>
       </c>
       <c r="O53">
-        <v>1.382457</v>
+        <v>-0.4062667200000004</v>
       </c>
       <c r="P53">
-        <v>3.225733</v>
+        <v>-0.9479556800000009</v>
       </c>
       <c r="Q53">
-        <v>24.125733</v>
+        <v>19.95204432</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.152350171274838</v>
+        <v>0.1559988759396742</v>
       </c>
       <c r="T53">
-        <v>1.550434819484014</v>
+        <v>1.6035279181688</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.3</v>
+        <v>0.2728326415688455</v>
       </c>
       <c r="W53">
-        <v>0.063</v>
+        <v>0.1067481682176935</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.5124874747131</v>
+        <v>0.9094421385628182</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1303885079242442</v>
+        <v>0.1313985079242442</v>
       </c>
       <c r="C54">
-        <v>50.70692804997513</v>
+        <v>47.71876204346604</v>
       </c>
       <c r="D54">
-        <v>138.7749280499751</v>
+        <v>137.745762043466</v>
       </c>
       <c r="E54">
-        <v>-19.83199999999999</v>
+        <v>-17.87299999999999</v>
       </c>
       <c r="F54">
-        <v>101.868</v>
+        <v>103.827</v>
       </c>
       <c r="G54">
         <v>13.8</v>
@@ -5709,37 +5709,37 @@
         <v>13.6</v>
       </c>
       <c r="M54">
-        <v>14.9542224</v>
+        <v>15.2418036</v>
       </c>
       <c r="N54">
-        <v>-1.354222400000001</v>
+        <v>-1.641803600000001</v>
       </c>
       <c r="O54">
-        <v>-0.4062667200000004</v>
+        <v>-0.4925410800000003</v>
       </c>
       <c r="P54">
-        <v>-0.9479556800000009</v>
+        <v>-1.149262520000001</v>
       </c>
       <c r="Q54">
-        <v>19.95204432</v>
+        <v>19.75073748</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1559988759396742</v>
+        <v>0.1583435328745608</v>
       </c>
       <c r="T54">
-        <v>1.6035279181688</v>
+        <v>1.637645533448987</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2728326415688455</v>
+        <v>0.2676848558788672</v>
       </c>
       <c r="W54">
-        <v>0.1067481682176935</v>
+        <v>0.1075038631569823</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9094421385628182</v>
+        <v>0.8922828529295574</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1313985079242442</v>
+        <v>0.1324085079242442</v>
       </c>
       <c r="C55">
-        <v>47.71876204346604</v>
+        <v>44.74574842109995</v>
       </c>
       <c r="D55">
-        <v>137.745762043466</v>
+        <v>136.7317484211</v>
       </c>
       <c r="E55">
-        <v>-17.87299999999999</v>
+        <v>-15.91399999999999</v>
       </c>
       <c r="F55">
-        <v>103.827</v>
+        <v>105.786</v>
       </c>
       <c r="G55">
         <v>13.8</v>
@@ -5791,37 +5791,37 @@
         <v>13.6</v>
       </c>
       <c r="M55">
-        <v>15.2418036</v>
+        <v>15.5293848</v>
       </c>
       <c r="N55">
-        <v>-1.641803600000001</v>
+        <v>-1.929384800000003</v>
       </c>
       <c r="O55">
-        <v>-0.4925410800000003</v>
+        <v>-0.5788154400000008</v>
       </c>
       <c r="P55">
-        <v>-1.149262520000001</v>
+        <v>-1.350569360000002</v>
       </c>
       <c r="Q55">
-        <v>19.75073748</v>
+        <v>19.54943064</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1583435328745608</v>
+        <v>0.1607901314153122</v>
       </c>
       <c r="T55">
-        <v>1.637645533448987</v>
+        <v>1.673246523306574</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2676848558788672</v>
+        <v>0.2627277289181474</v>
       </c>
       <c r="W55">
-        <v>0.1075038631569823</v>
+        <v>0.108231569394816</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8922828529295574</v>
+        <v>0.8757590963938248</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1324085079242442</v>
+        <v>0.1334185079242442</v>
       </c>
       <c r="C56">
-        <v>44.74574842109995</v>
+        <v>41.78755499603402</v>
       </c>
       <c r="D56">
-        <v>136.7317484211</v>
+        <v>135.732554996034</v>
       </c>
       <c r="E56">
-        <v>-15.91399999999999</v>
+        <v>-13.95499999999998</v>
       </c>
       <c r="F56">
-        <v>105.786</v>
+        <v>107.745</v>
       </c>
       <c r="G56">
         <v>13.8</v>
@@ -5873,37 +5873,37 @@
         <v>13.6</v>
       </c>
       <c r="M56">
-        <v>15.5293848</v>
+        <v>15.816966</v>
       </c>
       <c r="N56">
-        <v>-1.929384800000003</v>
+        <v>-2.216966000000003</v>
       </c>
       <c r="O56">
-        <v>-0.5788154400000008</v>
+        <v>-0.6650898000000008</v>
       </c>
       <c r="P56">
-        <v>-1.350569360000002</v>
+        <v>-1.551876200000002</v>
       </c>
       <c r="Q56">
-        <v>19.54943064</v>
+        <v>19.3481238</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1607901314153122</v>
+        <v>0.1633454676689858</v>
       </c>
       <c r="T56">
-        <v>1.673246523306574</v>
+        <v>1.710429779380053</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2627277289181474</v>
+        <v>0.2579508611196357</v>
       </c>
       <c r="W56">
-        <v>0.108231569394816</v>
+        <v>0.1089328135876375</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8757590963938248</v>
+        <v>0.8598362037321189</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1334185079242442</v>
+        <v>0.1344285079242442</v>
       </c>
       <c r="C57">
-        <v>41.78755499603402</v>
+        <v>38.84385922105764</v>
       </c>
       <c r="D57">
-        <v>135.732554996034</v>
+        <v>134.7478592210576</v>
       </c>
       <c r="E57">
-        <v>-13.95499999999998</v>
+        <v>-11.996</v>
       </c>
       <c r="F57">
-        <v>107.745</v>
+        <v>109.704</v>
       </c>
       <c r="G57">
         <v>13.8</v>
@@ -5955,37 +5955,37 @@
         <v>13.6</v>
       </c>
       <c r="M57">
-        <v>15.816966</v>
+        <v>16.1045472</v>
       </c>
       <c r="N57">
-        <v>-2.216966000000003</v>
+        <v>-2.504547200000001</v>
       </c>
       <c r="O57">
-        <v>-0.6650898000000008</v>
+        <v>-0.7513641600000003</v>
       </c>
       <c r="P57">
-        <v>-1.551876200000002</v>
+        <v>-1.753183040000001</v>
       </c>
       <c r="Q57">
-        <v>19.3481238</v>
+        <v>19.14681696</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1633454676689858</v>
+        <v>0.1660169555705537</v>
       </c>
       <c r="T57">
-        <v>1.710429779380053</v>
+        <v>1.749303183456873</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2579508611196357</v>
+        <v>0.2533445957424993</v>
       </c>
       <c r="W57">
-        <v>0.1089328135876375</v>
+        <v>0.1096090133450011</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8598362037321189</v>
+        <v>0.8444819858083312</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1344285079242442</v>
+        <v>0.1354385079242442</v>
       </c>
       <c r="C58">
-        <v>38.84385922105764</v>
+        <v>35.91434784144883</v>
       </c>
       <c r="D58">
-        <v>134.7478592210576</v>
+        <v>133.7773478414488</v>
       </c>
       <c r="E58">
-        <v>-11.996</v>
+        <v>-10.03699999999999</v>
       </c>
       <c r="F58">
-        <v>109.704</v>
+        <v>111.663</v>
       </c>
       <c r="G58">
         <v>13.8</v>
@@ -6037,37 +6037,37 @@
         <v>13.6</v>
       </c>
       <c r="M58">
-        <v>16.1045472</v>
+        <v>16.3921284</v>
       </c>
       <c r="N58">
-        <v>-2.504547200000001</v>
+        <v>-2.792128400000003</v>
       </c>
       <c r="O58">
-        <v>-0.7513641600000003</v>
+        <v>-0.8376385200000008</v>
       </c>
       <c r="P58">
-        <v>-1.753183040000001</v>
+        <v>-1.954489880000002</v>
       </c>
       <c r="Q58">
-        <v>19.14681696</v>
+        <v>18.94551012</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1660169555705537</v>
+        <v>0.1688126987233572</v>
       </c>
       <c r="T58">
-        <v>1.749303183456873</v>
+        <v>1.789984652839591</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2533445957424993</v>
+        <v>0.2488999537119291</v>
       </c>
       <c r="W58">
-        <v>0.1096090133450011</v>
+        <v>0.1102614867950888</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8444819858083312</v>
+        <v>0.8296665123730972</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1354385079242442</v>
+        <v>0.1364485079242442</v>
       </c>
       <c r="C59">
-        <v>35.91434784144883</v>
+        <v>32.99871656272518</v>
       </c>
       <c r="D59">
-        <v>133.7773478414488</v>
+        <v>132.8207165627252</v>
       </c>
       <c r="E59">
-        <v>-10.03699999999999</v>
+        <v>-8.077999999999989</v>
       </c>
       <c r="F59">
-        <v>111.663</v>
+        <v>113.622</v>
       </c>
       <c r="G59">
         <v>13.8</v>
@@ -6119,37 +6119,37 @@
         <v>13.6</v>
       </c>
       <c r="M59">
-        <v>16.3921284</v>
+        <v>16.6797096</v>
       </c>
       <c r="N59">
-        <v>-2.792128400000003</v>
+        <v>-3.079709600000001</v>
       </c>
       <c r="O59">
-        <v>-0.8376385200000008</v>
+        <v>-0.9239128800000003</v>
       </c>
       <c r="P59">
-        <v>-1.954489880000002</v>
+        <v>-2.155796720000001</v>
       </c>
       <c r="Q59">
-        <v>18.94551012</v>
+        <v>18.74420328</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1688126987233572</v>
+        <v>0.1717415725024848</v>
       </c>
       <c r="T59">
-        <v>1.789984652839591</v>
+        <v>1.832603335050057</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2488999537119291</v>
+        <v>0.2446085751996545</v>
       </c>
       <c r="W59">
-        <v>0.1102614867950888</v>
+        <v>0.1108914611606907</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8296665123730972</v>
+        <v>0.8153619173321818</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1364485079242442</v>
+        <v>0.1374585079242442</v>
       </c>
       <c r="C60">
-        <v>32.99871656272519</v>
+        <v>30.09666973254831</v>
       </c>
       <c r="D60">
-        <v>132.8207165627252</v>
+        <v>131.8776697325483</v>
       </c>
       <c r="E60">
-        <v>-8.078000000000003</v>
+        <v>-6.119</v>
       </c>
       <c r="F60">
-        <v>113.622</v>
+        <v>115.581</v>
       </c>
       <c r="G60">
         <v>13.8</v>
@@ -6201,37 +6201,37 @@
         <v>13.6</v>
       </c>
       <c r="M60">
-        <v>16.6797096</v>
+        <v>16.9672908</v>
       </c>
       <c r="N60">
-        <v>-3.079709600000001</v>
+        <v>-3.367290799999999</v>
       </c>
       <c r="O60">
-        <v>-0.9239128800000003</v>
+        <v>-1.01018724</v>
       </c>
       <c r="P60">
-        <v>-2.155796720000001</v>
+        <v>-2.35710356</v>
       </c>
       <c r="Q60">
-        <v>18.74420328</v>
+        <v>18.54289644</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1717415725024848</v>
+        <v>0.1748133181732771</v>
       </c>
       <c r="T60">
-        <v>1.832603335050057</v>
+        <v>1.877300977368351</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2446085751996545</v>
+        <v>0.2404626671454231</v>
       </c>
       <c r="W60">
-        <v>0.1108914611606907</v>
+        <v>0.1115000804630519</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8153619173321818</v>
+        <v>0.8015422238180772</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1374585079242442</v>
+        <v>0.1732202871228123</v>
       </c>
       <c r="C61">
-        <v>30.09666973254831</v>
+        <v>1.644109925968834</v>
       </c>
       <c r="D61">
-        <v>131.8776697325483</v>
+        <v>105.3841099259688</v>
       </c>
       <c r="E61">
-        <v>-6.119</v>
+        <v>-4.160000000000011</v>
       </c>
       <c r="F61">
-        <v>115.581</v>
+        <v>117.54</v>
       </c>
       <c r="G61">
         <v>13.8</v>
@@ -6283,45 +6283,45 @@
         <v>13.6</v>
       </c>
       <c r="M61">
-        <v>16.9672908</v>
+        <v>23.602032</v>
       </c>
       <c r="N61">
-        <v>-3.367290799999999</v>
+        <v>-10.002032</v>
       </c>
       <c r="O61">
-        <v>-1.01018724</v>
+        <v>-3.000609599999999</v>
       </c>
       <c r="P61">
-        <v>-2.35710356</v>
+        <v>-7.001422399999997</v>
       </c>
       <c r="Q61">
-        <v>18.54289644</v>
+        <v>13.8985776</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1748133181732771</v>
+        <v>0.1839180991240291</v>
       </c>
       <c r="T61">
-        <v>1.877300977368351</v>
+        <v>2.009786634039973</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.2404626671454231</v>
+        <v>0.1728664718359843</v>
       </c>
       <c r="W61">
-        <v>0.1115000804630519</v>
+        <v>0.1660884124553343</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8015422238180772</v>
+        <v>0.5762215727866145</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1732202871228123</v>
+        <v>0.1747702871228123</v>
       </c>
       <c r="C62">
-        <v>1.644109925968834</v>
+        <v>-1.224576295094408</v>
       </c>
       <c r="D62">
-        <v>105.3841099259688</v>
+        <v>104.4744237049056</v>
       </c>
       <c r="E62">
-        <v>-4.160000000000011</v>
+        <v>-2.201000000000008</v>
       </c>
       <c r="F62">
-        <v>117.54</v>
+        <v>119.499</v>
       </c>
       <c r="G62">
         <v>13.8</v>
@@ -6365,37 +6365,37 @@
         <v>13.6</v>
       </c>
       <c r="M62">
-        <v>23.602032</v>
+        <v>23.9953992</v>
       </c>
       <c r="N62">
-        <v>-10.002032</v>
+        <v>-10.3953992</v>
       </c>
       <c r="O62">
-        <v>-3.000609599999999</v>
+        <v>-3.11861976</v>
       </c>
       <c r="P62">
-        <v>-7.001422399999997</v>
+        <v>-7.27677944</v>
       </c>
       <c r="Q62">
-        <v>13.8985776</v>
+        <v>13.62322056</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1839180991240291</v>
+        <v>0.1874595888451581</v>
       </c>
       <c r="T62">
-        <v>2.009786634039973</v>
+        <v>2.061319624656384</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1728664718359843</v>
+        <v>0.1700325952485091</v>
       </c>
       <c r="W62">
-        <v>0.1660884124553343</v>
+        <v>0.1666574548740994</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5762215727866145</v>
+        <v>0.5667753174950305</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1747702871228123</v>
+        <v>0.1763202871228123</v>
       </c>
       <c r="C63">
-        <v>-1.224576295094408</v>
+        <v>-4.077691917481346</v>
       </c>
       <c r="D63">
-        <v>104.4744237049056</v>
+        <v>103.5803080825187</v>
       </c>
       <c r="E63">
-        <v>-2.201000000000008</v>
+        <v>-0.2420000000000044</v>
       </c>
       <c r="F63">
-        <v>119.499</v>
+        <v>121.458</v>
       </c>
       <c r="G63">
         <v>13.8</v>
@@ -6447,37 +6447,37 @@
         <v>13.6</v>
       </c>
       <c r="M63">
-        <v>23.9953992</v>
+        <v>24.3887664</v>
       </c>
       <c r="N63">
-        <v>-10.3953992</v>
+        <v>-10.7887664</v>
       </c>
       <c r="O63">
-        <v>-3.11861976</v>
+        <v>-3.23662992</v>
       </c>
       <c r="P63">
-        <v>-7.27677944</v>
+        <v>-7.55213648</v>
       </c>
       <c r="Q63">
-        <v>13.62322056</v>
+        <v>13.34786352</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1874595888451581</v>
+        <v>0.191187472762136</v>
       </c>
       <c r="T63">
-        <v>2.061319624656384</v>
+        <v>2.115564877936814</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1700325952485091</v>
+        <v>0.1672901340348235</v>
       </c>
       <c r="W63">
-        <v>0.1666574548740994</v>
+        <v>0.1672081410858074</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5667753174950305</v>
+        <v>0.5576337801160784</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1763202871228123</v>
+        <v>0.1778702871228123</v>
       </c>
       <c r="C64">
-        <v>-4.077691917481346</v>
+        <v>-6.915633318961369</v>
       </c>
       <c r="D64">
-        <v>103.5803080825187</v>
+        <v>102.7013666810386</v>
       </c>
       <c r="E64">
-        <v>-0.2420000000000044</v>
+        <v>1.716999999999999</v>
       </c>
       <c r="F64">
-        <v>121.458</v>
+        <v>123.417</v>
       </c>
       <c r="G64">
         <v>13.8</v>
@@ -6529,37 +6529,37 @@
         <v>13.6</v>
       </c>
       <c r="M64">
-        <v>24.3887664</v>
+        <v>24.7821336</v>
       </c>
       <c r="N64">
-        <v>-10.7887664</v>
+        <v>-11.1821336</v>
       </c>
       <c r="O64">
-        <v>-3.23662992</v>
+        <v>-3.35464008</v>
       </c>
       <c r="P64">
-        <v>-7.55213648</v>
+        <v>-7.827493520000001</v>
       </c>
       <c r="Q64">
-        <v>13.34786352</v>
+        <v>13.07250648</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.191187472762136</v>
+        <v>0.1951168639178694</v>
       </c>
       <c r="T64">
-        <v>2.115564877936814</v>
+        <v>2.172742307070242</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1672901340348235</v>
+        <v>0.1646347350818898</v>
       </c>
       <c r="W64">
-        <v>0.1672081410858074</v>
+        <v>0.1677413451955566</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5576337801160784</v>
+        <v>0.548782450272966</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1778702871228123</v>
+        <v>0.1794202871228123</v>
       </c>
       <c r="C65">
-        <v>-6.915633318961369</v>
+        <v>-9.738783536490658</v>
       </c>
       <c r="D65">
-        <v>102.7013666810386</v>
+        <v>101.8372164635093</v>
       </c>
       <c r="E65">
-        <v>1.716999999999999</v>
+        <v>3.676000000000002</v>
       </c>
       <c r="F65">
-        <v>123.417</v>
+        <v>125.376</v>
       </c>
       <c r="G65">
         <v>13.8</v>
@@ -6611,37 +6611,37 @@
         <v>13.6</v>
       </c>
       <c r="M65">
-        <v>24.7821336</v>
+        <v>25.1755008</v>
       </c>
       <c r="N65">
-        <v>-11.1821336</v>
+        <v>-11.5755008</v>
       </c>
       <c r="O65">
-        <v>-3.35464008</v>
+        <v>-3.47265024</v>
       </c>
       <c r="P65">
-        <v>-7.827493520000001</v>
+        <v>-8.10285056</v>
       </c>
       <c r="Q65">
-        <v>13.07250648</v>
+        <v>12.79714944</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1951168639178694</v>
+        <v>0.1992645545822547</v>
       </c>
       <c r="T65">
-        <v>2.172742307070242</v>
+        <v>2.233096260044416</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1646347350818898</v>
+        <v>0.1620623173462353</v>
       </c>
       <c r="W65">
-        <v>0.1677413451955566</v>
+        <v>0.168257886676876</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.548782450272966</v>
+        <v>0.5402077244874509</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1794202871228123</v>
+        <v>0.1809702871228123</v>
       </c>
       <c r="C66">
-        <v>-9.738783536490658</v>
+        <v>-12.54751282279075</v>
       </c>
       <c r="D66">
-        <v>101.8372164635093</v>
+        <v>100.9874871772093</v>
       </c>
       <c r="E66">
-        <v>3.676000000000002</v>
+        <v>5.635000000000005</v>
       </c>
       <c r="F66">
-        <v>125.376</v>
+        <v>127.335</v>
       </c>
       <c r="G66">
         <v>13.8</v>
@@ -6693,37 +6693,37 @@
         <v>13.6</v>
       </c>
       <c r="M66">
-        <v>25.1755008</v>
+        <v>25.568868</v>
       </c>
       <c r="N66">
-        <v>-11.5755008</v>
+        <v>-11.968868</v>
       </c>
       <c r="O66">
-        <v>-3.47265024</v>
+        <v>-3.5906604</v>
       </c>
       <c r="P66">
-        <v>-8.10285056</v>
+        <v>-8.3782076</v>
       </c>
       <c r="Q66">
-        <v>12.79714944</v>
+        <v>12.5217924</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1992645545822547</v>
+        <v>0.2036492561417477</v>
       </c>
       <c r="T66">
-        <v>2.233096260044416</v>
+        <v>2.296899010331399</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1620623173462353</v>
+        <v>0.159569050925524</v>
       </c>
       <c r="W66">
-        <v>0.168257886676876</v>
+        <v>0.1687585345741548</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5402077244874509</v>
+        <v>0.5318968364184132</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1809702871228123</v>
+        <v>0.1825202871228123</v>
       </c>
       <c r="C67">
-        <v>-12.54751282279075</v>
+        <v>-15.34217917529288</v>
       </c>
       <c r="D67">
-        <v>100.9874871772093</v>
+        <v>100.1518208247071</v>
       </c>
       <c r="E67">
-        <v>5.635000000000005</v>
+        <v>7.594000000000008</v>
       </c>
       <c r="F67">
-        <v>127.335</v>
+        <v>129.294</v>
       </c>
       <c r="G67">
         <v>13.8</v>
@@ -6775,37 +6775,37 @@
         <v>13.6</v>
       </c>
       <c r="M67">
-        <v>25.568868</v>
+        <v>25.9622352</v>
       </c>
       <c r="N67">
-        <v>-11.968868</v>
+        <v>-12.3622352</v>
       </c>
       <c r="O67">
-        <v>-3.5906604</v>
+        <v>-3.70867056</v>
       </c>
       <c r="P67">
-        <v>-8.3782076</v>
+        <v>-8.653564640000001</v>
       </c>
       <c r="Q67">
-        <v>12.5217924</v>
+        <v>12.24643536</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2036492561417477</v>
+        <v>0.2082918813223873</v>
       </c>
       <c r="T67">
-        <v>2.296899010331399</v>
+        <v>2.36445486357644</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.159569050925524</v>
+        <v>0.157151338032713</v>
       </c>
       <c r="W67">
-        <v>0.1687585345741548</v>
+        <v>0.1692440113230312</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5318968364184132</v>
+        <v>0.5238377934423766</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1825202871228123</v>
+        <v>0.1840702871228123</v>
       </c>
       <c r="C68">
-        <v>-15.34217917529288</v>
+        <v>-18.12312883903621</v>
       </c>
       <c r="D68">
-        <v>100.1518208247071</v>
+        <v>99.3298711609638</v>
       </c>
       <c r="E68">
-        <v>7.594000000000008</v>
+        <v>9.553000000000011</v>
       </c>
       <c r="F68">
-        <v>129.294</v>
+        <v>131.253</v>
       </c>
       <c r="G68">
         <v>13.8</v>
@@ -6857,37 +6857,37 @@
         <v>13.6</v>
       </c>
       <c r="M68">
-        <v>25.9622352</v>
+        <v>26.3556024</v>
       </c>
       <c r="N68">
-        <v>-12.3622352</v>
+        <v>-12.7556024</v>
       </c>
       <c r="O68">
-        <v>-3.70867056</v>
+        <v>-3.82668072</v>
       </c>
       <c r="P68">
-        <v>-8.653564640000001</v>
+        <v>-8.92892168</v>
       </c>
       <c r="Q68">
-        <v>12.24643536</v>
+        <v>11.97107832</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2082918813223873</v>
+        <v>0.213215877726096</v>
       </c>
       <c r="T68">
-        <v>2.36445486357644</v>
+        <v>2.436105010957545</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.157151338032713</v>
+        <v>0.1548057956740158</v>
       </c>
       <c r="W68">
-        <v>0.1692440113230312</v>
+        <v>0.1697149962286577</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5238377934423766</v>
+        <v>0.5160193189133859</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1840702871228123</v>
+        <v>0.1856202871228123</v>
       </c>
       <c r="C69">
-        <v>-18.12312883903621</v>
+        <v>-20.89069678500354</v>
       </c>
       <c r="D69">
-        <v>99.3298711609638</v>
+        <v>98.52130321499648</v>
       </c>
       <c r="E69">
-        <v>9.553000000000011</v>
+        <v>11.51200000000001</v>
       </c>
       <c r="F69">
-        <v>131.253</v>
+        <v>133.212</v>
       </c>
       <c r="G69">
         <v>13.8</v>
@@ -6939,37 +6939,37 @@
         <v>13.6</v>
       </c>
       <c r="M69">
-        <v>26.3556024</v>
+        <v>26.74896960000001</v>
       </c>
       <c r="N69">
-        <v>-12.7556024</v>
+        <v>-13.1489696</v>
       </c>
       <c r="O69">
-        <v>-3.82668072</v>
+        <v>-3.944690880000001</v>
       </c>
       <c r="P69">
-        <v>-8.92892168</v>
+        <v>-9.204278720000003</v>
       </c>
       <c r="Q69">
-        <v>11.97107832</v>
+        <v>11.69572128</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.213215877726096</v>
+        <v>0.2184476239050365</v>
       </c>
       <c r="T69">
-        <v>2.436105010957545</v>
+        <v>2.512233292549968</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1548057956740158</v>
+        <v>0.1525292398552802</v>
       </c>
       <c r="W69">
-        <v>0.1697149962286577</v>
+        <v>0.1701721286370597</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5160193189133859</v>
+        <v>0.5084307995176007</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1856202871228123</v>
+        <v>0.1871702871228123</v>
       </c>
       <c r="C70">
-        <v>-20.89069678500354</v>
+        <v>-23.64520716528327</v>
       </c>
       <c r="D70">
-        <v>98.52130321499648</v>
+        <v>97.72579283471676</v>
       </c>
       <c r="E70">
-        <v>11.51200000000001</v>
+        <v>13.47100000000002</v>
       </c>
       <c r="F70">
-        <v>133.212</v>
+        <v>135.171</v>
       </c>
       <c r="G70">
         <v>13.8</v>
@@ -7021,37 +7021,37 @@
         <v>13.6</v>
       </c>
       <c r="M70">
-        <v>26.74896960000001</v>
+        <v>27.14233680000001</v>
       </c>
       <c r="N70">
-        <v>-13.1489696</v>
+        <v>-13.5423368</v>
       </c>
       <c r="O70">
-        <v>-3.944690880000001</v>
+        <v>-4.062701040000001</v>
       </c>
       <c r="P70">
-        <v>-9.204278720000003</v>
+        <v>-9.479635760000004</v>
       </c>
       <c r="Q70">
-        <v>11.69572128</v>
+        <v>11.42036423999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2184476239050365</v>
+        <v>0.2240169020955216</v>
       </c>
       <c r="T70">
-        <v>2.512233292549968</v>
+        <v>2.593273076180612</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1525292398552802</v>
+        <v>0.1503186711617255</v>
       </c>
       <c r="W70">
-        <v>0.1701721286370597</v>
+        <v>0.1706160108307255</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5084307995176007</v>
+        <v>0.5010622372057515</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1871702871228123</v>
+        <v>0.2141692584357771</v>
       </c>
       <c r="C71">
-        <v>-23.64520716528327</v>
+        <v>-37.65426329248379</v>
       </c>
       <c r="D71">
-        <v>97.72579283471676</v>
+        <v>85.67573670751624</v>
       </c>
       <c r="E71">
-        <v>13.47100000000002</v>
+        <v>15.43000000000002</v>
       </c>
       <c r="F71">
-        <v>135.171</v>
+        <v>137.13</v>
       </c>
       <c r="G71">
         <v>13.8</v>
@@ -7103,45 +7103,45 @@
         <v>13.6</v>
       </c>
       <c r="M71">
-        <v>27.14233680000001</v>
+        <v>32.33525400000001</v>
       </c>
       <c r="N71">
-        <v>-13.5423368</v>
+        <v>-18.735254</v>
       </c>
       <c r="O71">
-        <v>-4.062701040000001</v>
+        <v>-5.620576200000001</v>
       </c>
       <c r="P71">
-        <v>-9.479635760000004</v>
+        <v>-13.1146778</v>
       </c>
       <c r="Q71">
-        <v>11.42036423999999</v>
+        <v>7.785322199999996</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2240169020955216</v>
+        <v>0.2331207032085881</v>
       </c>
       <c r="T71">
-        <v>2.593273076180612</v>
+        <v>2.725744475020014</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1503186711617255</v>
+        <v>0.126178071772685</v>
       </c>
       <c r="W71">
-        <v>0.1706160108307255</v>
+        <v>0.2060472106760009</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5010622372057515</v>
+        <v>0.4205935725756167</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2141692584357771</v>
+        <v>0.2160692584357771</v>
       </c>
       <c r="C72">
-        <v>-37.65426329248379</v>
+        <v>-40.35030461424849</v>
       </c>
       <c r="D72">
-        <v>85.67573670751624</v>
+        <v>84.93869538575154</v>
       </c>
       <c r="E72">
-        <v>15.43000000000002</v>
+        <v>17.38900000000002</v>
       </c>
       <c r="F72">
-        <v>137.13</v>
+        <v>139.089</v>
       </c>
       <c r="G72">
         <v>13.8</v>
@@ -7185,37 +7185,37 @@
         <v>13.6</v>
       </c>
       <c r="M72">
-        <v>32.33525400000001</v>
+        <v>32.79718620000001</v>
       </c>
       <c r="N72">
-        <v>-18.735254</v>
+        <v>-19.1971862</v>
       </c>
       <c r="O72">
-        <v>-5.620576200000001</v>
+        <v>-5.759155860000001</v>
       </c>
       <c r="P72">
-        <v>-13.1146778</v>
+        <v>-13.43803034</v>
       </c>
       <c r="Q72">
-        <v>7.785322199999996</v>
+        <v>7.461969659999994</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2331207032085881</v>
+        <v>0.2395800378019877</v>
       </c>
       <c r="T72">
-        <v>2.725744475020014</v>
+        <v>2.819735663813808</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.126178071772685</v>
+        <v>0.1244009158322246</v>
       </c>
       <c r="W72">
-        <v>0.2060472106760009</v>
+        <v>0.2064662640467614</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4205935725756167</v>
+        <v>0.4146697194407488</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.216069258435777</v>
+        <v>0.217969258435777</v>
       </c>
       <c r="C73">
-        <v>-40.35030461424843</v>
+        <v>-43.03377302903391</v>
       </c>
       <c r="D73">
-        <v>84.93869538575157</v>
+        <v>84.2142269709661</v>
       </c>
       <c r="E73">
-        <v>17.389</v>
+        <v>19.348</v>
       </c>
       <c r="F73">
-        <v>139.089</v>
+        <v>141.048</v>
       </c>
       <c r="G73">
         <v>13.8</v>
@@ -7267,37 +7267,37 @@
         <v>13.6</v>
       </c>
       <c r="M73">
-        <v>32.7971862</v>
+        <v>33.2591184</v>
       </c>
       <c r="N73">
-        <v>-19.1971862</v>
+        <v>-19.6591184</v>
       </c>
       <c r="O73">
-        <v>-5.759155859999999</v>
+        <v>-5.897735519999999</v>
       </c>
       <c r="P73">
-        <v>-13.43803034</v>
+        <v>-13.76138288</v>
       </c>
       <c r="Q73">
-        <v>7.461969660000001</v>
+        <v>7.138617119999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2395800378019876</v>
+        <v>0.2465007534377729</v>
       </c>
       <c r="T73">
-        <v>2.819735663813807</v>
+        <v>2.920440508950015</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1244009158322247</v>
+        <v>0.1226731253345549</v>
       </c>
       <c r="W73">
-        <v>0.2064662640467614</v>
+        <v>0.206873677046112</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4146697194407489</v>
+        <v>0.4089104177818497</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.217969258435777</v>
+        <v>0.219869258435777</v>
       </c>
       <c r="C74">
-        <v>-43.03377302903391</v>
+        <v>-45.70498753068482</v>
       </c>
       <c r="D74">
-        <v>84.2142269709661</v>
+        <v>83.50201246931519</v>
       </c>
       <c r="E74">
-        <v>19.348</v>
+        <v>21.307</v>
       </c>
       <c r="F74">
-        <v>141.048</v>
+        <v>143.007</v>
       </c>
       <c r="G74">
         <v>13.8</v>
@@ -7349,37 +7349,37 @@
         <v>13.6</v>
       </c>
       <c r="M74">
-        <v>33.2591184</v>
+        <v>33.72105060000001</v>
       </c>
       <c r="N74">
-        <v>-19.6591184</v>
+        <v>-20.1210506</v>
       </c>
       <c r="O74">
-        <v>-5.897735519999999</v>
+        <v>-6.036315180000001</v>
       </c>
       <c r="P74">
-        <v>-13.76138288</v>
+        <v>-14.08473542</v>
       </c>
       <c r="Q74">
-        <v>7.138617119999999</v>
+        <v>6.815264579999996</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2465007534377729</v>
+        <v>0.2539341146762089</v>
       </c>
       <c r="T74">
-        <v>2.920440508950015</v>
+        <v>3.028604972244459</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1226731253345549</v>
+        <v>0.1209926715628486</v>
       </c>
       <c r="W74">
-        <v>0.206873677046112</v>
+        <v>0.2072699280454803</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4089104177818497</v>
+        <v>0.4033089052094955</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.219869258435777</v>
+        <v>0.2217692584357771</v>
       </c>
       <c r="C75">
-        <v>-45.70498753068482</v>
+        <v>-48.36425641239532</v>
       </c>
       <c r="D75">
-        <v>83.50201246931519</v>
+        <v>82.80174358760469</v>
       </c>
       <c r="E75">
-        <v>21.307</v>
+        <v>23.26600000000001</v>
       </c>
       <c r="F75">
-        <v>143.007</v>
+        <v>144.966</v>
       </c>
       <c r="G75">
         <v>13.8</v>
@@ -7431,37 +7431,37 @@
         <v>13.6</v>
       </c>
       <c r="M75">
-        <v>33.72105060000001</v>
+        <v>34.1829828</v>
       </c>
       <c r="N75">
-        <v>-20.1210506</v>
+        <v>-20.5829828</v>
       </c>
       <c r="O75">
-        <v>-6.036315180000001</v>
+        <v>-6.174894840000001</v>
       </c>
       <c r="P75">
-        <v>-14.08473542</v>
+        <v>-14.40808796</v>
       </c>
       <c r="Q75">
-        <v>6.815264579999996</v>
+        <v>6.491912039999995</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2539341146762089</v>
+        <v>0.2619392729329862</v>
       </c>
       <c r="T75">
-        <v>3.028604972244459</v>
+        <v>3.145089778869246</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1209926715628486</v>
+        <v>0.119357635460648</v>
       </c>
       <c r="W75">
-        <v>0.2072699280454803</v>
+        <v>0.2076554695583792</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4033089052094955</v>
+        <v>0.3978587848688265</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2217692584357771</v>
+        <v>0.223669258435777</v>
       </c>
       <c r="C76">
-        <v>-48.36425641239532</v>
+        <v>-51.01187771166924</v>
       </c>
       <c r="D76">
-        <v>82.80174358760469</v>
+        <v>82.11312228833077</v>
       </c>
       <c r="E76">
-        <v>23.26600000000001</v>
+        <v>25.22500000000001</v>
       </c>
       <c r="F76">
-        <v>144.966</v>
+        <v>146.925</v>
       </c>
       <c r="G76">
         <v>13.8</v>
@@ -7513,37 +7513,37 @@
         <v>13.6</v>
       </c>
       <c r="M76">
-        <v>34.1829828</v>
+        <v>34.644915</v>
       </c>
       <c r="N76">
-        <v>-20.5829828</v>
+        <v>-21.044915</v>
       </c>
       <c r="O76">
-        <v>-6.174894840000001</v>
+        <v>-6.313474500000001</v>
       </c>
       <c r="P76">
-        <v>-14.40808796</v>
+        <v>-14.7314405</v>
       </c>
       <c r="Q76">
-        <v>6.491912039999995</v>
+        <v>6.168559499999997</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2619392729329862</v>
+        <v>0.2705848438503057</v>
       </c>
       <c r="T76">
-        <v>3.145089778869246</v>
+        <v>3.270893370024016</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.119357635460648</v>
+        <v>0.1177662003211727</v>
       </c>
       <c r="W76">
-        <v>0.2076554695583792</v>
+        <v>0.2080307299642675</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3978587848688265</v>
+        <v>0.3925540010705756</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.223669258435777</v>
+        <v>0.2255692584357771</v>
       </c>
       <c r="C77">
-        <v>-51.01187771166924</v>
+        <v>-53.64813963326034</v>
       </c>
       <c r="D77">
-        <v>82.11312228833077</v>
+        <v>81.43586036673967</v>
       </c>
       <c r="E77">
-        <v>25.22500000000001</v>
+        <v>27.18400000000001</v>
       </c>
       <c r="F77">
-        <v>146.925</v>
+        <v>148.884</v>
       </c>
       <c r="G77">
         <v>13.8</v>
@@ -7595,37 +7595,37 @@
         <v>13.6</v>
       </c>
       <c r="M77">
-        <v>34.644915</v>
+        <v>35.1068472</v>
       </c>
       <c r="N77">
-        <v>-21.044915</v>
+        <v>-21.5068472</v>
       </c>
       <c r="O77">
-        <v>-6.313474500000001</v>
+        <v>-6.45205416</v>
       </c>
       <c r="P77">
-        <v>-14.7314405</v>
+        <v>-15.05479304</v>
       </c>
       <c r="Q77">
-        <v>6.168559499999997</v>
+        <v>5.845206959999995</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2705848438503057</v>
+        <v>0.2799508790107351</v>
       </c>
       <c r="T77">
-        <v>3.270893370024016</v>
+        <v>3.407180593775017</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1177662003211727</v>
+        <v>0.1162166450537888</v>
       </c>
       <c r="W77">
-        <v>0.2080307299642675</v>
+        <v>0.2083961150963166</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3925540010705756</v>
+        <v>0.3873888168459627</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2255692584357771</v>
+        <v>0.227469258435777</v>
       </c>
       <c r="C78">
-        <v>-53.64813963326034</v>
+        <v>-56.27332095135345</v>
       </c>
       <c r="D78">
-        <v>81.43586036673967</v>
+        <v>80.76967904864657</v>
       </c>
       <c r="E78">
-        <v>27.18400000000001</v>
+        <v>29.14300000000001</v>
       </c>
       <c r="F78">
-        <v>148.884</v>
+        <v>150.843</v>
       </c>
       <c r="G78">
         <v>13.8</v>
@@ -7677,37 +7677,37 @@
         <v>13.6</v>
       </c>
       <c r="M78">
-        <v>35.1068472</v>
+        <v>35.5687794</v>
       </c>
       <c r="N78">
-        <v>-21.5068472</v>
+        <v>-21.9687794</v>
       </c>
       <c r="O78">
-        <v>-6.45205416</v>
+        <v>-6.590633820000001</v>
       </c>
       <c r="P78">
-        <v>-15.05479304</v>
+        <v>-15.37814558</v>
       </c>
       <c r="Q78">
-        <v>5.845206959999995</v>
+        <v>5.521854419999997</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2799508790107351</v>
+        <v>0.2901313520112018</v>
       </c>
       <c r="T78">
-        <v>3.407180593775017</v>
+        <v>3.555318880460888</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1162166450537888</v>
+        <v>0.1147073379751682</v>
       </c>
       <c r="W78">
-        <v>0.2083961150963166</v>
+        <v>0.2087520097054553</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3873888168459627</v>
+        <v>0.3823577932505606</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.227469258435777</v>
+        <v>0.2293692584357771</v>
       </c>
       <c r="C79">
-        <v>-56.27332095135345</v>
+        <v>-58.88769139216585</v>
       </c>
       <c r="D79">
-        <v>80.76967904864657</v>
+        <v>80.11430860783418</v>
       </c>
       <c r="E79">
-        <v>29.14300000000001</v>
+        <v>31.10200000000002</v>
       </c>
       <c r="F79">
-        <v>150.843</v>
+        <v>152.802</v>
       </c>
       <c r="G79">
         <v>13.8</v>
@@ -7759,37 +7759,37 @@
         <v>13.6</v>
       </c>
       <c r="M79">
-        <v>35.5687794</v>
+        <v>36.0307116</v>
       </c>
       <c r="N79">
-        <v>-21.9687794</v>
+        <v>-22.4307116</v>
       </c>
       <c r="O79">
-        <v>-6.590633820000001</v>
+        <v>-6.72921348</v>
       </c>
       <c r="P79">
-        <v>-15.37814558</v>
+        <v>-15.70149812</v>
       </c>
       <c r="Q79">
-        <v>5.521854419999997</v>
+        <v>5.198501879999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2901313520112018</v>
+        <v>0.3012373225571656</v>
       </c>
       <c r="T79">
-        <v>3.555318880460888</v>
+        <v>3.716924284118202</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1147073379751682</v>
+        <v>0.1132367310780507</v>
       </c>
       <c r="W79">
-        <v>0.2087520097054553</v>
+        <v>0.2090987788117957</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3823577932505606</v>
+        <v>0.3774557702601689</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2293692584357771</v>
+        <v>0.2312692584357771</v>
       </c>
       <c r="C80">
-        <v>-58.88769139216585</v>
+        <v>-61.49151199807154</v>
       </c>
       <c r="D80">
-        <v>80.11430860783418</v>
+        <v>79.46948800192848</v>
       </c>
       <c r="E80">
-        <v>31.10200000000002</v>
+        <v>33.06100000000002</v>
       </c>
       <c r="F80">
-        <v>152.802</v>
+        <v>154.761</v>
       </c>
       <c r="G80">
         <v>13.8</v>
@@ -7841,37 +7841,37 @@
         <v>13.6</v>
       </c>
       <c r="M80">
-        <v>36.0307116</v>
+        <v>36.49264380000001</v>
       </c>
       <c r="N80">
-        <v>-22.4307116</v>
+        <v>-22.89264380000001</v>
       </c>
       <c r="O80">
-        <v>-6.72921348</v>
+        <v>-6.867793140000003</v>
       </c>
       <c r="P80">
-        <v>-15.70149812</v>
+        <v>-16.02485066000001</v>
       </c>
       <c r="Q80">
-        <v>5.198501879999997</v>
+        <v>4.875149339999993</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3012373225571656</v>
+        <v>0.3134010045836973</v>
       </c>
       <c r="T80">
-        <v>3.716924284118202</v>
+        <v>3.893920678600021</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1132367310780507</v>
+        <v>0.1118033547352905</v>
       </c>
       <c r="W80">
-        <v>0.2090987788117957</v>
+        <v>0.2094367689534185</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3774557702601689</v>
+        <v>0.372677849117635</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2312692584357771</v>
+        <v>0.233169258435777</v>
       </c>
       <c r="C81">
-        <v>-61.49151199807154</v>
+        <v>-64.08503547428185</v>
       </c>
       <c r="D81">
-        <v>79.46948800192848</v>
+        <v>78.83496452571818</v>
       </c>
       <c r="E81">
-        <v>33.06100000000002</v>
+        <v>35.02000000000002</v>
       </c>
       <c r="F81">
-        <v>154.761</v>
+        <v>156.72</v>
       </c>
       <c r="G81">
         <v>13.8</v>
@@ -7923,37 +7923,37 @@
         <v>13.6</v>
       </c>
       <c r="M81">
-        <v>36.49264380000001</v>
+        <v>36.95457600000001</v>
       </c>
       <c r="N81">
-        <v>-22.89264380000001</v>
+        <v>-23.35457600000001</v>
       </c>
       <c r="O81">
-        <v>-6.867793140000003</v>
+        <v>-7.006372800000002</v>
       </c>
       <c r="P81">
-        <v>-16.02485066000001</v>
+        <v>-16.34820320000001</v>
       </c>
       <c r="Q81">
-        <v>4.875149339999993</v>
+        <v>4.551796799999991</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3134010045836973</v>
+        <v>0.3267810548128822</v>
       </c>
       <c r="T81">
-        <v>3.893920678600021</v>
+        <v>4.088616712530022</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1118033547352905</v>
+        <v>0.1104058128010994</v>
       </c>
       <c r="W81">
-        <v>0.2094367689534185</v>
+        <v>0.2097663093415008</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.372677849117635</v>
+        <v>0.3680193760036645</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.233169258435777</v>
+        <v>0.2350692584357771</v>
       </c>
       <c r="C82">
-        <v>-64.08503547428185</v>
+        <v>-66.66850651904879</v>
       </c>
       <c r="D82">
-        <v>78.83496452571818</v>
+        <v>78.21049348095121</v>
       </c>
       <c r="E82">
-        <v>35.02000000000002</v>
+        <v>36.979</v>
       </c>
       <c r="F82">
-        <v>156.72</v>
+        <v>158.679</v>
       </c>
       <c r="G82">
         <v>13.8</v>
@@ -8005,37 +8005,37 @@
         <v>13.6</v>
       </c>
       <c r="M82">
-        <v>36.95457600000001</v>
+        <v>37.4165082</v>
       </c>
       <c r="N82">
-        <v>-23.35457600000001</v>
+        <v>-23.8165082</v>
       </c>
       <c r="O82">
-        <v>-7.006372800000002</v>
+        <v>-7.14495246</v>
       </c>
       <c r="P82">
-        <v>-16.34820320000001</v>
+        <v>-16.67155574</v>
       </c>
       <c r="Q82">
-        <v>4.551796799999991</v>
+        <v>4.228444259999996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3267810548128822</v>
+        <v>0.3415695313819813</v>
       </c>
       <c r="T82">
-        <v>4.088616712530022</v>
+        <v>4.303807065821076</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1104058128010994</v>
+        <v>0.1090427780751599</v>
       </c>
       <c r="W82">
-        <v>0.2097663093415008</v>
+        <v>0.2100877129298773</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3680193760036645</v>
+        <v>0.3634759269171997</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2350692584357771</v>
+        <v>0.236969258435777</v>
       </c>
       <c r="C83">
-        <v>-66.66850651904879</v>
+        <v>-69.24216213829821</v>
       </c>
       <c r="D83">
-        <v>78.21049348095121</v>
+        <v>77.5958378617018</v>
       </c>
       <c r="E83">
-        <v>36.979</v>
+        <v>38.938</v>
       </c>
       <c r="F83">
-        <v>158.679</v>
+        <v>160.638</v>
       </c>
       <c r="G83">
         <v>13.8</v>
@@ -8087,37 +8087,37 @@
         <v>13.6</v>
       </c>
       <c r="M83">
-        <v>37.4165082</v>
+        <v>37.8784404</v>
       </c>
       <c r="N83">
-        <v>-23.8165082</v>
+        <v>-24.2784404</v>
       </c>
       <c r="O83">
-        <v>-7.14495246</v>
+        <v>-7.28353212</v>
       </c>
       <c r="P83">
-        <v>-16.67155574</v>
+        <v>-16.99490828</v>
       </c>
       <c r="Q83">
-        <v>4.228444259999996</v>
+        <v>3.905091719999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3415695313819813</v>
+        <v>0.3580011720143135</v>
       </c>
       <c r="T83">
-        <v>4.303807065821076</v>
+        <v>4.542907458366691</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1090427780751599</v>
+        <v>0.1077129880986336</v>
       </c>
       <c r="W83">
-        <v>0.2100877129298773</v>
+        <v>0.2104012774063422</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3634759269171997</v>
+        <v>0.3590432936621119</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.236969258435777</v>
+        <v>0.2388692584357771</v>
       </c>
       <c r="C84">
-        <v>-69.24216213829821</v>
+        <v>-71.80623194554254</v>
       </c>
       <c r="D84">
-        <v>77.5958378617018</v>
+        <v>76.99076805445748</v>
       </c>
       <c r="E84">
-        <v>38.938</v>
+        <v>40.89700000000001</v>
       </c>
       <c r="F84">
-        <v>160.638</v>
+        <v>162.597</v>
       </c>
       <c r="G84">
         <v>13.8</v>
@@ -8169,37 +8169,37 @@
         <v>13.6</v>
       </c>
       <c r="M84">
-        <v>37.8784404</v>
+        <v>38.3403726</v>
       </c>
       <c r="N84">
-        <v>-24.2784404</v>
+        <v>-24.7403726</v>
       </c>
       <c r="O84">
-        <v>-7.28353212</v>
+        <v>-7.42211178</v>
       </c>
       <c r="P84">
-        <v>-16.99490828</v>
+        <v>-17.31826082</v>
       </c>
       <c r="Q84">
-        <v>3.905091719999998</v>
+        <v>3.58173918</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3580011720143135</v>
+        <v>0.376365946838685</v>
       </c>
       <c r="T84">
-        <v>4.542907458366691</v>
+        <v>4.81013730885885</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1077129880986336</v>
+        <v>0.1064152412540717</v>
       </c>
       <c r="W84">
-        <v>0.2104012774063422</v>
+        <v>0.2107072861122899</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3590432936621119</v>
+        <v>0.3547174708469056</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2388692584357771</v>
+        <v>0.2407692584357771</v>
       </c>
       <c r="C85">
-        <v>-71.80623194554254</v>
+        <v>-74.36093844787003</v>
       </c>
       <c r="D85">
-        <v>76.99076805445748</v>
+        <v>76.39506155212999</v>
       </c>
       <c r="E85">
-        <v>40.89700000000001</v>
+        <v>42.85600000000001</v>
       </c>
       <c r="F85">
-        <v>162.597</v>
+        <v>164.556</v>
       </c>
       <c r="G85">
         <v>13.8</v>
@@ -8251,37 +8251,37 @@
         <v>13.6</v>
       </c>
       <c r="M85">
-        <v>38.3403726</v>
+        <v>38.8023048</v>
       </c>
       <c r="N85">
-        <v>-24.7403726</v>
+        <v>-25.2023048</v>
       </c>
       <c r="O85">
-        <v>-7.42211178</v>
+        <v>-7.560691439999999</v>
       </c>
       <c r="P85">
-        <v>-17.31826082</v>
+        <v>-17.64161336</v>
       </c>
       <c r="Q85">
-        <v>3.58173918</v>
+        <v>3.258386639999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.376365946838685</v>
+        <v>0.3970263185161028</v>
       </c>
       <c r="T85">
-        <v>4.81013730885885</v>
+        <v>5.110770890662529</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1064152412540717</v>
+        <v>0.1051483931439042</v>
       </c>
       <c r="W85">
-        <v>0.2107072861122899</v>
+        <v>0.2110060088966674</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3547174708469056</v>
+        <v>0.350494643813014</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2407692584357771</v>
+        <v>0.242669258435777</v>
       </c>
       <c r="C86">
-        <v>-74.36093844787003</v>
+        <v>-76.90649731875932</v>
       </c>
       <c r="D86">
-        <v>76.39506155212999</v>
+        <v>75.80850268124067</v>
       </c>
       <c r="E86">
-        <v>42.85600000000001</v>
+        <v>44.81499999999998</v>
       </c>
       <c r="F86">
-        <v>164.556</v>
+        <v>166.515</v>
       </c>
       <c r="G86">
         <v>13.8</v>
@@ -8333,37 +8333,37 @@
         <v>13.6</v>
       </c>
       <c r="M86">
-        <v>38.8023048</v>
+        <v>39.264237</v>
       </c>
       <c r="N86">
-        <v>-25.2023048</v>
+        <v>-25.664237</v>
       </c>
       <c r="O86">
-        <v>-7.560691439999999</v>
+        <v>-7.6992711</v>
       </c>
       <c r="P86">
-        <v>-17.64161336</v>
+        <v>-17.9649659</v>
       </c>
       <c r="Q86">
-        <v>3.258386639999998</v>
+        <v>2.935034099999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3970263185161026</v>
+        <v>0.420441406417176</v>
       </c>
       <c r="T86">
-        <v>5.110770890662526</v>
+        <v>5.451488950040027</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1051483931439042</v>
+        <v>0.1039113532245641</v>
       </c>
       <c r="W86">
-        <v>0.2110060088966674</v>
+        <v>0.2112977029096478</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.350494643813014</v>
+        <v>0.3463711774152137</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.242669258435777</v>
+        <v>0.244569258435777</v>
       </c>
       <c r="C87">
-        <v>-76.90649731875932</v>
+        <v>-79.4431176584219</v>
       </c>
       <c r="D87">
-        <v>75.80850268124067</v>
+        <v>75.23088234157809</v>
       </c>
       <c r="E87">
-        <v>44.81499999999998</v>
+        <v>46.77399999999999</v>
       </c>
       <c r="F87">
-        <v>166.515</v>
+        <v>168.474</v>
       </c>
       <c r="G87">
         <v>13.8</v>
@@ -8415,37 +8415,37 @@
         <v>13.6</v>
       </c>
       <c r="M87">
-        <v>39.264237</v>
+        <v>39.7261692</v>
       </c>
       <c r="N87">
-        <v>-25.664237</v>
+        <v>-26.1261692</v>
       </c>
       <c r="O87">
-        <v>-7.6992711</v>
+        <v>-7.837850759999999</v>
       </c>
       <c r="P87">
-        <v>-17.9649659</v>
+        <v>-18.28831844</v>
       </c>
       <c r="Q87">
-        <v>2.935034099999999</v>
+        <v>2.611681559999997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.420441406417176</v>
+        <v>0.4472015068755458</v>
       </c>
       <c r="T87">
-        <v>5.451488950040027</v>
+        <v>5.840881017900029</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1039113532245641</v>
+        <v>0.1027030816754413</v>
       </c>
       <c r="W87">
-        <v>0.2112977029096478</v>
+        <v>0.211582613340931</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3463711774152137</v>
+        <v>0.3423436055848044</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.244569258435777</v>
+        <v>0.246469258435777</v>
       </c>
       <c r="C88">
-        <v>-79.4431176584219</v>
+        <v>-81.97100224233209</v>
       </c>
       <c r="D88">
-        <v>75.23088234157809</v>
+        <v>74.6619977576679</v>
       </c>
       <c r="E88">
-        <v>46.77399999999999</v>
+        <v>48.73299999999999</v>
       </c>
       <c r="F88">
-        <v>168.474</v>
+        <v>170.433</v>
       </c>
       <c r="G88">
         <v>13.8</v>
@@ -8497,37 +8497,37 @@
         <v>13.6</v>
       </c>
       <c r="M88">
-        <v>39.7261692</v>
+        <v>40.1881014</v>
       </c>
       <c r="N88">
-        <v>-26.1261692</v>
+        <v>-26.5881014</v>
       </c>
       <c r="O88">
-        <v>-7.837850759999999</v>
+        <v>-7.97643042</v>
       </c>
       <c r="P88">
-        <v>-18.28831844</v>
+        <v>-18.61167098</v>
       </c>
       <c r="Q88">
-        <v>2.611681559999997</v>
+        <v>2.288329019999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4472015068755458</v>
+        <v>0.4780785458659724</v>
       </c>
       <c r="T88">
-        <v>5.840881017900029</v>
+        <v>6.290179557738493</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1027030816754413</v>
+        <v>0.1015225864837696</v>
       </c>
       <c r="W88">
-        <v>0.211582613340931</v>
+        <v>0.2118609741071271</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3423436055848044</v>
+        <v>0.3384086216125651</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.246469258435777</v>
+        <v>0.2483692584357771</v>
       </c>
       <c r="C89">
-        <v>-81.97100224233209</v>
+        <v>-84.49034775856602</v>
       </c>
       <c r="D89">
-        <v>74.6619977576679</v>
+        <v>74.10165224143398</v>
       </c>
       <c r="E89">
-        <v>48.73299999999999</v>
+        <v>50.69199999999999</v>
       </c>
       <c r="F89">
-        <v>170.433</v>
+        <v>172.392</v>
       </c>
       <c r="G89">
         <v>13.8</v>
@@ -8579,37 +8579,37 @@
         <v>13.6</v>
       </c>
       <c r="M89">
-        <v>40.1881014</v>
+        <v>40.6500336</v>
       </c>
       <c r="N89">
-        <v>-26.5881014</v>
+        <v>-27.0500336</v>
       </c>
       <c r="O89">
-        <v>-7.97643042</v>
+        <v>-8.115010079999999</v>
       </c>
       <c r="P89">
-        <v>-18.61167098</v>
+        <v>-18.93502352</v>
       </c>
       <c r="Q89">
-        <v>2.288329019999999</v>
+        <v>1.964976479999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4780785458659724</v>
+        <v>0.5141017580214702</v>
       </c>
       <c r="T89">
-        <v>6.290179557738493</v>
+        <v>6.814361187550035</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1015225864837696</v>
+        <v>0.1003689207282722</v>
       </c>
       <c r="W89">
-        <v>0.2118609741071271</v>
+        <v>0.2121330084922734</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3384086216125651</v>
+        <v>0.3345630690942406</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2483692584357771</v>
+        <v>0.250269258435777</v>
       </c>
       <c r="C90">
-        <v>-84.49034775856602</v>
+        <v>-87.00134503453253</v>
       </c>
       <c r="D90">
-        <v>74.10165224143398</v>
+        <v>73.54965496546747</v>
       </c>
       <c r="E90">
-        <v>50.69199999999999</v>
+        <v>52.651</v>
       </c>
       <c r="F90">
-        <v>172.392</v>
+        <v>174.351</v>
       </c>
       <c r="G90">
         <v>13.8</v>
@@ -8661,37 +8661,37 @@
         <v>13.6</v>
       </c>
       <c r="M90">
-        <v>40.6500336</v>
+        <v>41.1119658</v>
       </c>
       <c r="N90">
-        <v>-27.0500336</v>
+        <v>-27.5119658</v>
       </c>
       <c r="O90">
-        <v>-8.115010079999999</v>
+        <v>-8.253589739999999</v>
       </c>
       <c r="P90">
-        <v>-18.93502352</v>
+        <v>-19.25837606</v>
       </c>
       <c r="Q90">
-        <v>1.964976479999997</v>
+        <v>1.641623939999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5141017580214702</v>
+        <v>0.5566746451143312</v>
       </c>
       <c r="T90">
-        <v>6.814361187550035</v>
+        <v>7.433848568236403</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1003689207282722</v>
+        <v>0.09924118004593203</v>
       </c>
       <c r="W90">
-        <v>0.2121330084922734</v>
+        <v>0.2123989297451692</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3345630690942406</v>
+        <v>0.3308039334864401</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.250269258435777</v>
+        <v>0.252169258435777</v>
       </c>
       <c r="C91">
-        <v>-87.00134503453253</v>
+        <v>-89.50417925364532</v>
       </c>
       <c r="D91">
-        <v>73.54965496546747</v>
+        <v>73.00582074635469</v>
       </c>
       <c r="E91">
-        <v>52.651</v>
+        <v>54.61</v>
       </c>
       <c r="F91">
-        <v>174.351</v>
+        <v>176.31</v>
       </c>
       <c r="G91">
         <v>13.8</v>
@@ -8743,37 +8743,37 @@
         <v>13.6</v>
       </c>
       <c r="M91">
-        <v>41.1119658</v>
+        <v>41.573898</v>
       </c>
       <c r="N91">
-        <v>-27.5119658</v>
+        <v>-27.973898</v>
       </c>
       <c r="O91">
-        <v>-8.253589739999999</v>
+        <v>-8.392169399999998</v>
       </c>
       <c r="P91">
-        <v>-19.25837606</v>
+        <v>-19.5817286</v>
       </c>
       <c r="Q91">
-        <v>1.641623939999999</v>
+        <v>1.3182714</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5566746451143312</v>
+        <v>0.6077621096257643</v>
       </c>
       <c r="T91">
-        <v>7.433848568236403</v>
+        <v>8.177233425060043</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09924118004593203</v>
+        <v>0.09813850026764391</v>
       </c>
       <c r="W91">
-        <v>0.2123989297451692</v>
+        <v>0.2126589416368896</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3308039334864401</v>
+        <v>0.3271283342254797</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.252169258435777</v>
+        <v>0.254069258435777</v>
       </c>
       <c r="C92">
-        <v>-89.50417925364532</v>
+        <v>-91.9990301624529</v>
       </c>
       <c r="D92">
-        <v>73.00582074635469</v>
+        <v>72.46996983754711</v>
       </c>
       <c r="E92">
-        <v>54.61</v>
+        <v>56.569</v>
       </c>
       <c r="F92">
-        <v>176.31</v>
+        <v>178.269</v>
       </c>
       <c r="G92">
         <v>13.8</v>
@@ -8825,37 +8825,37 @@
         <v>13.6</v>
       </c>
       <c r="M92">
-        <v>41.573898</v>
+        <v>42.0358302</v>
       </c>
       <c r="N92">
-        <v>-27.973898</v>
+        <v>-28.4358302</v>
       </c>
       <c r="O92">
-        <v>-8.392169399999998</v>
+        <v>-8.53074906</v>
       </c>
       <c r="P92">
-        <v>-19.5817286</v>
+        <v>-19.90508114</v>
       </c>
       <c r="Q92">
-        <v>1.3182714</v>
+        <v>0.9949188599999985</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6077621096257643</v>
+        <v>0.670202344028627</v>
       </c>
       <c r="T92">
-        <v>8.177233425060043</v>
+        <v>9.085814916733382</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09813850026764391</v>
+        <v>0.09706005520975772</v>
       </c>
       <c r="W92">
-        <v>0.2126589416368896</v>
+        <v>0.2129132389815391</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3271283342254797</v>
+        <v>0.323533517365859</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.254069258435777</v>
+        <v>0.2559692584357771</v>
       </c>
       <c r="C93">
-        <v>-91.9990301624529</v>
+        <v>-94.48607226871339</v>
       </c>
       <c r="D93">
-        <v>72.46996983754711</v>
+        <v>71.94192773128663</v>
       </c>
       <c r="E93">
-        <v>56.569</v>
+        <v>58.52800000000001</v>
       </c>
       <c r="F93">
-        <v>178.269</v>
+        <v>180.228</v>
       </c>
       <c r="G93">
         <v>13.8</v>
@@ -8907,37 +8907,37 @@
         <v>13.6</v>
       </c>
       <c r="M93">
-        <v>42.0358302</v>
+        <v>42.49776240000001</v>
       </c>
       <c r="N93">
-        <v>-28.4358302</v>
+        <v>-28.8977624</v>
       </c>
       <c r="O93">
-        <v>-8.53074906</v>
+        <v>-8.669328720000001</v>
       </c>
       <c r="P93">
-        <v>-19.90508114</v>
+        <v>-20.22843368</v>
       </c>
       <c r="Q93">
-        <v>0.9949188599999985</v>
+        <v>0.6715663199999966</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.670202344028627</v>
+        <v>0.7482526370322056</v>
       </c>
       <c r="T93">
-        <v>9.085814916733382</v>
+        <v>10.22154178132506</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09706005520975772</v>
+        <v>0.09600505460965163</v>
       </c>
       <c r="W93">
-        <v>0.2129132389815391</v>
+        <v>0.2131620081230442</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.323533517365859</v>
+        <v>0.3200168486988387</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2559692584357771</v>
+        <v>0.257869258435777</v>
       </c>
       <c r="C94">
-        <v>-94.48607226871339</v>
+        <v>-96.96547503087228</v>
       </c>
       <c r="D94">
-        <v>71.94192773128663</v>
+        <v>71.42152496912773</v>
       </c>
       <c r="E94">
-        <v>58.52800000000001</v>
+        <v>60.48700000000001</v>
       </c>
       <c r="F94">
-        <v>180.228</v>
+        <v>182.187</v>
       </c>
       <c r="G94">
         <v>13.8</v>
@@ -8989,37 +8989,37 @@
         <v>13.6</v>
       </c>
       <c r="M94">
-        <v>42.49776240000001</v>
+        <v>42.95969460000001</v>
       </c>
       <c r="N94">
-        <v>-28.8977624</v>
+        <v>-29.3596946</v>
       </c>
       <c r="O94">
-        <v>-8.669328720000001</v>
+        <v>-8.807908380000001</v>
       </c>
       <c r="P94">
-        <v>-20.22843368</v>
+        <v>-20.55178622</v>
       </c>
       <c r="Q94">
-        <v>0.6715663199999966</v>
+        <v>0.3482137799999947</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7482526370322056</v>
+        <v>0.8486030137510922</v>
       </c>
       <c r="T94">
-        <v>10.22154178132506</v>
+        <v>11.68176203580007</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09600505460965163</v>
+        <v>0.09497274219449409</v>
       </c>
       <c r="W94">
-        <v>0.2131620081230442</v>
+        <v>0.2134054273905383</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3200168486988387</v>
+        <v>0.3165758073149803</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.257869258435777</v>
+        <v>0.259769258435777</v>
       </c>
       <c r="C95">
-        <v>-96.96547503087228</v>
+        <v>-99.43740303937594</v>
       </c>
       <c r="D95">
-        <v>71.42152496912773</v>
+        <v>70.90859696062408</v>
       </c>
       <c r="E95">
-        <v>60.48700000000001</v>
+        <v>62.44600000000001</v>
       </c>
       <c r="F95">
-        <v>182.187</v>
+        <v>184.146</v>
       </c>
       <c r="G95">
         <v>13.8</v>
@@ -9071,37 +9071,37 @@
         <v>13.6</v>
       </c>
       <c r="M95">
-        <v>42.95969460000001</v>
+        <v>43.42162680000001</v>
       </c>
       <c r="N95">
-        <v>-29.3596946</v>
+        <v>-29.8216268</v>
       </c>
       <c r="O95">
-        <v>-8.807908380000001</v>
+        <v>-8.94648804</v>
       </c>
       <c r="P95">
-        <v>-20.55178622</v>
+        <v>-20.87513876000001</v>
       </c>
       <c r="Q95">
-        <v>0.3482137799999947</v>
+        <v>0.02486123999999279</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8486030137510922</v>
+        <v>0.9824035160429412</v>
       </c>
       <c r="T95">
-        <v>11.68176203580007</v>
+        <v>13.62872237510008</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09497274219449409</v>
+        <v>0.09396239387327607</v>
       </c>
       <c r="W95">
-        <v>0.2134054273905383</v>
+        <v>0.2136436675246815</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3165758073149803</v>
+        <v>0.3132079795775868</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.259769258435777</v>
+        <v>0.261669258435777</v>
       </c>
       <c r="C96">
-        <v>-99.43740303937594</v>
+        <v>-101.9020161902275</v>
       </c>
       <c r="D96">
-        <v>70.90859696062408</v>
+        <v>70.40298380977255</v>
       </c>
       <c r="E96">
-        <v>62.44600000000001</v>
+        <v>64.40500000000002</v>
       </c>
       <c r="F96">
-        <v>184.146</v>
+        <v>186.105</v>
       </c>
       <c r="G96">
         <v>13.8</v>
@@ -9153,37 +9153,37 @@
         <v>13.6</v>
       </c>
       <c r="M96">
-        <v>43.42162680000001</v>
+        <v>43.88355900000001</v>
       </c>
       <c r="N96">
-        <v>-29.8216268</v>
+        <v>-30.283559</v>
       </c>
       <c r="O96">
-        <v>-8.94648804</v>
+        <v>-9.085067700000002</v>
       </c>
       <c r="P96">
-        <v>-20.87513876000001</v>
+        <v>-21.1984913</v>
       </c>
       <c r="Q96">
-        <v>0.02486123999999279</v>
+        <v>-0.298491300000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9824035160429412</v>
+        <v>1.16972421925153</v>
       </c>
       <c r="T96">
-        <v>13.62872237510008</v>
+        <v>16.3544668501201</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09396239387327607</v>
+        <v>0.09297331604303105</v>
       </c>
       <c r="W96">
-        <v>0.2136436675246815</v>
+        <v>0.2138768920770533</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3132079795775868</v>
+        <v>0.3099110534767702</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.261669258435777</v>
+        <v>0.2635692584357771</v>
       </c>
       <c r="C97">
-        <v>-101.9020161902275</v>
+        <v>-104.3594698511703</v>
       </c>
       <c r="D97">
-        <v>70.40298380977255</v>
+        <v>69.90453014882969</v>
       </c>
       <c r="E97">
-        <v>64.40500000000002</v>
+        <v>66.36400000000002</v>
       </c>
       <c r="F97">
-        <v>186.105</v>
+        <v>188.064</v>
       </c>
       <c r="G97">
         <v>13.8</v>
@@ -9235,37 +9235,37 @@
         <v>13.6</v>
       </c>
       <c r="M97">
-        <v>43.88355900000001</v>
+        <v>44.3454912</v>
       </c>
       <c r="N97">
-        <v>-30.283559</v>
+        <v>-30.7454912</v>
       </c>
       <c r="O97">
-        <v>-9.085067700000002</v>
+        <v>-9.223647360000001</v>
       </c>
       <c r="P97">
-        <v>-21.1984913</v>
+        <v>-21.52184384</v>
       </c>
       <c r="Q97">
-        <v>-0.298491300000002</v>
+        <v>-0.6218438400000039</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.16972421925153</v>
+        <v>1.450705274064413</v>
       </c>
       <c r="T97">
-        <v>16.3544668501201</v>
+        <v>20.44308356265014</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09297331604303105</v>
+        <v>0.09200484400091616</v>
       </c>
       <c r="W97">
-        <v>0.2138768920770533</v>
+        <v>0.214105257784584</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3099110534767702</v>
+        <v>0.3066828133363871</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2635692584357771</v>
+        <v>0.2654692584357771</v>
       </c>
       <c r="C98">
-        <v>-104.3594698511703</v>
+        <v>-106.8099150208619</v>
       </c>
       <c r="D98">
-        <v>69.90453014882969</v>
+        <v>69.41308497913809</v>
       </c>
       <c r="E98">
-        <v>66.36399999999999</v>
+        <v>68.32299999999999</v>
       </c>
       <c r="F98">
-        <v>188.064</v>
+        <v>190.023</v>
       </c>
       <c r="G98">
         <v>13.8</v>
@@ -9317,37 +9317,37 @@
         <v>13.6</v>
       </c>
       <c r="M98">
-        <v>44.3454912</v>
+        <v>44.8074234</v>
       </c>
       <c r="N98">
-        <v>-30.7454912</v>
+        <v>-31.2074234</v>
       </c>
       <c r="O98">
-        <v>-9.223647359999999</v>
+        <v>-9.362227019999999</v>
       </c>
       <c r="P98">
-        <v>-21.52184384</v>
+        <v>-21.84519638</v>
       </c>
       <c r="Q98">
-        <v>-0.6218438399999968</v>
+        <v>-0.9451963799999987</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.45070527406441</v>
+        <v>1.919007032085879</v>
       </c>
       <c r="T98">
-        <v>20.44308356265009</v>
+        <v>27.25744475020012</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09200484400091616</v>
+        <v>0.09105634045451497</v>
       </c>
       <c r="W98">
-        <v>0.214105257784584</v>
+        <v>0.2143289149208254</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3066828133363872</v>
+        <v>0.3035211348483833</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2654692584357771</v>
+        <v>0.267369258435777</v>
       </c>
       <c r="C99">
-        <v>-106.8099150208619</v>
+        <v>-109.2534984813799</v>
       </c>
       <c r="D99">
-        <v>69.41308497913809</v>
+        <v>68.92850151862007</v>
       </c>
       <c r="E99">
-        <v>68.32299999999999</v>
+        <v>70.282</v>
       </c>
       <c r="F99">
-        <v>190.023</v>
+        <v>191.982</v>
       </c>
       <c r="G99">
         <v>13.8</v>
@@ -9399,37 +9399,37 @@
         <v>13.6</v>
       </c>
       <c r="M99">
-        <v>44.8074234</v>
+        <v>45.2693556</v>
       </c>
       <c r="N99">
-        <v>-31.2074234</v>
+        <v>-31.6693556</v>
       </c>
       <c r="O99">
-        <v>-9.362227019999999</v>
+        <v>-9.50080668</v>
       </c>
       <c r="P99">
-        <v>-21.84519638</v>
+        <v>-22.16854892</v>
       </c>
       <c r="Q99">
-        <v>-0.9451963799999987</v>
+        <v>-1.268548920000004</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.919007032085879</v>
+        <v>2.855610548128818</v>
       </c>
       <c r="T99">
-        <v>27.25744475020012</v>
+        <v>40.88616712530017</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09105634045451497</v>
+        <v>0.09012719412334642</v>
       </c>
       <c r="W99">
-        <v>0.2143289149208254</v>
+        <v>0.2145480076257149</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3035211348483833</v>
+        <v>0.3004239804111548</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.267369258435777</v>
+        <v>0.269269258435777</v>
       </c>
       <c r="C100">
-        <v>-109.2534984813799</v>
+        <v>-111.6903629443849</v>
       </c>
       <c r="D100">
-        <v>68.92850151862007</v>
+        <v>68.4506370556151</v>
       </c>
       <c r="E100">
-        <v>70.282</v>
+        <v>72.241</v>
       </c>
       <c r="F100">
-        <v>191.982</v>
+        <v>193.941</v>
       </c>
       <c r="G100">
         <v>13.8</v>
@@ -9481,37 +9481,37 @@
         <v>13.6</v>
       </c>
       <c r="M100">
-        <v>45.2693556</v>
+        <v>45.7312878</v>
       </c>
       <c r="N100">
-        <v>-31.6693556</v>
+        <v>-32.1312878</v>
       </c>
       <c r="O100">
-        <v>-9.50080668</v>
+        <v>-9.63938634</v>
       </c>
       <c r="P100">
-        <v>-22.16854892</v>
+        <v>-22.49190146</v>
       </c>
       <c r="Q100">
-        <v>-1.268548920000004</v>
+        <v>-1.591901460000003</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.855610548128818</v>
+        <v>5.665421096257637</v>
       </c>
       <c r="T100">
-        <v>40.88616712530017</v>
+        <v>81.77233425060034</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09012719412334642</v>
+        <v>0.08921681842513082</v>
       </c>
       <c r="W100">
-        <v>0.2145480076257149</v>
+        <v>0.2147626742153542</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3004239804111548</v>
+        <v>0.297389394750436</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.269269258435777</v>
-      </c>
-      <c r="C101">
-        <v>-111.6903629443849</v>
-      </c>
-      <c r="D101">
-        <v>68.4506370556151</v>
-      </c>
-      <c r="E101">
-        <v>72.241</v>
-      </c>
-      <c r="F101">
-        <v>193.941</v>
-      </c>
-      <c r="G101">
-        <v>13.8</v>
-      </c>
-      <c r="H101">
-        <v>74.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>34.5</v>
-      </c>
-      <c r="K101">
-        <v>20.9</v>
-      </c>
-      <c r="L101">
-        <v>13.6</v>
-      </c>
-      <c r="M101">
-        <v>45.7312878</v>
-      </c>
-      <c r="N101">
-        <v>-32.1312878</v>
-      </c>
-      <c r="O101">
-        <v>-9.63938634</v>
-      </c>
-      <c r="P101">
-        <v>-22.49190146</v>
-      </c>
-      <c r="Q101">
-        <v>-1.591901460000003</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.665421096257637</v>
-      </c>
-      <c r="T101">
-        <v>81.77233425060034</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08921681842513082</v>
-      </c>
-      <c r="W101">
-        <v>0.2147626742153542</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.297389394750436</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
